--- a/Documents/Planification_Projet_2026.xlsx
+++ b/Documents/Planification_Projet_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lerouxe.SNIRW\Projet_banc_test_self\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fauret.SNIRW\Projet_banc_test_self\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55649459-8598-4EBA-B1E7-E6DEA77B3838}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB1C592-604F-48DE-A3FE-B57D5DBD865C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SRC" sheetId="1" r:id="rId1"/>
@@ -2022,37 +2022,30 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2071,12 +2064,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2618,12 +2618,12 @@
       <c r="Y1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="57">
+      <c r="Z1" s="80">
         <v>2024</v>
       </c>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="59"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="82"/>
       <c r="AD1" s="6"/>
       <c r="AE1" s="4" t="s">
         <v>2</v>
@@ -2678,10 +2678,10 @@
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
       <c r="I3" s="13" t="s">
         <v>5</v>
       </c>
@@ -2746,31 +2746,31 @@
         <v>25</v>
       </c>
       <c r="AD3" s="6"/>
-      <c r="AE3" s="64" t="s">
+      <c r="AE3" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="65"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="65"/>
-      <c r="AL3" s="66"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="60"/>
     </row>
     <row r="4" spans="1:38" ht="14.25" customHeight="1">
-      <c r="D4" s="60"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
       <c r="AD4" s="6"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="61"/>
-      <c r="AG4" s="61"/>
-      <c r="AH4" s="61"/>
-      <c r="AI4" s="61"/>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="68"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="62"/>
+      <c r="AG4" s="62"/>
+      <c r="AH4" s="62"/>
+      <c r="AI4" s="62"/>
+      <c r="AJ4" s="62"/>
+      <c r="AK4" s="62"/>
+      <c r="AL4" s="63"/>
     </row>
     <row r="5" spans="1:38" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
@@ -2811,20 +2811,20 @@
       <c r="AA5" s="16"/>
       <c r="AC5" s="16"/>
       <c r="AD5" s="6"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="68"/>
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="62"/>
+      <c r="AG5" s="62"/>
+      <c r="AH5" s="62"/>
+      <c r="AI5" s="62"/>
+      <c r="AJ5" s="62"/>
+      <c r="AK5" s="62"/>
+      <c r="AL5" s="63"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="72"/>
+      <c r="B6" s="68"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -2852,14 +2852,14 @@
       <c r="AB6" s="17"/>
       <c r="AC6" s="17"/>
       <c r="AD6" s="6"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="61"/>
-      <c r="AG6" s="61"/>
-      <c r="AH6" s="61"/>
-      <c r="AI6" s="61"/>
-      <c r="AJ6" s="61"/>
-      <c r="AK6" s="61"/>
-      <c r="AL6" s="68"/>
+      <c r="AE6" s="61"/>
+      <c r="AF6" s="62"/>
+      <c r="AG6" s="62"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="62"/>
+      <c r="AK6" s="62"/>
+      <c r="AL6" s="63"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="55"/>
@@ -2891,20 +2891,20 @@
       <c r="AB7" s="17"/>
       <c r="AC7" s="17"/>
       <c r="AD7" s="6"/>
-      <c r="AE7" s="67"/>
-      <c r="AF7" s="61"/>
-      <c r="AG7" s="61"/>
-      <c r="AH7" s="61"/>
-      <c r="AI7" s="61"/>
-      <c r="AJ7" s="61"/>
-      <c r="AK7" s="61"/>
-      <c r="AL7" s="68"/>
+      <c r="AE7" s="61"/>
+      <c r="AF7" s="62"/>
+      <c r="AG7" s="62"/>
+      <c r="AH7" s="62"/>
+      <c r="AI7" s="62"/>
+      <c r="AJ7" s="62"/>
+      <c r="AK7" s="62"/>
+      <c r="AL7" s="63"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="63"/>
+      <c r="B8" s="69"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
@@ -2932,14 +2932,14 @@
       <c r="AB8" s="17"/>
       <c r="AC8" s="17"/>
       <c r="AD8" s="6"/>
-      <c r="AE8" s="67"/>
-      <c r="AF8" s="61"/>
-      <c r="AG8" s="61"/>
-      <c r="AH8" s="61"/>
-      <c r="AI8" s="61"/>
-      <c r="AJ8" s="61"/>
-      <c r="AK8" s="61"/>
-      <c r="AL8" s="68"/>
+      <c r="AE8" s="61"/>
+      <c r="AF8" s="62"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="62"/>
+      <c r="AL8" s="63"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1">
       <c r="A9" s="55"/>
@@ -2971,20 +2971,20 @@
       <c r="AB9" s="17"/>
       <c r="AC9" s="17"/>
       <c r="AD9" s="6"/>
-      <c r="AE9" s="67"/>
-      <c r="AF9" s="61"/>
-      <c r="AG9" s="61"/>
-      <c r="AH9" s="61"/>
-      <c r="AI9" s="61"/>
-      <c r="AJ9" s="61"/>
-      <c r="AK9" s="61"/>
-      <c r="AL9" s="68"/>
+      <c r="AE9" s="61"/>
+      <c r="AF9" s="62"/>
+      <c r="AG9" s="62"/>
+      <c r="AH9" s="62"/>
+      <c r="AI9" s="62"/>
+      <c r="AJ9" s="62"/>
+      <c r="AK9" s="62"/>
+      <c r="AL9" s="63"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="63"/>
+      <c r="B10" s="69"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -3012,14 +3012,14 @@
       <c r="AB10" s="17"/>
       <c r="AC10" s="17"/>
       <c r="AD10" s="6"/>
-      <c r="AE10" s="67"/>
-      <c r="AF10" s="61"/>
-      <c r="AG10" s="61"/>
-      <c r="AH10" s="61"/>
-      <c r="AI10" s="61"/>
-      <c r="AJ10" s="61"/>
-      <c r="AK10" s="61"/>
-      <c r="AL10" s="68"/>
+      <c r="AE10" s="61"/>
+      <c r="AF10" s="62"/>
+      <c r="AG10" s="62"/>
+      <c r="AH10" s="62"/>
+      <c r="AI10" s="62"/>
+      <c r="AJ10" s="62"/>
+      <c r="AK10" s="62"/>
+      <c r="AL10" s="63"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1">
       <c r="A11" s="55"/>
@@ -3051,20 +3051,20 @@
       <c r="AB11" s="17"/>
       <c r="AC11" s="17"/>
       <c r="AD11" s="6"/>
-      <c r="AE11" s="67"/>
-      <c r="AF11" s="61"/>
-      <c r="AG11" s="61"/>
-      <c r="AH11" s="61"/>
-      <c r="AI11" s="61"/>
-      <c r="AJ11" s="61"/>
-      <c r="AK11" s="61"/>
-      <c r="AL11" s="68"/>
+      <c r="AE11" s="61"/>
+      <c r="AF11" s="62"/>
+      <c r="AG11" s="62"/>
+      <c r="AH11" s="62"/>
+      <c r="AI11" s="62"/>
+      <c r="AJ11" s="62"/>
+      <c r="AK11" s="62"/>
+      <c r="AL11" s="63"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="63"/>
+      <c r="B12" s="69"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -3092,14 +3092,14 @@
       <c r="AB12" s="17"/>
       <c r="AC12" s="17"/>
       <c r="AD12" s="6"/>
-      <c r="AE12" s="67"/>
-      <c r="AF12" s="61"/>
-      <c r="AG12" s="61"/>
-      <c r="AH12" s="61"/>
-      <c r="AI12" s="61"/>
-      <c r="AJ12" s="61"/>
-      <c r="AK12" s="61"/>
-      <c r="AL12" s="68"/>
+      <c r="AE12" s="61"/>
+      <c r="AF12" s="62"/>
+      <c r="AG12" s="62"/>
+      <c r="AH12" s="62"/>
+      <c r="AI12" s="62"/>
+      <c r="AJ12" s="62"/>
+      <c r="AK12" s="62"/>
+      <c r="AL12" s="63"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1">
       <c r="A13" s="55"/>
@@ -3131,20 +3131,20 @@
       <c r="AB13" s="17"/>
       <c r="AC13" s="17"/>
       <c r="AD13" s="6"/>
-      <c r="AE13" s="67"/>
-      <c r="AF13" s="61"/>
-      <c r="AG13" s="61"/>
-      <c r="AH13" s="61"/>
-      <c r="AI13" s="61"/>
-      <c r="AJ13" s="61"/>
-      <c r="AK13" s="61"/>
-      <c r="AL13" s="68"/>
+      <c r="AE13" s="61"/>
+      <c r="AF13" s="62"/>
+      <c r="AG13" s="62"/>
+      <c r="AH13" s="62"/>
+      <c r="AI13" s="62"/>
+      <c r="AJ13" s="62"/>
+      <c r="AK13" s="62"/>
+      <c r="AL13" s="63"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="63"/>
+      <c r="B14" s="69"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -3172,14 +3172,14 @@
       <c r="AB14" s="17"/>
       <c r="AC14" s="17"/>
       <c r="AD14" s="6"/>
-      <c r="AE14" s="67"/>
-      <c r="AF14" s="61"/>
-      <c r="AG14" s="61"/>
-      <c r="AH14" s="61"/>
-      <c r="AI14" s="61"/>
-      <c r="AJ14" s="61"/>
-      <c r="AK14" s="61"/>
-      <c r="AL14" s="68"/>
+      <c r="AE14" s="61"/>
+      <c r="AF14" s="62"/>
+      <c r="AG14" s="62"/>
+      <c r="AH14" s="62"/>
+      <c r="AI14" s="62"/>
+      <c r="AJ14" s="62"/>
+      <c r="AK14" s="62"/>
+      <c r="AL14" s="63"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1">
       <c r="A15" s="55"/>
@@ -3211,20 +3211,20 @@
       <c r="AB15" s="17"/>
       <c r="AC15" s="17"/>
       <c r="AD15" s="6"/>
-      <c r="AE15" s="67"/>
-      <c r="AF15" s="61"/>
-      <c r="AG15" s="61"/>
-      <c r="AH15" s="61"/>
-      <c r="AI15" s="61"/>
-      <c r="AJ15" s="61"/>
-      <c r="AK15" s="61"/>
-      <c r="AL15" s="68"/>
+      <c r="AE15" s="61"/>
+      <c r="AF15" s="62"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="62"/>
+      <c r="AL15" s="63"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="54"/>
+      <c r="B16" s="56"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -3252,14 +3252,14 @@
       <c r="AB16" s="17"/>
       <c r="AC16" s="17"/>
       <c r="AD16" s="6"/>
-      <c r="AE16" s="67"/>
-      <c r="AF16" s="61"/>
-      <c r="AG16" s="61"/>
-      <c r="AH16" s="61"/>
-      <c r="AI16" s="61"/>
-      <c r="AJ16" s="61"/>
-      <c r="AK16" s="61"/>
-      <c r="AL16" s="68"/>
+      <c r="AE16" s="61"/>
+      <c r="AF16" s="62"/>
+      <c r="AG16" s="62"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="62"/>
+      <c r="AJ16" s="62"/>
+      <c r="AK16" s="62"/>
+      <c r="AL16" s="63"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
       <c r="A17" s="55"/>
@@ -3291,20 +3291,20 @@
       <c r="AB17" s="17"/>
       <c r="AC17" s="17"/>
       <c r="AD17" s="6"/>
-      <c r="AE17" s="67"/>
-      <c r="AF17" s="61"/>
-      <c r="AG17" s="61"/>
-      <c r="AH17" s="61"/>
-      <c r="AI17" s="61"/>
-      <c r="AJ17" s="61"/>
-      <c r="AK17" s="61"/>
-      <c r="AL17" s="68"/>
+      <c r="AE17" s="61"/>
+      <c r="AF17" s="62"/>
+      <c r="AG17" s="62"/>
+      <c r="AH17" s="62"/>
+      <c r="AI17" s="62"/>
+      <c r="AJ17" s="62"/>
+      <c r="AK17" s="62"/>
+      <c r="AL17" s="63"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="54"/>
+      <c r="B18" s="56"/>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -3332,14 +3332,14 @@
       <c r="AB18" s="17"/>
       <c r="AC18" s="17"/>
       <c r="AD18" s="6"/>
-      <c r="AE18" s="67"/>
-      <c r="AF18" s="61"/>
-      <c r="AG18" s="61"/>
-      <c r="AH18" s="61"/>
-      <c r="AI18" s="61"/>
-      <c r="AJ18" s="61"/>
-      <c r="AK18" s="61"/>
-      <c r="AL18" s="68"/>
+      <c r="AE18" s="61"/>
+      <c r="AF18" s="62"/>
+      <c r="AG18" s="62"/>
+      <c r="AH18" s="62"/>
+      <c r="AI18" s="62"/>
+      <c r="AJ18" s="62"/>
+      <c r="AK18" s="62"/>
+      <c r="AL18" s="63"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1">
       <c r="A19" s="55"/>
@@ -3371,20 +3371,20 @@
       <c r="AB19" s="17"/>
       <c r="AC19" s="17"/>
       <c r="AD19" s="6"/>
-      <c r="AE19" s="67"/>
-      <c r="AF19" s="61"/>
-      <c r="AG19" s="61"/>
-      <c r="AH19" s="61"/>
-      <c r="AI19" s="61"/>
-      <c r="AJ19" s="61"/>
-      <c r="AK19" s="61"/>
-      <c r="AL19" s="68"/>
+      <c r="AE19" s="61"/>
+      <c r="AF19" s="62"/>
+      <c r="AG19" s="62"/>
+      <c r="AH19" s="62"/>
+      <c r="AI19" s="62"/>
+      <c r="AJ19" s="62"/>
+      <c r="AK19" s="62"/>
+      <c r="AL19" s="63"/>
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="54"/>
+      <c r="B20" s="56"/>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -3412,14 +3412,14 @@
       <c r="AB20" s="17"/>
       <c r="AC20" s="17"/>
       <c r="AD20" s="6"/>
-      <c r="AE20" s="67"/>
-      <c r="AF20" s="61"/>
-      <c r="AG20" s="61"/>
-      <c r="AH20" s="61"/>
-      <c r="AI20" s="61"/>
-      <c r="AJ20" s="61"/>
-      <c r="AK20" s="61"/>
-      <c r="AL20" s="68"/>
+      <c r="AE20" s="61"/>
+      <c r="AF20" s="62"/>
+      <c r="AG20" s="62"/>
+      <c r="AH20" s="62"/>
+      <c r="AI20" s="62"/>
+      <c r="AJ20" s="62"/>
+      <c r="AK20" s="62"/>
+      <c r="AL20" s="63"/>
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
       <c r="A21" s="55"/>
@@ -3451,20 +3451,20 @@
       <c r="AB21" s="17"/>
       <c r="AC21" s="17"/>
       <c r="AD21" s="6"/>
-      <c r="AE21" s="67"/>
-      <c r="AF21" s="61"/>
-      <c r="AG21" s="61"/>
-      <c r="AH21" s="61"/>
-      <c r="AI21" s="61"/>
-      <c r="AJ21" s="61"/>
-      <c r="AK21" s="61"/>
-      <c r="AL21" s="68"/>
+      <c r="AE21" s="61"/>
+      <c r="AF21" s="62"/>
+      <c r="AG21" s="62"/>
+      <c r="AH21" s="62"/>
+      <c r="AI21" s="62"/>
+      <c r="AJ21" s="62"/>
+      <c r="AK21" s="62"/>
+      <c r="AL21" s="63"/>
     </row>
     <row r="22" spans="1:38" ht="15" customHeight="1">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="54"/>
+      <c r="B22" s="56"/>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -3492,14 +3492,14 @@
       <c r="AB22" s="17"/>
       <c r="AC22" s="17"/>
       <c r="AD22" s="6"/>
-      <c r="AE22" s="67"/>
-      <c r="AF22" s="61"/>
-      <c r="AG22" s="61"/>
-      <c r="AH22" s="61"/>
-      <c r="AI22" s="61"/>
-      <c r="AJ22" s="61"/>
-      <c r="AK22" s="61"/>
-      <c r="AL22" s="68"/>
+      <c r="AE22" s="61"/>
+      <c r="AF22" s="62"/>
+      <c r="AG22" s="62"/>
+      <c r="AH22" s="62"/>
+      <c r="AI22" s="62"/>
+      <c r="AJ22" s="62"/>
+      <c r="AK22" s="62"/>
+      <c r="AL22" s="63"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
       <c r="A23" s="55"/>
@@ -3531,20 +3531,20 @@
       <c r="AB23" s="17"/>
       <c r="AC23" s="17"/>
       <c r="AD23" s="6"/>
-      <c r="AE23" s="67"/>
-      <c r="AF23" s="61"/>
-      <c r="AG23" s="61"/>
-      <c r="AH23" s="61"/>
-      <c r="AI23" s="61"/>
-      <c r="AJ23" s="61"/>
-      <c r="AK23" s="61"/>
-      <c r="AL23" s="68"/>
+      <c r="AE23" s="61"/>
+      <c r="AF23" s="62"/>
+      <c r="AG23" s="62"/>
+      <c r="AH23" s="62"/>
+      <c r="AI23" s="62"/>
+      <c r="AJ23" s="62"/>
+      <c r="AK23" s="62"/>
+      <c r="AL23" s="63"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="54"/>
+      <c r="B24" s="56"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -3572,14 +3572,14 @@
       <c r="AB24" s="17"/>
       <c r="AC24" s="17"/>
       <c r="AD24" s="6"/>
-      <c r="AE24" s="67"/>
-      <c r="AF24" s="61"/>
-      <c r="AG24" s="61"/>
-      <c r="AH24" s="61"/>
-      <c r="AI24" s="61"/>
-      <c r="AJ24" s="61"/>
-      <c r="AK24" s="61"/>
-      <c r="AL24" s="68"/>
+      <c r="AE24" s="61"/>
+      <c r="AF24" s="62"/>
+      <c r="AG24" s="62"/>
+      <c r="AH24" s="62"/>
+      <c r="AI24" s="62"/>
+      <c r="AJ24" s="62"/>
+      <c r="AK24" s="62"/>
+      <c r="AL24" s="63"/>
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" s="55"/>
@@ -3611,20 +3611,20 @@
       <c r="AB25" s="17"/>
       <c r="AC25" s="17"/>
       <c r="AD25" s="6"/>
-      <c r="AE25" s="67"/>
-      <c r="AF25" s="61"/>
-      <c r="AG25" s="61"/>
-      <c r="AH25" s="61"/>
-      <c r="AI25" s="61"/>
-      <c r="AJ25" s="61"/>
-      <c r="AK25" s="61"/>
-      <c r="AL25" s="68"/>
+      <c r="AE25" s="61"/>
+      <c r="AF25" s="62"/>
+      <c r="AG25" s="62"/>
+      <c r="AH25" s="62"/>
+      <c r="AI25" s="62"/>
+      <c r="AJ25" s="62"/>
+      <c r="AK25" s="62"/>
+      <c r="AL25" s="63"/>
     </row>
     <row r="26" spans="1:38" ht="15" customHeight="1">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="54"/>
+      <c r="B26" s="56"/>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -3652,14 +3652,14 @@
       <c r="AB26" s="17"/>
       <c r="AC26" s="17"/>
       <c r="AD26" s="6"/>
-      <c r="AE26" s="67"/>
-      <c r="AF26" s="61"/>
-      <c r="AG26" s="61"/>
-      <c r="AH26" s="61"/>
-      <c r="AI26" s="61"/>
-      <c r="AJ26" s="61"/>
-      <c r="AK26" s="61"/>
-      <c r="AL26" s="68"/>
+      <c r="AE26" s="61"/>
+      <c r="AF26" s="62"/>
+      <c r="AG26" s="62"/>
+      <c r="AH26" s="62"/>
+      <c r="AI26" s="62"/>
+      <c r="AJ26" s="62"/>
+      <c r="AK26" s="62"/>
+      <c r="AL26" s="63"/>
     </row>
     <row r="27" spans="1:38" ht="15" customHeight="1">
       <c r="A27" s="55"/>
@@ -3691,20 +3691,20 @@
       <c r="AB27" s="17"/>
       <c r="AC27" s="17"/>
       <c r="AD27" s="6"/>
-      <c r="AE27" s="67"/>
-      <c r="AF27" s="61"/>
-      <c r="AG27" s="61"/>
-      <c r="AH27" s="61"/>
-      <c r="AI27" s="61"/>
-      <c r="AJ27" s="61"/>
-      <c r="AK27" s="61"/>
-      <c r="AL27" s="68"/>
+      <c r="AE27" s="61"/>
+      <c r="AF27" s="62"/>
+      <c r="AG27" s="62"/>
+      <c r="AH27" s="62"/>
+      <c r="AI27" s="62"/>
+      <c r="AJ27" s="62"/>
+      <c r="AK27" s="62"/>
+      <c r="AL27" s="63"/>
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="54"/>
+      <c r="B28" s="56"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -3732,14 +3732,14 @@
       <c r="AB28" s="17"/>
       <c r="AC28" s="17"/>
       <c r="AD28" s="6"/>
-      <c r="AE28" s="67"/>
-      <c r="AF28" s="61"/>
-      <c r="AG28" s="61"/>
-      <c r="AH28" s="61"/>
-      <c r="AI28" s="61"/>
-      <c r="AJ28" s="61"/>
-      <c r="AK28" s="61"/>
-      <c r="AL28" s="68"/>
+      <c r="AE28" s="61"/>
+      <c r="AF28" s="62"/>
+      <c r="AG28" s="62"/>
+      <c r="AH28" s="62"/>
+      <c r="AI28" s="62"/>
+      <c r="AJ28" s="62"/>
+      <c r="AK28" s="62"/>
+      <c r="AL28" s="63"/>
     </row>
     <row r="29" spans="1:38" ht="15" customHeight="1">
       <c r="A29" s="55"/>
@@ -3771,20 +3771,20 @@
       <c r="AB29" s="17"/>
       <c r="AC29" s="17"/>
       <c r="AD29" s="6"/>
-      <c r="AE29" s="67"/>
-      <c r="AF29" s="61"/>
-      <c r="AG29" s="61"/>
-      <c r="AH29" s="61"/>
-      <c r="AI29" s="61"/>
-      <c r="AJ29" s="61"/>
-      <c r="AK29" s="61"/>
-      <c r="AL29" s="68"/>
+      <c r="AE29" s="61"/>
+      <c r="AF29" s="62"/>
+      <c r="AG29" s="62"/>
+      <c r="AH29" s="62"/>
+      <c r="AI29" s="62"/>
+      <c r="AJ29" s="62"/>
+      <c r="AK29" s="62"/>
+      <c r="AL29" s="63"/>
     </row>
     <row r="30" spans="1:38" ht="15" customHeight="1">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="54"/>
+      <c r="B30" s="56"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -3812,14 +3812,14 @@
       <c r="AB30" s="17"/>
       <c r="AC30" s="17"/>
       <c r="AD30" s="6"/>
-      <c r="AE30" s="67"/>
-      <c r="AF30" s="61"/>
-      <c r="AG30" s="61"/>
-      <c r="AH30" s="61"/>
-      <c r="AI30" s="61"/>
-      <c r="AJ30" s="61"/>
-      <c r="AK30" s="61"/>
-      <c r="AL30" s="68"/>
+      <c r="AE30" s="61"/>
+      <c r="AF30" s="62"/>
+      <c r="AG30" s="62"/>
+      <c r="AH30" s="62"/>
+      <c r="AI30" s="62"/>
+      <c r="AJ30" s="62"/>
+      <c r="AK30" s="62"/>
+      <c r="AL30" s="63"/>
     </row>
     <row r="31" spans="1:38" ht="15" customHeight="1">
       <c r="A31" s="55"/>
@@ -3851,20 +3851,20 @@
       <c r="AB31" s="17"/>
       <c r="AC31" s="17"/>
       <c r="AD31" s="6"/>
-      <c r="AE31" s="67"/>
-      <c r="AF31" s="61"/>
-      <c r="AG31" s="61"/>
-      <c r="AH31" s="61"/>
-      <c r="AI31" s="61"/>
-      <c r="AJ31" s="61"/>
-      <c r="AK31" s="61"/>
-      <c r="AL31" s="68"/>
+      <c r="AE31" s="61"/>
+      <c r="AF31" s="62"/>
+      <c r="AG31" s="62"/>
+      <c r="AH31" s="62"/>
+      <c r="AI31" s="62"/>
+      <c r="AJ31" s="62"/>
+      <c r="AK31" s="62"/>
+      <c r="AL31" s="63"/>
     </row>
     <row r="32" spans="1:38" ht="15" customHeight="1">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="81"/>
+      <c r="B32" s="78"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -3892,14 +3892,14 @@
       <c r="AB32" s="17"/>
       <c r="AC32" s="17"/>
       <c r="AD32" s="6"/>
-      <c r="AE32" s="67"/>
-      <c r="AF32" s="61"/>
-      <c r="AG32" s="61"/>
-      <c r="AH32" s="61"/>
-      <c r="AI32" s="61"/>
-      <c r="AJ32" s="61"/>
-      <c r="AK32" s="61"/>
-      <c r="AL32" s="68"/>
+      <c r="AE32" s="61"/>
+      <c r="AF32" s="62"/>
+      <c r="AG32" s="62"/>
+      <c r="AH32" s="62"/>
+      <c r="AI32" s="62"/>
+      <c r="AJ32" s="62"/>
+      <c r="AK32" s="62"/>
+      <c r="AL32" s="63"/>
     </row>
     <row r="33" spans="1:38" ht="15" customHeight="1">
       <c r="A33" s="55"/>
@@ -3931,20 +3931,20 @@
       <c r="AB33" s="17"/>
       <c r="AC33" s="17"/>
       <c r="AD33" s="6"/>
-      <c r="AE33" s="67"/>
-      <c r="AF33" s="61"/>
-      <c r="AG33" s="61"/>
-      <c r="AH33" s="61"/>
-      <c r="AI33" s="61"/>
-      <c r="AJ33" s="61"/>
-      <c r="AK33" s="61"/>
-      <c r="AL33" s="68"/>
+      <c r="AE33" s="61"/>
+      <c r="AF33" s="62"/>
+      <c r="AG33" s="62"/>
+      <c r="AH33" s="62"/>
+      <c r="AI33" s="62"/>
+      <c r="AJ33" s="62"/>
+      <c r="AK33" s="62"/>
+      <c r="AL33" s="63"/>
     </row>
     <row r="34" spans="1:38" ht="15" customHeight="1">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="82"/>
+      <c r="B34" s="79"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -3972,14 +3972,14 @@
       <c r="AB34" s="17"/>
       <c r="AC34" s="17"/>
       <c r="AD34" s="6"/>
-      <c r="AE34" s="67"/>
-      <c r="AF34" s="61"/>
-      <c r="AG34" s="61"/>
-      <c r="AH34" s="61"/>
-      <c r="AI34" s="61"/>
-      <c r="AJ34" s="61"/>
-      <c r="AK34" s="61"/>
-      <c r="AL34" s="68"/>
+      <c r="AE34" s="61"/>
+      <c r="AF34" s="62"/>
+      <c r="AG34" s="62"/>
+      <c r="AH34" s="62"/>
+      <c r="AI34" s="62"/>
+      <c r="AJ34" s="62"/>
+      <c r="AK34" s="62"/>
+      <c r="AL34" s="63"/>
     </row>
     <row r="35" spans="1:38" ht="15" customHeight="1">
       <c r="A35" s="55"/>
@@ -4011,20 +4011,20 @@
       <c r="AB35" s="17"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="6"/>
-      <c r="AE35" s="69"/>
-      <c r="AF35" s="70"/>
-      <c r="AG35" s="70"/>
-      <c r="AH35" s="70"/>
-      <c r="AI35" s="70"/>
-      <c r="AJ35" s="70"/>
-      <c r="AK35" s="70"/>
-      <c r="AL35" s="71"/>
+      <c r="AE35" s="64"/>
+      <c r="AF35" s="65"/>
+      <c r="AG35" s="65"/>
+      <c r="AH35" s="65"/>
+      <c r="AI35" s="65"/>
+      <c r="AJ35" s="65"/>
+      <c r="AK35" s="65"/>
+      <c r="AL35" s="66"/>
     </row>
     <row r="36" spans="1:38" ht="15" customHeight="1">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="54"/>
+      <c r="B36" s="56"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -4101,10 +4101,10 @@
       <c r="AL37" s="6"/>
     </row>
     <row r="38" spans="1:38" ht="15" customHeight="1">
-      <c r="A38" s="56" t="s">
+      <c r="A38" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="54"/>
+      <c r="B38" s="56"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -4171,22 +4171,22 @@
       <c r="AB39" s="17"/>
       <c r="AC39" s="17"/>
       <c r="AD39" s="6"/>
-      <c r="AE39" s="73" t="s">
+      <c r="AE39" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="AF39" s="74"/>
-      <c r="AG39" s="74"/>
-      <c r="AH39" s="74"/>
-      <c r="AI39" s="74"/>
-      <c r="AJ39" s="74"/>
-      <c r="AK39" s="74"/>
-      <c r="AL39" s="75"/>
+      <c r="AF39" s="71"/>
+      <c r="AG39" s="71"/>
+      <c r="AH39" s="71"/>
+      <c r="AI39" s="71"/>
+      <c r="AJ39" s="71"/>
+      <c r="AK39" s="71"/>
+      <c r="AL39" s="72"/>
     </row>
     <row r="40" spans="1:38" ht="15" customHeight="1">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="54"/>
+      <c r="B40" s="56"/>
       <c r="D40" s="22"/>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -4214,14 +4214,14 @@
       <c r="AB40" s="17"/>
       <c r="AC40" s="17"/>
       <c r="AD40" s="6"/>
-      <c r="AE40" s="76"/>
-      <c r="AF40" s="61"/>
-      <c r="AG40" s="61"/>
-      <c r="AH40" s="61"/>
-      <c r="AI40" s="61"/>
-      <c r="AJ40" s="61"/>
-      <c r="AK40" s="61"/>
-      <c r="AL40" s="77"/>
+      <c r="AE40" s="73"/>
+      <c r="AF40" s="62"/>
+      <c r="AG40" s="62"/>
+      <c r="AH40" s="62"/>
+      <c r="AI40" s="62"/>
+      <c r="AJ40" s="62"/>
+      <c r="AK40" s="62"/>
+      <c r="AL40" s="74"/>
     </row>
     <row r="41" spans="1:38" ht="15" customHeight="1">
       <c r="A41" s="55"/>
@@ -4253,20 +4253,20 @@
       <c r="AB41" s="17"/>
       <c r="AC41" s="17"/>
       <c r="AD41" s="6"/>
-      <c r="AE41" s="76"/>
-      <c r="AF41" s="61"/>
-      <c r="AG41" s="61"/>
-      <c r="AH41" s="61"/>
-      <c r="AI41" s="61"/>
-      <c r="AJ41" s="61"/>
-      <c r="AK41" s="61"/>
-      <c r="AL41" s="77"/>
+      <c r="AE41" s="73"/>
+      <c r="AF41" s="62"/>
+      <c r="AG41" s="62"/>
+      <c r="AH41" s="62"/>
+      <c r="AI41" s="62"/>
+      <c r="AJ41" s="62"/>
+      <c r="AK41" s="62"/>
+      <c r="AL41" s="74"/>
     </row>
     <row r="42" spans="1:38" ht="15" customHeight="1">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="54"/>
+      <c r="B42" s="56"/>
       <c r="D42" s="22"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -4294,14 +4294,14 @@
       <c r="AB42" s="17"/>
       <c r="AC42" s="17"/>
       <c r="AD42" s="6"/>
-      <c r="AE42" s="76"/>
-      <c r="AF42" s="61"/>
-      <c r="AG42" s="61"/>
-      <c r="AH42" s="61"/>
-      <c r="AI42" s="61"/>
-      <c r="AJ42" s="61"/>
-      <c r="AK42" s="61"/>
-      <c r="AL42" s="77"/>
+      <c r="AE42" s="73"/>
+      <c r="AF42" s="62"/>
+      <c r="AG42" s="62"/>
+      <c r="AH42" s="62"/>
+      <c r="AI42" s="62"/>
+      <c r="AJ42" s="62"/>
+      <c r="AK42" s="62"/>
+      <c r="AL42" s="74"/>
     </row>
     <row r="43" spans="1:38" ht="15" customHeight="1">
       <c r="A43" s="55"/>
@@ -4333,20 +4333,20 @@
       <c r="AB43" s="17"/>
       <c r="AC43" s="17"/>
       <c r="AD43" s="6"/>
-      <c r="AE43" s="76"/>
-      <c r="AF43" s="61"/>
-      <c r="AG43" s="61"/>
-      <c r="AH43" s="61"/>
-      <c r="AI43" s="61"/>
-      <c r="AJ43" s="61"/>
-      <c r="AK43" s="61"/>
-      <c r="AL43" s="77"/>
+      <c r="AE43" s="73"/>
+      <c r="AF43" s="62"/>
+      <c r="AG43" s="62"/>
+      <c r="AH43" s="62"/>
+      <c r="AI43" s="62"/>
+      <c r="AJ43" s="62"/>
+      <c r="AK43" s="62"/>
+      <c r="AL43" s="74"/>
     </row>
     <row r="44" spans="1:38" ht="15" customHeight="1">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="62"/>
+      <c r="B44" s="83"/>
       <c r="D44" s="22"/>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -4374,14 +4374,14 @@
       <c r="AB44" s="17"/>
       <c r="AC44" s="17"/>
       <c r="AD44" s="6"/>
-      <c r="AE44" s="76"/>
-      <c r="AF44" s="61"/>
-      <c r="AG44" s="61"/>
-      <c r="AH44" s="61"/>
-      <c r="AI44" s="61"/>
-      <c r="AJ44" s="61"/>
-      <c r="AK44" s="61"/>
-      <c r="AL44" s="77"/>
+      <c r="AE44" s="73"/>
+      <c r="AF44" s="62"/>
+      <c r="AG44" s="62"/>
+      <c r="AH44" s="62"/>
+      <c r="AI44" s="62"/>
+      <c r="AJ44" s="62"/>
+      <c r="AK44" s="62"/>
+      <c r="AL44" s="74"/>
     </row>
     <row r="45" spans="1:38" ht="15" customHeight="1">
       <c r="A45" s="55"/>
@@ -4413,20 +4413,20 @@
       <c r="AB45" s="17"/>
       <c r="AC45" s="17"/>
       <c r="AD45" s="6"/>
-      <c r="AE45" s="76"/>
-      <c r="AF45" s="61"/>
-      <c r="AG45" s="61"/>
-      <c r="AH45" s="61"/>
-      <c r="AI45" s="61"/>
-      <c r="AJ45" s="61"/>
-      <c r="AK45" s="61"/>
-      <c r="AL45" s="77"/>
+      <c r="AE45" s="73"/>
+      <c r="AF45" s="62"/>
+      <c r="AG45" s="62"/>
+      <c r="AH45" s="62"/>
+      <c r="AI45" s="62"/>
+      <c r="AJ45" s="62"/>
+      <c r="AK45" s="62"/>
+      <c r="AL45" s="74"/>
     </row>
     <row r="46" spans="1:38" ht="15" customHeight="1">
-      <c r="A46" s="56" t="s">
+      <c r="A46" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="54"/>
+      <c r="B46" s="56"/>
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -4454,14 +4454,14 @@
       <c r="AB46" s="17"/>
       <c r="AC46" s="17"/>
       <c r="AD46" s="6"/>
-      <c r="AE46" s="76"/>
-      <c r="AF46" s="61"/>
-      <c r="AG46" s="61"/>
-      <c r="AH46" s="61"/>
-      <c r="AI46" s="61"/>
-      <c r="AJ46" s="61"/>
-      <c r="AK46" s="61"/>
-      <c r="AL46" s="77"/>
+      <c r="AE46" s="73"/>
+      <c r="AF46" s="62"/>
+      <c r="AG46" s="62"/>
+      <c r="AH46" s="62"/>
+      <c r="AI46" s="62"/>
+      <c r="AJ46" s="62"/>
+      <c r="AK46" s="62"/>
+      <c r="AL46" s="74"/>
     </row>
     <row r="47" spans="1:38" ht="15" customHeight="1">
       <c r="A47" s="55"/>
@@ -4493,20 +4493,20 @@
       <c r="AB47" s="17"/>
       <c r="AC47" s="17"/>
       <c r="AD47" s="6"/>
-      <c r="AE47" s="76"/>
-      <c r="AF47" s="61"/>
-      <c r="AG47" s="61"/>
-      <c r="AH47" s="61"/>
-      <c r="AI47" s="61"/>
-      <c r="AJ47" s="61"/>
-      <c r="AK47" s="61"/>
-      <c r="AL47" s="77"/>
+      <c r="AE47" s="73"/>
+      <c r="AF47" s="62"/>
+      <c r="AG47" s="62"/>
+      <c r="AH47" s="62"/>
+      <c r="AI47" s="62"/>
+      <c r="AJ47" s="62"/>
+      <c r="AK47" s="62"/>
+      <c r="AL47" s="74"/>
     </row>
     <row r="48" spans="1:38" ht="15" customHeight="1">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="54"/>
+      <c r="B48" s="56"/>
       <c r="D48" s="22"/>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -4534,14 +4534,14 @@
       <c r="AB48" s="17"/>
       <c r="AC48" s="17"/>
       <c r="AD48" s="6"/>
-      <c r="AE48" s="76"/>
-      <c r="AF48" s="61"/>
-      <c r="AG48" s="61"/>
-      <c r="AH48" s="61"/>
-      <c r="AI48" s="61"/>
-      <c r="AJ48" s="61"/>
-      <c r="AK48" s="61"/>
-      <c r="AL48" s="77"/>
+      <c r="AE48" s="73"/>
+      <c r="AF48" s="62"/>
+      <c r="AG48" s="62"/>
+      <c r="AH48" s="62"/>
+      <c r="AI48" s="62"/>
+      <c r="AJ48" s="62"/>
+      <c r="AK48" s="62"/>
+      <c r="AL48" s="74"/>
     </row>
     <row r="49" spans="1:38" ht="15" customHeight="1">
       <c r="A49" s="55"/>
@@ -4573,20 +4573,20 @@
       <c r="AB49" s="17"/>
       <c r="AC49" s="17"/>
       <c r="AD49" s="6"/>
-      <c r="AE49" s="76"/>
-      <c r="AF49" s="61"/>
-      <c r="AG49" s="61"/>
-      <c r="AH49" s="61"/>
-      <c r="AI49" s="61"/>
-      <c r="AJ49" s="61"/>
-      <c r="AK49" s="61"/>
-      <c r="AL49" s="77"/>
+      <c r="AE49" s="73"/>
+      <c r="AF49" s="62"/>
+      <c r="AG49" s="62"/>
+      <c r="AH49" s="62"/>
+      <c r="AI49" s="62"/>
+      <c r="AJ49" s="62"/>
+      <c r="AK49" s="62"/>
+      <c r="AL49" s="74"/>
     </row>
     <row r="50" spans="1:38" ht="15" customHeight="1">
-      <c r="A50" s="56" t="s">
+      <c r="A50" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="54"/>
+      <c r="B50" s="56"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -4614,14 +4614,14 @@
       <c r="AB50" s="17"/>
       <c r="AC50" s="17"/>
       <c r="AD50" s="6"/>
-      <c r="AE50" s="76"/>
-      <c r="AF50" s="61"/>
-      <c r="AG50" s="61"/>
-      <c r="AH50" s="61"/>
-      <c r="AI50" s="61"/>
-      <c r="AJ50" s="61"/>
-      <c r="AK50" s="61"/>
-      <c r="AL50" s="77"/>
+      <c r="AE50" s="73"/>
+      <c r="AF50" s="62"/>
+      <c r="AG50" s="62"/>
+      <c r="AH50" s="62"/>
+      <c r="AI50" s="62"/>
+      <c r="AJ50" s="62"/>
+      <c r="AK50" s="62"/>
+      <c r="AL50" s="74"/>
     </row>
     <row r="51" spans="1:38" ht="15" customHeight="1">
       <c r="A51" s="55"/>
@@ -4653,20 +4653,20 @@
       <c r="AB51" s="17"/>
       <c r="AC51" s="17"/>
       <c r="AD51" s="6"/>
-      <c r="AE51" s="76"/>
-      <c r="AF51" s="61"/>
-      <c r="AG51" s="61"/>
-      <c r="AH51" s="61"/>
-      <c r="AI51" s="61"/>
-      <c r="AJ51" s="61"/>
-      <c r="AK51" s="61"/>
-      <c r="AL51" s="77"/>
+      <c r="AE51" s="73"/>
+      <c r="AF51" s="62"/>
+      <c r="AG51" s="62"/>
+      <c r="AH51" s="62"/>
+      <c r="AI51" s="62"/>
+      <c r="AJ51" s="62"/>
+      <c r="AK51" s="62"/>
+      <c r="AL51" s="74"/>
     </row>
     <row r="52" spans="1:38" ht="15" customHeight="1">
-      <c r="A52" s="56" t="s">
+      <c r="A52" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="54"/>
+      <c r="B52" s="56"/>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
@@ -4694,14 +4694,14 @@
       <c r="AB52" s="17"/>
       <c r="AC52" s="17"/>
       <c r="AD52" s="6"/>
-      <c r="AE52" s="76"/>
-      <c r="AF52" s="61"/>
-      <c r="AG52" s="61"/>
-      <c r="AH52" s="61"/>
-      <c r="AI52" s="61"/>
-      <c r="AJ52" s="61"/>
-      <c r="AK52" s="61"/>
-      <c r="AL52" s="77"/>
+      <c r="AE52" s="73"/>
+      <c r="AF52" s="62"/>
+      <c r="AG52" s="62"/>
+      <c r="AH52" s="62"/>
+      <c r="AI52" s="62"/>
+      <c r="AJ52" s="62"/>
+      <c r="AK52" s="62"/>
+      <c r="AL52" s="74"/>
     </row>
     <row r="53" spans="1:38" ht="15" customHeight="1">
       <c r="A53" s="55"/>
@@ -4733,20 +4733,20 @@
       <c r="AB53" s="17"/>
       <c r="AC53" s="17"/>
       <c r="AD53" s="6"/>
-      <c r="AE53" s="76"/>
-      <c r="AF53" s="61"/>
-      <c r="AG53" s="61"/>
-      <c r="AH53" s="61"/>
-      <c r="AI53" s="61"/>
-      <c r="AJ53" s="61"/>
-      <c r="AK53" s="61"/>
-      <c r="AL53" s="77"/>
+      <c r="AE53" s="73"/>
+      <c r="AF53" s="62"/>
+      <c r="AG53" s="62"/>
+      <c r="AH53" s="62"/>
+      <c r="AI53" s="62"/>
+      <c r="AJ53" s="62"/>
+      <c r="AK53" s="62"/>
+      <c r="AL53" s="74"/>
     </row>
     <row r="54" spans="1:38" ht="15" customHeight="1">
-      <c r="A54" s="56" t="s">
+      <c r="A54" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="54"/>
+      <c r="B54" s="56"/>
       <c r="D54" s="22"/>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -4774,14 +4774,14 @@
       <c r="AB54" s="17"/>
       <c r="AC54" s="17"/>
       <c r="AD54" s="6"/>
-      <c r="AE54" s="76"/>
-      <c r="AF54" s="61"/>
-      <c r="AG54" s="61"/>
-      <c r="AH54" s="61"/>
-      <c r="AI54" s="61"/>
-      <c r="AJ54" s="61"/>
-      <c r="AK54" s="61"/>
-      <c r="AL54" s="77"/>
+      <c r="AE54" s="73"/>
+      <c r="AF54" s="62"/>
+      <c r="AG54" s="62"/>
+      <c r="AH54" s="62"/>
+      <c r="AI54" s="62"/>
+      <c r="AJ54" s="62"/>
+      <c r="AK54" s="62"/>
+      <c r="AL54" s="74"/>
     </row>
     <row r="55" spans="1:38" ht="15" customHeight="1">
       <c r="A55" s="55"/>
@@ -4813,20 +4813,20 @@
       <c r="AB55" s="17"/>
       <c r="AC55" s="17"/>
       <c r="AD55" s="6"/>
-      <c r="AE55" s="76"/>
-      <c r="AF55" s="61"/>
-      <c r="AG55" s="61"/>
-      <c r="AH55" s="61"/>
-      <c r="AI55" s="61"/>
-      <c r="AJ55" s="61"/>
-      <c r="AK55" s="61"/>
-      <c r="AL55" s="77"/>
+      <c r="AE55" s="73"/>
+      <c r="AF55" s="62"/>
+      <c r="AG55" s="62"/>
+      <c r="AH55" s="62"/>
+      <c r="AI55" s="62"/>
+      <c r="AJ55" s="62"/>
+      <c r="AK55" s="62"/>
+      <c r="AL55" s="74"/>
     </row>
     <row r="56" spans="1:38" ht="15" customHeight="1">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="54"/>
+      <c r="B56" s="56"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -4854,14 +4854,14 @@
       <c r="AB56" s="17"/>
       <c r="AC56" s="17"/>
       <c r="AD56" s="6"/>
-      <c r="AE56" s="78"/>
-      <c r="AF56" s="79"/>
-      <c r="AG56" s="79"/>
-      <c r="AH56" s="79"/>
-      <c r="AI56" s="79"/>
-      <c r="AJ56" s="79"/>
-      <c r="AK56" s="79"/>
-      <c r="AL56" s="80"/>
+      <c r="AE56" s="75"/>
+      <c r="AF56" s="76"/>
+      <c r="AG56" s="76"/>
+      <c r="AH56" s="76"/>
+      <c r="AI56" s="76"/>
+      <c r="AJ56" s="76"/>
+      <c r="AK56" s="76"/>
+      <c r="AL56" s="77"/>
     </row>
     <row r="57" spans="1:38" ht="15" customHeight="1">
       <c r="A57" s="55"/>
@@ -4905,10 +4905,10 @@
       <c r="AL57" s="38"/>
     </row>
     <row r="58" spans="1:38" ht="15" customHeight="1">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="54"/>
+      <c r="B58" s="56"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -4989,8 +4989,8 @@
       <c r="AL59" s="38"/>
     </row>
     <row r="60" spans="1:38" ht="15" customHeight="1">
-      <c r="A60" s="83"/>
-      <c r="B60" s="83"/>
+      <c r="A60" s="57"/>
+      <c r="B60" s="57"/>
       <c r="D60" s="22"/>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -5071,8 +5071,8 @@
       <c r="AL61" s="38"/>
     </row>
     <row r="62" spans="1:38" ht="15" customHeight="1">
-      <c r="A62" s="83"/>
-      <c r="B62" s="83"/>
+      <c r="A62" s="57"/>
+      <c r="B62" s="57"/>
       <c r="D62" s="22"/>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -5151,8 +5151,8 @@
       <c r="AL63" s="38"/>
     </row>
     <row r="64" spans="1:38" ht="15" customHeight="1">
-      <c r="A64" s="83"/>
-      <c r="B64" s="83"/>
+      <c r="A64" s="57"/>
+      <c r="B64" s="57"/>
       <c r="D64" s="22"/>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
@@ -8071,32 +8071,29 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="AE3:AL35"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="B6:B7"/>
@@ -8113,29 +8110,32 @@
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="B46:B47"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="86" orientation="portrait"/>
@@ -8192,12 +8192,12 @@
       <c r="X1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="57">
+      <c r="Y1" s="80">
         <v>2026</v>
       </c>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="59"/>
+      <c r="Z1" s="81"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="82"/>
       <c r="AC1" s="6"/>
       <c r="AD1" s="4" t="s">
         <v>2</v>
@@ -8316,16 +8316,16 @@
         <v>25</v>
       </c>
       <c r="AC3" s="6"/>
-      <c r="AD3" s="64" t="s">
+      <c r="AD3" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="65"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="66"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="60"/>
     </row>
     <row r="4" spans="1:37" ht="14.25" customHeight="1">
       <c r="F4" s="12"/>
@@ -8351,14 +8351,14 @@
       <c r="AA4" s="12"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="6"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="61"/>
-      <c r="AF4" s="61"/>
-      <c r="AG4" s="61"/>
-      <c r="AH4" s="61"/>
-      <c r="AI4" s="61"/>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="68"/>
+      <c r="AD4" s="61"/>
+      <c r="AE4" s="62"/>
+      <c r="AF4" s="62"/>
+      <c r="AG4" s="62"/>
+      <c r="AH4" s="62"/>
+      <c r="AI4" s="62"/>
+      <c r="AJ4" s="62"/>
+      <c r="AK4" s="63"/>
     </row>
     <row r="5" spans="1:37" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
@@ -8404,17 +8404,17 @@
       <c r="AA5" s="12"/>
       <c r="AB5" s="16"/>
       <c r="AC5" s="6"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="61"/>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="68"/>
+      <c r="AD5" s="61"/>
+      <c r="AE5" s="62"/>
+      <c r="AF5" s="62"/>
+      <c r="AG5" s="62"/>
+      <c r="AH5" s="62"/>
+      <c r="AI5" s="62"/>
+      <c r="AJ5" s="62"/>
+      <c r="AK5" s="63"/>
     </row>
     <row r="6" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="54" t="s">
         <v>63</v>
       </c>
       <c r="B6" s="86" t="s">
@@ -8449,14 +8449,14 @@
       <c r="AA6" s="17"/>
       <c r="AB6" s="17"/>
       <c r="AC6" s="6"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="61"/>
-      <c r="AF6" s="61"/>
-      <c r="AG6" s="61"/>
-      <c r="AH6" s="61"/>
-      <c r="AI6" s="61"/>
-      <c r="AJ6" s="61"/>
-      <c r="AK6" s="68"/>
+      <c r="AD6" s="61"/>
+      <c r="AE6" s="62"/>
+      <c r="AF6" s="62"/>
+      <c r="AG6" s="62"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="62"/>
+      <c r="AK6" s="63"/>
     </row>
     <row r="7" spans="1:37" ht="14.25" customHeight="1">
       <c r="A7" s="55"/>
@@ -8496,20 +8496,20 @@
       <c r="AA7" s="17"/>
       <c r="AB7" s="17"/>
       <c r="AC7" s="6"/>
-      <c r="AD7" s="67"/>
-      <c r="AE7" s="61"/>
-      <c r="AF7" s="61"/>
-      <c r="AG7" s="61"/>
-      <c r="AH7" s="61"/>
-      <c r="AI7" s="61"/>
-      <c r="AJ7" s="61"/>
-      <c r="AK7" s="68"/>
+      <c r="AD7" s="61"/>
+      <c r="AE7" s="62"/>
+      <c r="AF7" s="62"/>
+      <c r="AG7" s="62"/>
+      <c r="AH7" s="62"/>
+      <c r="AI7" s="62"/>
+      <c r="AJ7" s="62"/>
+      <c r="AK7" s="63"/>
     </row>
     <row r="8" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="85" t="s">
         <v>66</v>
       </c>
       <c r="D8" s="22"/>
@@ -8541,14 +8541,14 @@
       <c r="AA8" s="17"/>
       <c r="AB8" s="17"/>
       <c r="AC8" s="6"/>
-      <c r="AD8" s="67"/>
-      <c r="AE8" s="61"/>
-      <c r="AF8" s="61"/>
-      <c r="AG8" s="61"/>
-      <c r="AH8" s="61"/>
-      <c r="AI8" s="61"/>
-      <c r="AJ8" s="61"/>
-      <c r="AK8" s="68"/>
+      <c r="AD8" s="61"/>
+      <c r="AE8" s="62"/>
+      <c r="AF8" s="62"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="63"/>
     </row>
     <row r="9" spans="1:37" ht="14.25" customHeight="1">
       <c r="A9" s="55"/>
@@ -8584,20 +8584,20 @@
       <c r="AA9" s="17"/>
       <c r="AB9" s="17"/>
       <c r="AC9" s="6"/>
-      <c r="AD9" s="67"/>
-      <c r="AE9" s="61"/>
-      <c r="AF9" s="61"/>
-      <c r="AG9" s="61"/>
-      <c r="AH9" s="61"/>
-      <c r="AI9" s="61"/>
-      <c r="AJ9" s="61"/>
-      <c r="AK9" s="68"/>
+      <c r="AD9" s="61"/>
+      <c r="AE9" s="62"/>
+      <c r="AF9" s="62"/>
+      <c r="AG9" s="62"/>
+      <c r="AH9" s="62"/>
+      <c r="AI9" s="62"/>
+      <c r="AJ9" s="62"/>
+      <c r="AK9" s="63"/>
     </row>
     <row r="10" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="85" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="22"/>
@@ -8629,14 +8629,14 @@
       <c r="AA10" s="17"/>
       <c r="AB10" s="17"/>
       <c r="AC10" s="6"/>
-      <c r="AD10" s="67"/>
-      <c r="AE10" s="61"/>
-      <c r="AF10" s="61"/>
-      <c r="AG10" s="61"/>
-      <c r="AH10" s="61"/>
-      <c r="AI10" s="61"/>
-      <c r="AJ10" s="61"/>
-      <c r="AK10" s="68"/>
+      <c r="AD10" s="61"/>
+      <c r="AE10" s="62"/>
+      <c r="AF10" s="62"/>
+      <c r="AG10" s="62"/>
+      <c r="AH10" s="62"/>
+      <c r="AI10" s="62"/>
+      <c r="AJ10" s="62"/>
+      <c r="AK10" s="63"/>
     </row>
     <row r="11" spans="1:37" ht="14.25" customHeight="1">
       <c r="A11" s="55"/>
@@ -8653,7 +8653,7 @@
       <c r="H11" s="17"/>
       <c r="I11" s="40"/>
       <c r="J11" s="40"/>
-      <c r="K11" s="17"/>
+      <c r="K11" s="40"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="17"/>
@@ -8672,20 +8672,20 @@
       <c r="AA11" s="17"/>
       <c r="AB11" s="17"/>
       <c r="AC11" s="6"/>
-      <c r="AD11" s="67"/>
-      <c r="AE11" s="61"/>
-      <c r="AF11" s="61"/>
-      <c r="AG11" s="61"/>
-      <c r="AH11" s="61"/>
-      <c r="AI11" s="61"/>
-      <c r="AJ11" s="61"/>
-      <c r="AK11" s="68"/>
+      <c r="AD11" s="61"/>
+      <c r="AE11" s="62"/>
+      <c r="AF11" s="62"/>
+      <c r="AG11" s="62"/>
+      <c r="AH11" s="62"/>
+      <c r="AI11" s="62"/>
+      <c r="AJ11" s="62"/>
+      <c r="AK11" s="63"/>
     </row>
     <row r="12" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="85" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="22"/>
@@ -8717,14 +8717,14 @@
       <c r="AA12" s="17"/>
       <c r="AB12" s="17"/>
       <c r="AC12" s="6"/>
-      <c r="AD12" s="67"/>
-      <c r="AE12" s="61"/>
-      <c r="AF12" s="61"/>
-      <c r="AG12" s="61"/>
-      <c r="AH12" s="61"/>
-      <c r="AI12" s="61"/>
-      <c r="AJ12" s="61"/>
-      <c r="AK12" s="68"/>
+      <c r="AD12" s="61"/>
+      <c r="AE12" s="62"/>
+      <c r="AF12" s="62"/>
+      <c r="AG12" s="62"/>
+      <c r="AH12" s="62"/>
+      <c r="AI12" s="62"/>
+      <c r="AJ12" s="62"/>
+      <c r="AK12" s="63"/>
     </row>
     <row r="13" spans="1:37" ht="17.25" customHeight="1">
       <c r="A13" s="55"/>
@@ -8760,20 +8760,20 @@
       <c r="AA13" s="17"/>
       <c r="AB13" s="17"/>
       <c r="AC13" s="6"/>
-      <c r="AD13" s="67"/>
-      <c r="AE13" s="61"/>
-      <c r="AF13" s="61"/>
-      <c r="AG13" s="61"/>
-      <c r="AH13" s="61"/>
-      <c r="AI13" s="61"/>
-      <c r="AJ13" s="61"/>
-      <c r="AK13" s="68"/>
+      <c r="AD13" s="61"/>
+      <c r="AE13" s="62"/>
+      <c r="AF13" s="62"/>
+      <c r="AG13" s="62"/>
+      <c r="AH13" s="62"/>
+      <c r="AI13" s="62"/>
+      <c r="AJ13" s="62"/>
+      <c r="AK13" s="63"/>
     </row>
     <row r="14" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="85" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="22"/>
@@ -8805,14 +8805,14 @@
       <c r="AA14" s="17"/>
       <c r="AB14" s="17"/>
       <c r="AC14" s="6"/>
-      <c r="AD14" s="67"/>
-      <c r="AE14" s="61"/>
-      <c r="AF14" s="61"/>
-      <c r="AG14" s="61"/>
-      <c r="AH14" s="61"/>
-      <c r="AI14" s="61"/>
-      <c r="AJ14" s="61"/>
-      <c r="AK14" s="68"/>
+      <c r="AD14" s="61"/>
+      <c r="AE14" s="62"/>
+      <c r="AF14" s="62"/>
+      <c r="AG14" s="62"/>
+      <c r="AH14" s="62"/>
+      <c r="AI14" s="62"/>
+      <c r="AJ14" s="62"/>
+      <c r="AK14" s="63"/>
     </row>
     <row r="15" spans="1:37" ht="17.25" customHeight="1">
       <c r="A15" s="55"/>
@@ -8829,7 +8829,7 @@
       <c r="H15" s="17"/>
       <c r="I15" s="40"/>
       <c r="J15" s="40"/>
-      <c r="K15" s="17"/>
+      <c r="K15" s="40"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
       <c r="N15" s="17"/>
@@ -8848,20 +8848,20 @@
       <c r="AA15" s="17"/>
       <c r="AB15" s="17"/>
       <c r="AC15" s="6"/>
-      <c r="AD15" s="67"/>
-      <c r="AE15" s="61"/>
-      <c r="AF15" s="61"/>
-      <c r="AG15" s="61"/>
-      <c r="AH15" s="61"/>
-      <c r="AI15" s="61"/>
-      <c r="AJ15" s="61"/>
-      <c r="AK15" s="68"/>
+      <c r="AD15" s="61"/>
+      <c r="AE15" s="62"/>
+      <c r="AF15" s="62"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="63"/>
     </row>
     <row r="16" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="85" t="s">
         <v>70</v>
       </c>
       <c r="D16" s="22"/>
@@ -8893,14 +8893,14 @@
       <c r="AA16" s="17"/>
       <c r="AB16" s="17"/>
       <c r="AC16" s="6"/>
-      <c r="AD16" s="67"/>
-      <c r="AE16" s="61"/>
-      <c r="AF16" s="61"/>
-      <c r="AG16" s="61"/>
-      <c r="AH16" s="61"/>
-      <c r="AI16" s="61"/>
-      <c r="AJ16" s="61"/>
-      <c r="AK16" s="68"/>
+      <c r="AD16" s="61"/>
+      <c r="AE16" s="62"/>
+      <c r="AF16" s="62"/>
+      <c r="AG16" s="62"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="62"/>
+      <c r="AJ16" s="62"/>
+      <c r="AK16" s="63"/>
     </row>
     <row r="17" spans="1:37" ht="17.25" customHeight="1">
       <c r="A17" s="55"/>
@@ -8936,20 +8936,20 @@
       <c r="AA17" s="17"/>
       <c r="AB17" s="17"/>
       <c r="AC17" s="6"/>
-      <c r="AD17" s="67"/>
-      <c r="AE17" s="61"/>
-      <c r="AF17" s="61"/>
-      <c r="AG17" s="61"/>
-      <c r="AH17" s="61"/>
-      <c r="AI17" s="61"/>
-      <c r="AJ17" s="61"/>
-      <c r="AK17" s="68"/>
+      <c r="AD17" s="61"/>
+      <c r="AE17" s="62"/>
+      <c r="AF17" s="62"/>
+      <c r="AG17" s="62"/>
+      <c r="AH17" s="62"/>
+      <c r="AI17" s="62"/>
+      <c r="AJ17" s="62"/>
+      <c r="AK17" s="63"/>
     </row>
     <row r="18" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="84" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="22"/>
@@ -8981,14 +8981,14 @@
       <c r="AA18" s="17"/>
       <c r="AB18" s="17"/>
       <c r="AC18" s="6"/>
-      <c r="AD18" s="67"/>
-      <c r="AE18" s="61"/>
-      <c r="AF18" s="61"/>
-      <c r="AG18" s="61"/>
-      <c r="AH18" s="61"/>
-      <c r="AI18" s="61"/>
-      <c r="AJ18" s="61"/>
-      <c r="AK18" s="68"/>
+      <c r="AD18" s="61"/>
+      <c r="AE18" s="62"/>
+      <c r="AF18" s="62"/>
+      <c r="AG18" s="62"/>
+      <c r="AH18" s="62"/>
+      <c r="AI18" s="62"/>
+      <c r="AJ18" s="62"/>
+      <c r="AK18" s="63"/>
     </row>
     <row r="19" spans="1:37" ht="14.25" customHeight="1">
       <c r="A19" s="55"/>
@@ -9024,20 +9024,20 @@
       <c r="AA19" s="17"/>
       <c r="AB19" s="17"/>
       <c r="AC19" s="6"/>
-      <c r="AD19" s="67"/>
-      <c r="AE19" s="61"/>
-      <c r="AF19" s="61"/>
-      <c r="AG19" s="61"/>
-      <c r="AH19" s="61"/>
-      <c r="AI19" s="61"/>
-      <c r="AJ19" s="61"/>
-      <c r="AK19" s="68"/>
+      <c r="AD19" s="61"/>
+      <c r="AE19" s="62"/>
+      <c r="AF19" s="62"/>
+      <c r="AG19" s="62"/>
+      <c r="AH19" s="62"/>
+      <c r="AI19" s="62"/>
+      <c r="AJ19" s="62"/>
+      <c r="AK19" s="63"/>
     </row>
     <row r="20" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="84" t="s">
         <v>73</v>
       </c>
       <c r="D20" s="22"/>
@@ -9069,14 +9069,14 @@
       <c r="AA20" s="17"/>
       <c r="AB20" s="17"/>
       <c r="AC20" s="6"/>
-      <c r="AD20" s="67"/>
-      <c r="AE20" s="61"/>
-      <c r="AF20" s="61"/>
-      <c r="AG20" s="61"/>
-      <c r="AH20" s="61"/>
-      <c r="AI20" s="61"/>
-      <c r="AJ20" s="61"/>
-      <c r="AK20" s="68"/>
+      <c r="AD20" s="61"/>
+      <c r="AE20" s="62"/>
+      <c r="AF20" s="62"/>
+      <c r="AG20" s="62"/>
+      <c r="AH20" s="62"/>
+      <c r="AI20" s="62"/>
+      <c r="AJ20" s="62"/>
+      <c r="AK20" s="63"/>
     </row>
     <row r="21" spans="1:37" ht="14.25" customHeight="1">
       <c r="A21" s="55"/>
@@ -9093,7 +9093,7 @@
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
       <c r="J21" s="40"/>
-      <c r="K21" s="17"/>
+      <c r="K21" s="40"/>
       <c r="L21" s="28"/>
       <c r="M21" s="28"/>
       <c r="N21" s="17"/>
@@ -9112,20 +9112,20 @@
       <c r="AA21" s="17"/>
       <c r="AB21" s="17"/>
       <c r="AC21" s="6"/>
-      <c r="AD21" s="67"/>
-      <c r="AE21" s="61"/>
-      <c r="AF21" s="61"/>
-      <c r="AG21" s="61"/>
-      <c r="AH21" s="61"/>
-      <c r="AI21" s="61"/>
-      <c r="AJ21" s="61"/>
-      <c r="AK21" s="68"/>
+      <c r="AD21" s="61"/>
+      <c r="AE21" s="62"/>
+      <c r="AF21" s="62"/>
+      <c r="AG21" s="62"/>
+      <c r="AH21" s="62"/>
+      <c r="AI21" s="62"/>
+      <c r="AJ21" s="62"/>
+      <c r="AK21" s="63"/>
     </row>
     <row r="22" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="85" t="s">
         <v>75</v>
       </c>
       <c r="D22" s="22"/>
@@ -9157,14 +9157,14 @@
       <c r="AA22" s="17"/>
       <c r="AB22" s="17"/>
       <c r="AC22" s="6"/>
-      <c r="AD22" s="67"/>
-      <c r="AE22" s="61"/>
-      <c r="AF22" s="61"/>
-      <c r="AG22" s="61"/>
-      <c r="AH22" s="61"/>
-      <c r="AI22" s="61"/>
-      <c r="AJ22" s="61"/>
-      <c r="AK22" s="68"/>
+      <c r="AD22" s="61"/>
+      <c r="AE22" s="62"/>
+      <c r="AF22" s="62"/>
+      <c r="AG22" s="62"/>
+      <c r="AH22" s="62"/>
+      <c r="AI22" s="62"/>
+      <c r="AJ22" s="62"/>
+      <c r="AK22" s="63"/>
     </row>
     <row r="23" spans="1:37" ht="14.25" customHeight="1">
       <c r="A23" s="55"/>
@@ -9181,7 +9181,7 @@
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
       <c r="J23" s="40"/>
-      <c r="K23" s="17"/>
+      <c r="K23" s="40"/>
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
       <c r="N23" s="17"/>
@@ -9200,20 +9200,20 @@
       <c r="AA23" s="17"/>
       <c r="AB23" s="17"/>
       <c r="AC23" s="6"/>
-      <c r="AD23" s="67"/>
-      <c r="AE23" s="61"/>
-      <c r="AF23" s="61"/>
-      <c r="AG23" s="61"/>
-      <c r="AH23" s="61"/>
-      <c r="AI23" s="61"/>
-      <c r="AJ23" s="61"/>
-      <c r="AK23" s="68"/>
+      <c r="AD23" s="61"/>
+      <c r="AE23" s="62"/>
+      <c r="AF23" s="62"/>
+      <c r="AG23" s="62"/>
+      <c r="AH23" s="62"/>
+      <c r="AI23" s="62"/>
+      <c r="AJ23" s="62"/>
+      <c r="AK23" s="63"/>
     </row>
     <row r="24" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="84" t="s">
         <v>77</v>
       </c>
       <c r="D24" s="22"/>
@@ -9245,14 +9245,14 @@
       <c r="AA24" s="17"/>
       <c r="AB24" s="17"/>
       <c r="AC24" s="6"/>
-      <c r="AD24" s="67"/>
-      <c r="AE24" s="61"/>
-      <c r="AF24" s="61"/>
-      <c r="AG24" s="61"/>
-      <c r="AH24" s="61"/>
-      <c r="AI24" s="61"/>
-      <c r="AJ24" s="61"/>
-      <c r="AK24" s="68"/>
+      <c r="AD24" s="61"/>
+      <c r="AE24" s="62"/>
+      <c r="AF24" s="62"/>
+      <c r="AG24" s="62"/>
+      <c r="AH24" s="62"/>
+      <c r="AI24" s="62"/>
+      <c r="AJ24" s="62"/>
+      <c r="AK24" s="63"/>
     </row>
     <row r="25" spans="1:37" ht="14.25" customHeight="1">
       <c r="A25" s="55"/>
@@ -9268,8 +9268,8 @@
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
       <c r="N25" s="17"/>
@@ -9288,20 +9288,20 @@
       <c r="AA25" s="17"/>
       <c r="AB25" s="17"/>
       <c r="AC25" s="6"/>
-      <c r="AD25" s="67"/>
-      <c r="AE25" s="61"/>
-      <c r="AF25" s="61"/>
-      <c r="AG25" s="61"/>
-      <c r="AH25" s="61"/>
-      <c r="AI25" s="61"/>
-      <c r="AJ25" s="61"/>
-      <c r="AK25" s="68"/>
+      <c r="AD25" s="61"/>
+      <c r="AE25" s="62"/>
+      <c r="AF25" s="62"/>
+      <c r="AG25" s="62"/>
+      <c r="AH25" s="62"/>
+      <c r="AI25" s="62"/>
+      <c r="AJ25" s="62"/>
+      <c r="AK25" s="63"/>
     </row>
     <row r="26" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="85" t="s">
         <v>66</v>
       </c>
       <c r="D26" s="22"/>
@@ -9313,8 +9313,8 @@
       </c>
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
       <c r="N26" s="17"/>
@@ -9333,14 +9333,14 @@
       <c r="AA26" s="17"/>
       <c r="AB26" s="17"/>
       <c r="AC26" s="6"/>
-      <c r="AD26" s="67"/>
-      <c r="AE26" s="61"/>
-      <c r="AF26" s="61"/>
-      <c r="AG26" s="61"/>
-      <c r="AH26" s="61"/>
-      <c r="AI26" s="61"/>
-      <c r="AJ26" s="61"/>
-      <c r="AK26" s="68"/>
+      <c r="AD26" s="61"/>
+      <c r="AE26" s="62"/>
+      <c r="AF26" s="62"/>
+      <c r="AG26" s="62"/>
+      <c r="AH26" s="62"/>
+      <c r="AI26" s="62"/>
+      <c r="AJ26" s="62"/>
+      <c r="AK26" s="63"/>
     </row>
     <row r="27" spans="1:37" ht="17.25" customHeight="1">
       <c r="A27" s="55"/>
@@ -9356,8 +9356,8 @@
       </c>
       <c r="H27" s="40"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
       <c r="L27" s="31"/>
       <c r="M27" s="31"/>
       <c r="N27" s="17"/>
@@ -9376,20 +9376,20 @@
       <c r="AA27" s="17"/>
       <c r="AB27" s="17"/>
       <c r="AC27" s="6"/>
-      <c r="AD27" s="67"/>
-      <c r="AE27" s="61"/>
-      <c r="AF27" s="61"/>
-      <c r="AG27" s="61"/>
-      <c r="AH27" s="61"/>
-      <c r="AI27" s="61"/>
-      <c r="AJ27" s="61"/>
-      <c r="AK27" s="68"/>
+      <c r="AD27" s="61"/>
+      <c r="AE27" s="62"/>
+      <c r="AF27" s="62"/>
+      <c r="AG27" s="62"/>
+      <c r="AH27" s="62"/>
+      <c r="AI27" s="62"/>
+      <c r="AJ27" s="62"/>
+      <c r="AK27" s="63"/>
     </row>
     <row r="28" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="85" t="s">
+      <c r="B28" s="84" t="s">
         <v>80</v>
       </c>
       <c r="D28" s="22"/>
@@ -9421,14 +9421,14 @@
       <c r="AA28" s="17"/>
       <c r="AB28" s="17"/>
       <c r="AC28" s="6"/>
-      <c r="AD28" s="67"/>
-      <c r="AE28" s="61"/>
-      <c r="AF28" s="61"/>
-      <c r="AG28" s="61"/>
-      <c r="AH28" s="61"/>
-      <c r="AI28" s="61"/>
-      <c r="AJ28" s="61"/>
-      <c r="AK28" s="68"/>
+      <c r="AD28" s="61"/>
+      <c r="AE28" s="62"/>
+      <c r="AF28" s="62"/>
+      <c r="AG28" s="62"/>
+      <c r="AH28" s="62"/>
+      <c r="AI28" s="62"/>
+      <c r="AJ28" s="62"/>
+      <c r="AK28" s="63"/>
     </row>
     <row r="29" spans="1:37" ht="14.25" customHeight="1">
       <c r="A29" s="55"/>
@@ -9464,20 +9464,20 @@
       <c r="AA29" s="17"/>
       <c r="AB29" s="17"/>
       <c r="AC29" s="6"/>
-      <c r="AD29" s="67"/>
-      <c r="AE29" s="61"/>
-      <c r="AF29" s="61"/>
-      <c r="AG29" s="61"/>
-      <c r="AH29" s="61"/>
-      <c r="AI29" s="61"/>
-      <c r="AJ29" s="61"/>
-      <c r="AK29" s="68"/>
+      <c r="AD29" s="61"/>
+      <c r="AE29" s="62"/>
+      <c r="AF29" s="62"/>
+      <c r="AG29" s="62"/>
+      <c r="AH29" s="62"/>
+      <c r="AI29" s="62"/>
+      <c r="AJ29" s="62"/>
+      <c r="AK29" s="63"/>
     </row>
     <row r="30" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="84" t="s">
+      <c r="B30" s="85" t="s">
         <v>69</v>
       </c>
       <c r="D30" s="22"/>
@@ -9509,14 +9509,14 @@
       <c r="AA30" s="17"/>
       <c r="AB30" s="17"/>
       <c r="AC30" s="6"/>
-      <c r="AD30" s="67"/>
-      <c r="AE30" s="61"/>
-      <c r="AF30" s="61"/>
-      <c r="AG30" s="61"/>
-      <c r="AH30" s="61"/>
-      <c r="AI30" s="61"/>
-      <c r="AJ30" s="61"/>
-      <c r="AK30" s="68"/>
+      <c r="AD30" s="61"/>
+      <c r="AE30" s="62"/>
+      <c r="AF30" s="62"/>
+      <c r="AG30" s="62"/>
+      <c r="AH30" s="62"/>
+      <c r="AI30" s="62"/>
+      <c r="AJ30" s="62"/>
+      <c r="AK30" s="63"/>
     </row>
     <row r="31" spans="1:37" ht="14.25" customHeight="1">
       <c r="A31" s="55"/>
@@ -9532,8 +9532,8 @@
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="40"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
       <c r="L31" s="18"/>
       <c r="M31" s="18"/>
       <c r="N31" s="17"/>
@@ -9552,20 +9552,20 @@
       <c r="AA31" s="17"/>
       <c r="AB31" s="17"/>
       <c r="AC31" s="6"/>
-      <c r="AD31" s="69"/>
-      <c r="AE31" s="70"/>
-      <c r="AF31" s="70"/>
-      <c r="AG31" s="70"/>
-      <c r="AH31" s="70"/>
-      <c r="AI31" s="70"/>
-      <c r="AJ31" s="70"/>
-      <c r="AK31" s="71"/>
+      <c r="AD31" s="64"/>
+      <c r="AE31" s="65"/>
+      <c r="AF31" s="65"/>
+      <c r="AG31" s="65"/>
+      <c r="AH31" s="65"/>
+      <c r="AI31" s="65"/>
+      <c r="AJ31" s="65"/>
+      <c r="AK31" s="66"/>
     </row>
     <row r="32" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="85" t="s">
+      <c r="B32" s="84" t="s">
         <v>83</v>
       </c>
       <c r="D32" s="22"/>
@@ -9582,8 +9582,8 @@
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
       <c r="N32" s="35"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
       <c r="Q32" s="17"/>
       <c r="R32" s="17"/>
       <c r="S32" s="18"/>
@@ -9650,10 +9650,10 @@
       <c r="AK33" s="52"/>
     </row>
     <row r="34" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="84" t="s">
+      <c r="B34" s="85" t="s">
         <v>71</v>
       </c>
       <c r="D34" s="22"/>
@@ -9670,7 +9670,7 @@
       <c r="L34" s="30"/>
       <c r="M34" s="23"/>
       <c r="N34" s="17"/>
-      <c r="O34" s="35"/>
+      <c r="O34" s="17"/>
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="17"/>
@@ -9685,14 +9685,14 @@
       <c r="AA34" s="17"/>
       <c r="AB34" s="17"/>
       <c r="AC34" s="6"/>
-      <c r="AD34" s="73"/>
-      <c r="AE34" s="74"/>
-      <c r="AF34" s="74"/>
-      <c r="AG34" s="74"/>
-      <c r="AH34" s="74"/>
-      <c r="AI34" s="74"/>
-      <c r="AJ34" s="74"/>
-      <c r="AK34" s="75"/>
+      <c r="AD34" s="70"/>
+      <c r="AE34" s="71"/>
+      <c r="AF34" s="71"/>
+      <c r="AG34" s="71"/>
+      <c r="AH34" s="71"/>
+      <c r="AI34" s="71"/>
+      <c r="AJ34" s="71"/>
+      <c r="AK34" s="72"/>
     </row>
     <row r="35" spans="1:37" ht="14.25" customHeight="1">
       <c r="A35" s="55"/>
@@ -9728,20 +9728,20 @@
       <c r="AA35" s="17"/>
       <c r="AB35" s="17"/>
       <c r="AC35" s="6"/>
-      <c r="AD35" s="76"/>
-      <c r="AE35" s="61"/>
-      <c r="AF35" s="61"/>
-      <c r="AG35" s="61"/>
-      <c r="AH35" s="61"/>
-      <c r="AI35" s="61"/>
-      <c r="AJ35" s="61"/>
-      <c r="AK35" s="77"/>
+      <c r="AD35" s="73"/>
+      <c r="AE35" s="62"/>
+      <c r="AF35" s="62"/>
+      <c r="AG35" s="62"/>
+      <c r="AH35" s="62"/>
+      <c r="AI35" s="62"/>
+      <c r="AJ35" s="62"/>
+      <c r="AK35" s="74"/>
     </row>
     <row r="36" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="85" t="s">
+      <c r="B36" s="84" t="s">
         <v>73</v>
       </c>
       <c r="D36" s="22"/>
@@ -9773,14 +9773,14 @@
       <c r="AA36" s="17"/>
       <c r="AB36" s="17"/>
       <c r="AC36" s="6"/>
-      <c r="AD36" s="76"/>
-      <c r="AE36" s="61"/>
-      <c r="AF36" s="61"/>
-      <c r="AG36" s="61"/>
-      <c r="AH36" s="61"/>
-      <c r="AI36" s="61"/>
-      <c r="AJ36" s="61"/>
-      <c r="AK36" s="77"/>
+      <c r="AD36" s="73"/>
+      <c r="AE36" s="62"/>
+      <c r="AF36" s="62"/>
+      <c r="AG36" s="62"/>
+      <c r="AH36" s="62"/>
+      <c r="AI36" s="62"/>
+      <c r="AJ36" s="62"/>
+      <c r="AK36" s="74"/>
     </row>
     <row r="37" spans="1:37" ht="14.25" customHeight="1">
       <c r="A37" s="55"/>
@@ -9797,7 +9797,7 @@
       <c r="H37" s="32"/>
       <c r="I37" s="17"/>
       <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
+      <c r="K37" s="40"/>
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
       <c r="N37" s="17"/>
@@ -9816,20 +9816,20 @@
       <c r="AA37" s="17"/>
       <c r="AB37" s="17"/>
       <c r="AC37" s="6"/>
-      <c r="AD37" s="76"/>
-      <c r="AE37" s="61"/>
-      <c r="AF37" s="61"/>
-      <c r="AG37" s="61"/>
-      <c r="AH37" s="61"/>
-      <c r="AI37" s="61"/>
-      <c r="AJ37" s="61"/>
-      <c r="AK37" s="77"/>
+      <c r="AD37" s="73"/>
+      <c r="AE37" s="62"/>
+      <c r="AF37" s="62"/>
+      <c r="AG37" s="62"/>
+      <c r="AH37" s="62"/>
+      <c r="AI37" s="62"/>
+      <c r="AJ37" s="62"/>
+      <c r="AK37" s="74"/>
     </row>
     <row r="38" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A38" s="56" t="s">
+      <c r="A38" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="84" t="s">
+      <c r="B38" s="85" t="s">
         <v>75</v>
       </c>
       <c r="D38" s="22"/>
@@ -9861,14 +9861,14 @@
       <c r="AA38" s="17"/>
       <c r="AB38" s="17"/>
       <c r="AC38" s="6"/>
-      <c r="AD38" s="76"/>
-      <c r="AE38" s="61"/>
-      <c r="AF38" s="61"/>
-      <c r="AG38" s="61"/>
-      <c r="AH38" s="61"/>
-      <c r="AI38" s="61"/>
-      <c r="AJ38" s="61"/>
-      <c r="AK38" s="77"/>
+      <c r="AD38" s="73"/>
+      <c r="AE38" s="62"/>
+      <c r="AF38" s="62"/>
+      <c r="AG38" s="62"/>
+      <c r="AH38" s="62"/>
+      <c r="AI38" s="62"/>
+      <c r="AJ38" s="62"/>
+      <c r="AK38" s="74"/>
     </row>
     <row r="39" spans="1:37" ht="14.25" customHeight="1">
       <c r="A39" s="55"/>
@@ -9904,20 +9904,20 @@
       <c r="AA39" s="17"/>
       <c r="AB39" s="17"/>
       <c r="AC39" s="6"/>
-      <c r="AD39" s="76"/>
-      <c r="AE39" s="61"/>
-      <c r="AF39" s="61"/>
-      <c r="AG39" s="61"/>
-      <c r="AH39" s="61"/>
-      <c r="AI39" s="61"/>
-      <c r="AJ39" s="61"/>
-      <c r="AK39" s="77"/>
+      <c r="AD39" s="73"/>
+      <c r="AE39" s="62"/>
+      <c r="AF39" s="62"/>
+      <c r="AG39" s="62"/>
+      <c r="AH39" s="62"/>
+      <c r="AI39" s="62"/>
+      <c r="AJ39" s="62"/>
+      <c r="AK39" s="74"/>
     </row>
     <row r="40" spans="1:37" ht="15" customHeight="1">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="85" t="s">
+      <c r="B40" s="84" t="s">
         <v>77</v>
       </c>
       <c r="D40" s="22"/>
@@ -9949,14 +9949,14 @@
       <c r="AA40" s="17"/>
       <c r="AB40" s="17"/>
       <c r="AC40" s="6"/>
-      <c r="AD40" s="76"/>
-      <c r="AE40" s="61"/>
-      <c r="AF40" s="61"/>
-      <c r="AG40" s="61"/>
-      <c r="AH40" s="61"/>
-      <c r="AI40" s="61"/>
-      <c r="AJ40" s="61"/>
-      <c r="AK40" s="77"/>
+      <c r="AD40" s="73"/>
+      <c r="AE40" s="62"/>
+      <c r="AF40" s="62"/>
+      <c r="AG40" s="62"/>
+      <c r="AH40" s="62"/>
+      <c r="AI40" s="62"/>
+      <c r="AJ40" s="62"/>
+      <c r="AK40" s="74"/>
     </row>
     <row r="41" spans="1:37" ht="15" customHeight="1">
       <c r="A41" s="55"/>
@@ -9973,7 +9973,7 @@
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
+      <c r="K41" s="40"/>
       <c r="L41" s="18"/>
       <c r="M41" s="18"/>
       <c r="N41" s="17"/>
@@ -9992,20 +9992,20 @@
       <c r="AA41" s="17"/>
       <c r="AB41" s="17"/>
       <c r="AC41" s="6"/>
-      <c r="AD41" s="76"/>
-      <c r="AE41" s="61"/>
-      <c r="AF41" s="61"/>
-      <c r="AG41" s="61"/>
-      <c r="AH41" s="61"/>
-      <c r="AI41" s="61"/>
-      <c r="AJ41" s="61"/>
-      <c r="AK41" s="77"/>
+      <c r="AD41" s="73"/>
+      <c r="AE41" s="62"/>
+      <c r="AF41" s="62"/>
+      <c r="AG41" s="62"/>
+      <c r="AH41" s="62"/>
+      <c r="AI41" s="62"/>
+      <c r="AJ41" s="62"/>
+      <c r="AK41" s="74"/>
     </row>
     <row r="42" spans="1:37" ht="15" customHeight="1">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="84" t="s">
+      <c r="B42" s="85" t="s">
         <v>66</v>
       </c>
       <c r="D42" s="22"/>
@@ -10037,14 +10037,14 @@
       <c r="AA42" s="17"/>
       <c r="AB42" s="17"/>
       <c r="AC42" s="6"/>
-      <c r="AD42" s="76"/>
-      <c r="AE42" s="61"/>
-      <c r="AF42" s="61"/>
-      <c r="AG42" s="61"/>
-      <c r="AH42" s="61"/>
-      <c r="AI42" s="61"/>
-      <c r="AJ42" s="61"/>
-      <c r="AK42" s="77"/>
+      <c r="AD42" s="73"/>
+      <c r="AE42" s="62"/>
+      <c r="AF42" s="62"/>
+      <c r="AG42" s="62"/>
+      <c r="AH42" s="62"/>
+      <c r="AI42" s="62"/>
+      <c r="AJ42" s="62"/>
+      <c r="AK42" s="74"/>
     </row>
     <row r="43" spans="1:37" ht="15" customHeight="1">
       <c r="A43" s="55"/>
@@ -10080,20 +10080,20 @@
       <c r="AA43" s="17"/>
       <c r="AB43" s="17"/>
       <c r="AC43" s="6"/>
-      <c r="AD43" s="76"/>
-      <c r="AE43" s="61"/>
-      <c r="AF43" s="61"/>
-      <c r="AG43" s="61"/>
-      <c r="AH43" s="61"/>
-      <c r="AI43" s="61"/>
-      <c r="AJ43" s="61"/>
-      <c r="AK43" s="77"/>
+      <c r="AD43" s="73"/>
+      <c r="AE43" s="62"/>
+      <c r="AF43" s="62"/>
+      <c r="AG43" s="62"/>
+      <c r="AH43" s="62"/>
+      <c r="AI43" s="62"/>
+      <c r="AJ43" s="62"/>
+      <c r="AK43" s="74"/>
     </row>
     <row r="44" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="85" t="s">
+      <c r="B44" s="84" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="22"/>
@@ -10125,14 +10125,14 @@
       <c r="AA44" s="17"/>
       <c r="AB44" s="17"/>
       <c r="AC44" s="6"/>
-      <c r="AD44" s="76"/>
-      <c r="AE44" s="61"/>
-      <c r="AF44" s="61"/>
-      <c r="AG44" s="61"/>
-      <c r="AH44" s="61"/>
-      <c r="AI44" s="61"/>
-      <c r="AJ44" s="61"/>
-      <c r="AK44" s="77"/>
+      <c r="AD44" s="73"/>
+      <c r="AE44" s="62"/>
+      <c r="AF44" s="62"/>
+      <c r="AG44" s="62"/>
+      <c r="AH44" s="62"/>
+      <c r="AI44" s="62"/>
+      <c r="AJ44" s="62"/>
+      <c r="AK44" s="74"/>
     </row>
     <row r="45" spans="1:37" ht="14.25" customHeight="1">
       <c r="A45" s="55"/>
@@ -10147,9 +10147,9 @@
         <v>#VALUE!</v>
       </c>
       <c r="H45" s="17"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
       <c r="L45" s="18"/>
       <c r="M45" s="18"/>
       <c r="N45" s="17"/>
@@ -10168,20 +10168,20 @@
       <c r="AA45" s="17"/>
       <c r="AB45" s="17"/>
       <c r="AC45" s="6"/>
-      <c r="AD45" s="76"/>
-      <c r="AE45" s="61"/>
-      <c r="AF45" s="61"/>
-      <c r="AG45" s="61"/>
-      <c r="AH45" s="61"/>
-      <c r="AI45" s="61"/>
-      <c r="AJ45" s="61"/>
-      <c r="AK45" s="77"/>
+      <c r="AD45" s="73"/>
+      <c r="AE45" s="62"/>
+      <c r="AF45" s="62"/>
+      <c r="AG45" s="62"/>
+      <c r="AH45" s="62"/>
+      <c r="AI45" s="62"/>
+      <c r="AJ45" s="62"/>
+      <c r="AK45" s="74"/>
     </row>
     <row r="46" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A46" s="56" t="s">
+      <c r="A46" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="84" t="s">
+      <c r="B46" s="85" t="s">
         <v>67</v>
       </c>
       <c r="D46" s="22"/>
@@ -10213,14 +10213,14 @@
       <c r="AA46" s="17"/>
       <c r="AB46" s="17"/>
       <c r="AC46" s="6"/>
-      <c r="AD46" s="76"/>
-      <c r="AE46" s="61"/>
-      <c r="AF46" s="61"/>
-      <c r="AG46" s="61"/>
-      <c r="AH46" s="61"/>
-      <c r="AI46" s="61"/>
-      <c r="AJ46" s="61"/>
-      <c r="AK46" s="77"/>
+      <c r="AD46" s="73"/>
+      <c r="AE46" s="62"/>
+      <c r="AF46" s="62"/>
+      <c r="AG46" s="62"/>
+      <c r="AH46" s="62"/>
+      <c r="AI46" s="62"/>
+      <c r="AJ46" s="62"/>
+      <c r="AK46" s="74"/>
     </row>
     <row r="47" spans="1:37" ht="14.25" customHeight="1">
       <c r="A47" s="55"/>
@@ -10256,20 +10256,20 @@
       <c r="AA47" s="17"/>
       <c r="AB47" s="17"/>
       <c r="AC47" s="6"/>
-      <c r="AD47" s="76"/>
-      <c r="AE47" s="61"/>
-      <c r="AF47" s="61"/>
-      <c r="AG47" s="61"/>
-      <c r="AH47" s="61"/>
-      <c r="AI47" s="61"/>
-      <c r="AJ47" s="61"/>
-      <c r="AK47" s="77"/>
+      <c r="AD47" s="73"/>
+      <c r="AE47" s="62"/>
+      <c r="AF47" s="62"/>
+      <c r="AG47" s="62"/>
+      <c r="AH47" s="62"/>
+      <c r="AI47" s="62"/>
+      <c r="AJ47" s="62"/>
+      <c r="AK47" s="74"/>
     </row>
     <row r="48" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="85" t="s">
+      <c r="B48" s="84" t="s">
         <v>93</v>
       </c>
       <c r="D48" s="22"/>
@@ -10301,14 +10301,14 @@
       <c r="AA48" s="17"/>
       <c r="AB48" s="17"/>
       <c r="AC48" s="6"/>
-      <c r="AD48" s="78"/>
-      <c r="AE48" s="79"/>
-      <c r="AF48" s="79"/>
-      <c r="AG48" s="79"/>
-      <c r="AH48" s="79"/>
-      <c r="AI48" s="79"/>
-      <c r="AJ48" s="79"/>
-      <c r="AK48" s="80"/>
+      <c r="AD48" s="75"/>
+      <c r="AE48" s="76"/>
+      <c r="AF48" s="76"/>
+      <c r="AG48" s="76"/>
+      <c r="AH48" s="76"/>
+      <c r="AI48" s="76"/>
+      <c r="AJ48" s="76"/>
+      <c r="AK48" s="77"/>
     </row>
     <row r="49" spans="1:37" ht="14.25" customHeight="1">
       <c r="A49" s="55"/>
@@ -10323,9 +10323,9 @@
         <v>#VALUE!</v>
       </c>
       <c r="H49" s="40"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
       <c r="L49" s="18"/>
       <c r="M49" s="18"/>
       <c r="N49" s="17"/>
@@ -10356,10 +10356,10 @@
       <c r="AK49" s="38"/>
     </row>
     <row r="50" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A50" s="56" t="s">
+      <c r="A50" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="84" t="s">
         <v>95</v>
       </c>
       <c r="D50" s="22"/>
@@ -10414,13 +10414,13 @@
         <f t="array" aca="1" ref="G51" ca="1">IF(ISBLANK(INDIRECT(ADDRESS(ROW()-1,1,2,TRUE()))),"",IF((INDIRECT(ADDRESS(3,COLUMN(),2,1))="g"),"g"," "))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
       <c r="L51" s="18"/>
       <c r="M51" s="18"/>
-      <c r="N51" s="17"/>
+      <c r="N51" s="40"/>
       <c r="O51" s="17"/>
       <c r="P51" s="17"/>
       <c r="Q51" s="17"/>
@@ -10448,10 +10448,10 @@
       <c r="AK51" s="38"/>
     </row>
     <row r="52" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A52" s="56" t="s">
+      <c r="A52" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="85" t="s">
+      <c r="B52" s="84" t="s">
         <v>97</v>
       </c>
       <c r="D52" s="22"/>
@@ -10512,7 +10512,7 @@
       <c r="K53" s="17"/>
       <c r="L53" s="18"/>
       <c r="M53" s="18"/>
-      <c r="N53" s="17"/>
+      <c r="N53" s="40"/>
       <c r="O53" s="17"/>
       <c r="P53" s="17"/>
       <c r="Q53" s="17"/>
@@ -10540,10 +10540,10 @@
       <c r="AK53" s="38"/>
     </row>
     <row r="54" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A54" s="56" t="s">
+      <c r="A54" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="B54" s="85" t="s">
+      <c r="B54" s="84" t="s">
         <v>99</v>
       </c>
       <c r="D54" s="22"/>
@@ -10630,10 +10630,10 @@
       <c r="AK55" s="38"/>
     </row>
     <row r="56" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="B56" s="85" t="s">
+      <c r="B56" s="84" t="s">
         <v>101</v>
       </c>
       <c r="D56" s="22"/>
@@ -10710,10 +10710,10 @@
       <c r="AC57" s="6"/>
     </row>
     <row r="58" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="85" t="s">
+      <c r="B58" s="84" t="s">
         <v>103</v>
       </c>
       <c r="G58" s="12" t="e">
@@ -10783,10 +10783,10 @@
       <c r="AC59" s="6"/>
     </row>
     <row r="60" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A60" s="56" t="s">
+      <c r="A60" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="B60" s="85" t="s">
+      <c r="B60" s="84" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="12"/>
@@ -10860,10 +10860,10 @@
       <c r="AC61" s="6"/>
     </row>
     <row r="62" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A62" s="56" t="s">
+      <c r="A62" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="B62" s="85" t="s">
+      <c r="B62" s="84" t="s">
         <v>107</v>
       </c>
       <c r="F62" s="12"/>
@@ -10911,7 +10911,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="H63" s="40"/>
-      <c r="I63" s="24"/>
+      <c r="I63" s="40"/>
       <c r="J63" s="24"/>
       <c r="K63" s="24"/>
       <c r="L63" s="28"/>
@@ -10934,10 +10934,10 @@
       <c r="AC63" s="6"/>
     </row>
     <row r="64" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A64" s="56" t="s">
+      <c r="A64" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="B64" s="85" t="s">
+      <c r="B64" s="84" t="s">
         <v>109</v>
       </c>
       <c r="D64" s="22"/>
@@ -11010,10 +11010,10 @@
       <c r="AC65" s="6"/>
     </row>
     <row r="66" spans="1:29" ht="14.25" customHeight="1">
-      <c r="A66" s="56" t="s">
+      <c r="A66" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="B66" s="85" t="s">
+      <c r="B66" s="84" t="s">
         <v>111</v>
       </c>
       <c r="D66" s="22"/>
@@ -13905,20 +13905,41 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="AD3:AK31"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="AD34:AK48"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="B52:B53"/>
@@ -13935,41 +13956,20 @@
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="A52:A53"/>
-    <mergeCell ref="AD34:AK48"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="AD3:AK31"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="86" orientation="portrait"/>
@@ -14024,12 +14024,12 @@
       <c r="Z1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="57">
+      <c r="AA1" s="80">
         <v>2024</v>
       </c>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-      <c r="AD1" s="59"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="82"/>
       <c r="AE1" s="6"/>
       <c r="AF1" s="4" t="s">
         <v>2</v>
@@ -14085,10 +14085,10 @@
       <c r="A3" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
       <c r="J3" s="13" t="s">
         <v>5</v>
       </c>
@@ -14153,22 +14153,22 @@
         <v>25</v>
       </c>
       <c r="AE3" s="6"/>
-      <c r="AF3" s="64" t="s">
+      <c r="AF3" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="65"/>
-      <c r="AL3" s="65"/>
-      <c r="AM3" s="66"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="60"/>
     </row>
     <row r="4" spans="1:39" ht="14.25" customHeight="1">
-      <c r="D4" s="60"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
@@ -14191,14 +14191,14 @@
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="6"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="61"/>
-      <c r="AH4" s="61"/>
-      <c r="AI4" s="61"/>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="61"/>
-      <c r="AM4" s="68"/>
+      <c r="AF4" s="61"/>
+      <c r="AG4" s="62"/>
+      <c r="AH4" s="62"/>
+      <c r="AI4" s="62"/>
+      <c r="AJ4" s="62"/>
+      <c r="AK4" s="62"/>
+      <c r="AL4" s="62"/>
+      <c r="AM4" s="63"/>
     </row>
     <row r="5" spans="1:39" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
@@ -14250,20 +14250,20 @@
       <c r="AC5" s="12"/>
       <c r="AD5" s="16"/>
       <c r="AE5" s="6"/>
-      <c r="AF5" s="67"/>
-      <c r="AG5" s="61"/>
-      <c r="AH5" s="61"/>
-      <c r="AI5" s="61"/>
-      <c r="AJ5" s="61"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="61"/>
-      <c r="AM5" s="68"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="62"/>
+      <c r="AH5" s="62"/>
+      <c r="AI5" s="62"/>
+      <c r="AJ5" s="62"/>
+      <c r="AK5" s="62"/>
+      <c r="AL5" s="62"/>
+      <c r="AM5" s="63"/>
     </row>
     <row r="6" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="72"/>
+      <c r="B6" s="68"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -14295,14 +14295,14 @@
       <c r="AC6" s="17"/>
       <c r="AD6" s="17"/>
       <c r="AE6" s="6"/>
-      <c r="AF6" s="67"/>
-      <c r="AG6" s="61"/>
-      <c r="AH6" s="61"/>
-      <c r="AI6" s="61"/>
-      <c r="AJ6" s="61"/>
-      <c r="AK6" s="61"/>
-      <c r="AL6" s="61"/>
-      <c r="AM6" s="68"/>
+      <c r="AF6" s="61"/>
+      <c r="AG6" s="62"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="62"/>
+      <c r="AK6" s="62"/>
+      <c r="AL6" s="62"/>
+      <c r="AM6" s="63"/>
     </row>
     <row r="7" spans="1:39" ht="14.25" customHeight="1">
       <c r="A7" s="55"/>
@@ -14338,20 +14338,20 @@
       <c r="AC7" s="17"/>
       <c r="AD7" s="17"/>
       <c r="AE7" s="6"/>
-      <c r="AF7" s="67"/>
-      <c r="AG7" s="61"/>
-      <c r="AH7" s="61"/>
-      <c r="AI7" s="61"/>
-      <c r="AJ7" s="61"/>
-      <c r="AK7" s="61"/>
-      <c r="AL7" s="61"/>
-      <c r="AM7" s="68"/>
+      <c r="AF7" s="61"/>
+      <c r="AG7" s="62"/>
+      <c r="AH7" s="62"/>
+      <c r="AI7" s="62"/>
+      <c r="AJ7" s="62"/>
+      <c r="AK7" s="62"/>
+      <c r="AL7" s="62"/>
+      <c r="AM7" s="63"/>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="63"/>
+      <c r="B8" s="69"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
@@ -14383,14 +14383,14 @@
       <c r="AC8" s="17"/>
       <c r="AD8" s="17"/>
       <c r="AE8" s="6"/>
-      <c r="AF8" s="67"/>
-      <c r="AG8" s="61"/>
-      <c r="AH8" s="61"/>
-      <c r="AI8" s="61"/>
-      <c r="AJ8" s="61"/>
-      <c r="AK8" s="61"/>
-      <c r="AL8" s="61"/>
-      <c r="AM8" s="68"/>
+      <c r="AF8" s="61"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="62"/>
+      <c r="AL8" s="62"/>
+      <c r="AM8" s="63"/>
     </row>
     <row r="9" spans="1:39" ht="14.25" customHeight="1">
       <c r="A9" s="55"/>
@@ -14426,20 +14426,20 @@
       <c r="AC9" s="17"/>
       <c r="AD9" s="17"/>
       <c r="AE9" s="6"/>
-      <c r="AF9" s="67"/>
-      <c r="AG9" s="61"/>
-      <c r="AH9" s="61"/>
-      <c r="AI9" s="61"/>
-      <c r="AJ9" s="61"/>
-      <c r="AK9" s="61"/>
-      <c r="AL9" s="61"/>
-      <c r="AM9" s="68"/>
+      <c r="AF9" s="61"/>
+      <c r="AG9" s="62"/>
+      <c r="AH9" s="62"/>
+      <c r="AI9" s="62"/>
+      <c r="AJ9" s="62"/>
+      <c r="AK9" s="62"/>
+      <c r="AL9" s="62"/>
+      <c r="AM9" s="63"/>
     </row>
     <row r="10" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="63"/>
+      <c r="B10" s="69"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -14471,14 +14471,14 @@
       <c r="AC10" s="17"/>
       <c r="AD10" s="17"/>
       <c r="AE10" s="6"/>
-      <c r="AF10" s="67"/>
-      <c r="AG10" s="61"/>
-      <c r="AH10" s="61"/>
-      <c r="AI10" s="61"/>
-      <c r="AJ10" s="61"/>
-      <c r="AK10" s="61"/>
-      <c r="AL10" s="61"/>
-      <c r="AM10" s="68"/>
+      <c r="AF10" s="61"/>
+      <c r="AG10" s="62"/>
+      <c r="AH10" s="62"/>
+      <c r="AI10" s="62"/>
+      <c r="AJ10" s="62"/>
+      <c r="AK10" s="62"/>
+      <c r="AL10" s="62"/>
+      <c r="AM10" s="63"/>
     </row>
     <row r="11" spans="1:39" ht="14.25" customHeight="1">
       <c r="A11" s="55"/>
@@ -14514,20 +14514,20 @@
       <c r="AC11" s="17"/>
       <c r="AD11" s="17"/>
       <c r="AE11" s="6"/>
-      <c r="AF11" s="67"/>
-      <c r="AG11" s="61"/>
-      <c r="AH11" s="61"/>
-      <c r="AI11" s="61"/>
-      <c r="AJ11" s="61"/>
-      <c r="AK11" s="61"/>
-      <c r="AL11" s="61"/>
-      <c r="AM11" s="68"/>
+      <c r="AF11" s="61"/>
+      <c r="AG11" s="62"/>
+      <c r="AH11" s="62"/>
+      <c r="AI11" s="62"/>
+      <c r="AJ11" s="62"/>
+      <c r="AK11" s="62"/>
+      <c r="AL11" s="62"/>
+      <c r="AM11" s="63"/>
     </row>
     <row r="12" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="63"/>
+      <c r="B12" s="69"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -14559,14 +14559,14 @@
       <c r="AC12" s="17"/>
       <c r="AD12" s="17"/>
       <c r="AE12" s="6"/>
-      <c r="AF12" s="67"/>
-      <c r="AG12" s="61"/>
-      <c r="AH12" s="61"/>
-      <c r="AI12" s="61"/>
-      <c r="AJ12" s="61"/>
-      <c r="AK12" s="61"/>
-      <c r="AL12" s="61"/>
-      <c r="AM12" s="68"/>
+      <c r="AF12" s="61"/>
+      <c r="AG12" s="62"/>
+      <c r="AH12" s="62"/>
+      <c r="AI12" s="62"/>
+      <c r="AJ12" s="62"/>
+      <c r="AK12" s="62"/>
+      <c r="AL12" s="62"/>
+      <c r="AM12" s="63"/>
     </row>
     <row r="13" spans="1:39" ht="14.25" customHeight="1">
       <c r="A13" s="55"/>
@@ -14602,20 +14602,20 @@
       <c r="AC13" s="17"/>
       <c r="AD13" s="17"/>
       <c r="AE13" s="6"/>
-      <c r="AF13" s="67"/>
-      <c r="AG13" s="61"/>
-      <c r="AH13" s="61"/>
-      <c r="AI13" s="61"/>
-      <c r="AJ13" s="61"/>
-      <c r="AK13" s="61"/>
-      <c r="AL13" s="61"/>
-      <c r="AM13" s="68"/>
+      <c r="AF13" s="61"/>
+      <c r="AG13" s="62"/>
+      <c r="AH13" s="62"/>
+      <c r="AI13" s="62"/>
+      <c r="AJ13" s="62"/>
+      <c r="AK13" s="62"/>
+      <c r="AL13" s="62"/>
+      <c r="AM13" s="63"/>
     </row>
     <row r="14" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="63"/>
+      <c r="B14" s="69"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -14647,14 +14647,14 @@
       <c r="AC14" s="17"/>
       <c r="AD14" s="17"/>
       <c r="AE14" s="6"/>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="61"/>
-      <c r="AH14" s="61"/>
-      <c r="AI14" s="61"/>
-      <c r="AJ14" s="61"/>
-      <c r="AK14" s="61"/>
-      <c r="AL14" s="61"/>
-      <c r="AM14" s="68"/>
+      <c r="AF14" s="61"/>
+      <c r="AG14" s="62"/>
+      <c r="AH14" s="62"/>
+      <c r="AI14" s="62"/>
+      <c r="AJ14" s="62"/>
+      <c r="AK14" s="62"/>
+      <c r="AL14" s="62"/>
+      <c r="AM14" s="63"/>
     </row>
     <row r="15" spans="1:39" ht="17.25" customHeight="1">
       <c r="A15" s="55"/>
@@ -14690,20 +14690,20 @@
       <c r="AC15" s="17"/>
       <c r="AD15" s="17"/>
       <c r="AE15" s="6"/>
-      <c r="AF15" s="67"/>
-      <c r="AG15" s="61"/>
-      <c r="AH15" s="61"/>
-      <c r="AI15" s="61"/>
-      <c r="AJ15" s="61"/>
-      <c r="AK15" s="61"/>
-      <c r="AL15" s="61"/>
-      <c r="AM15" s="68"/>
+      <c r="AF15" s="61"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="62"/>
+      <c r="AL15" s="62"/>
+      <c r="AM15" s="63"/>
     </row>
     <row r="16" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="63"/>
+      <c r="B16" s="69"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -14735,14 +14735,14 @@
       <c r="AC16" s="17"/>
       <c r="AD16" s="17"/>
       <c r="AE16" s="6"/>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="61"/>
-      <c r="AH16" s="61"/>
-      <c r="AI16" s="61"/>
-      <c r="AJ16" s="61"/>
-      <c r="AK16" s="61"/>
-      <c r="AL16" s="61"/>
-      <c r="AM16" s="68"/>
+      <c r="AF16" s="61"/>
+      <c r="AG16" s="62"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="62"/>
+      <c r="AJ16" s="62"/>
+      <c r="AK16" s="62"/>
+      <c r="AL16" s="62"/>
+      <c r="AM16" s="63"/>
     </row>
     <row r="17" spans="1:39" ht="17.25" customHeight="1">
       <c r="A17" s="55"/>
@@ -14778,20 +14778,20 @@
       <c r="AC17" s="17"/>
       <c r="AD17" s="17"/>
       <c r="AE17" s="6"/>
-      <c r="AF17" s="67"/>
-      <c r="AG17" s="61"/>
-      <c r="AH17" s="61"/>
-      <c r="AI17" s="61"/>
-      <c r="AJ17" s="61"/>
-      <c r="AK17" s="61"/>
-      <c r="AL17" s="61"/>
-      <c r="AM17" s="68"/>
+      <c r="AF17" s="61"/>
+      <c r="AG17" s="62"/>
+      <c r="AH17" s="62"/>
+      <c r="AI17" s="62"/>
+      <c r="AJ17" s="62"/>
+      <c r="AK17" s="62"/>
+      <c r="AL17" s="62"/>
+      <c r="AM17" s="63"/>
     </row>
     <row r="18" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="63"/>
+      <c r="B18" s="69"/>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -14823,14 +14823,14 @@
       <c r="AC18" s="17"/>
       <c r="AD18" s="17"/>
       <c r="AE18" s="6"/>
-      <c r="AF18" s="67"/>
-      <c r="AG18" s="61"/>
-      <c r="AH18" s="61"/>
-      <c r="AI18" s="61"/>
-      <c r="AJ18" s="61"/>
-      <c r="AK18" s="61"/>
-      <c r="AL18" s="61"/>
-      <c r="AM18" s="68"/>
+      <c r="AF18" s="61"/>
+      <c r="AG18" s="62"/>
+      <c r="AH18" s="62"/>
+      <c r="AI18" s="62"/>
+      <c r="AJ18" s="62"/>
+      <c r="AK18" s="62"/>
+      <c r="AL18" s="62"/>
+      <c r="AM18" s="63"/>
     </row>
     <row r="19" spans="1:39" ht="17.25" customHeight="1">
       <c r="A19" s="55"/>
@@ -14866,20 +14866,20 @@
       <c r="AC19" s="17"/>
       <c r="AD19" s="17"/>
       <c r="AE19" s="6"/>
-      <c r="AF19" s="67"/>
-      <c r="AG19" s="61"/>
-      <c r="AH19" s="61"/>
-      <c r="AI19" s="61"/>
-      <c r="AJ19" s="61"/>
-      <c r="AK19" s="61"/>
-      <c r="AL19" s="61"/>
-      <c r="AM19" s="68"/>
+      <c r="AF19" s="61"/>
+      <c r="AG19" s="62"/>
+      <c r="AH19" s="62"/>
+      <c r="AI19" s="62"/>
+      <c r="AJ19" s="62"/>
+      <c r="AK19" s="62"/>
+      <c r="AL19" s="62"/>
+      <c r="AM19" s="63"/>
     </row>
     <row r="20" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="54"/>
+      <c r="B20" s="56"/>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -14911,14 +14911,14 @@
       <c r="AC20" s="17"/>
       <c r="AD20" s="17"/>
       <c r="AE20" s="6"/>
-      <c r="AF20" s="67"/>
-      <c r="AG20" s="61"/>
-      <c r="AH20" s="61"/>
-      <c r="AI20" s="61"/>
-      <c r="AJ20" s="61"/>
-      <c r="AK20" s="61"/>
-      <c r="AL20" s="61"/>
-      <c r="AM20" s="68"/>
+      <c r="AF20" s="61"/>
+      <c r="AG20" s="62"/>
+      <c r="AH20" s="62"/>
+      <c r="AI20" s="62"/>
+      <c r="AJ20" s="62"/>
+      <c r="AK20" s="62"/>
+      <c r="AL20" s="62"/>
+      <c r="AM20" s="63"/>
     </row>
     <row r="21" spans="1:39" ht="14.25" customHeight="1">
       <c r="A21" s="55"/>
@@ -14954,20 +14954,20 @@
       <c r="AC21" s="17"/>
       <c r="AD21" s="17"/>
       <c r="AE21" s="6"/>
-      <c r="AF21" s="67"/>
-      <c r="AG21" s="61"/>
-      <c r="AH21" s="61"/>
-      <c r="AI21" s="61"/>
-      <c r="AJ21" s="61"/>
-      <c r="AK21" s="61"/>
-      <c r="AL21" s="61"/>
-      <c r="AM21" s="68"/>
+      <c r="AF21" s="61"/>
+      <c r="AG21" s="62"/>
+      <c r="AH21" s="62"/>
+      <c r="AI21" s="62"/>
+      <c r="AJ21" s="62"/>
+      <c r="AK21" s="62"/>
+      <c r="AL21" s="62"/>
+      <c r="AM21" s="63"/>
     </row>
     <row r="22" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="54"/>
+      <c r="B22" s="56"/>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -14999,14 +14999,14 @@
       <c r="AC22" s="17"/>
       <c r="AD22" s="17"/>
       <c r="AE22" s="6"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="61"/>
-      <c r="AH22" s="61"/>
-      <c r="AI22" s="61"/>
-      <c r="AJ22" s="61"/>
-      <c r="AK22" s="61"/>
-      <c r="AL22" s="61"/>
-      <c r="AM22" s="68"/>
+      <c r="AF22" s="61"/>
+      <c r="AG22" s="62"/>
+      <c r="AH22" s="62"/>
+      <c r="AI22" s="62"/>
+      <c r="AJ22" s="62"/>
+      <c r="AK22" s="62"/>
+      <c r="AL22" s="62"/>
+      <c r="AM22" s="63"/>
     </row>
     <row r="23" spans="1:39" ht="14.25" customHeight="1">
       <c r="A23" s="55"/>
@@ -15042,20 +15042,20 @@
       <c r="AC23" s="17"/>
       <c r="AD23" s="17"/>
       <c r="AE23" s="6"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="61"/>
-      <c r="AH23" s="61"/>
-      <c r="AI23" s="61"/>
-      <c r="AJ23" s="61"/>
-      <c r="AK23" s="61"/>
-      <c r="AL23" s="61"/>
-      <c r="AM23" s="68"/>
+      <c r="AF23" s="61"/>
+      <c r="AG23" s="62"/>
+      <c r="AH23" s="62"/>
+      <c r="AI23" s="62"/>
+      <c r="AJ23" s="62"/>
+      <c r="AK23" s="62"/>
+      <c r="AL23" s="62"/>
+      <c r="AM23" s="63"/>
     </row>
     <row r="24" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="81"/>
+      <c r="B24" s="78"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -15087,14 +15087,14 @@
       <c r="AC24" s="17"/>
       <c r="AD24" s="17"/>
       <c r="AE24" s="6"/>
-      <c r="AF24" s="67"/>
-      <c r="AG24" s="61"/>
-      <c r="AH24" s="61"/>
-      <c r="AI24" s="61"/>
-      <c r="AJ24" s="61"/>
-      <c r="AK24" s="61"/>
-      <c r="AL24" s="61"/>
-      <c r="AM24" s="68"/>
+      <c r="AF24" s="61"/>
+      <c r="AG24" s="62"/>
+      <c r="AH24" s="62"/>
+      <c r="AI24" s="62"/>
+      <c r="AJ24" s="62"/>
+      <c r="AK24" s="62"/>
+      <c r="AL24" s="62"/>
+      <c r="AM24" s="63"/>
     </row>
     <row r="25" spans="1:39" ht="14.25" customHeight="1">
       <c r="A25" s="55"/>
@@ -15130,20 +15130,20 @@
       <c r="AC25" s="17"/>
       <c r="AD25" s="17"/>
       <c r="AE25" s="6"/>
-      <c r="AF25" s="67"/>
-      <c r="AG25" s="61"/>
-      <c r="AH25" s="61"/>
-      <c r="AI25" s="61"/>
-      <c r="AJ25" s="61"/>
-      <c r="AK25" s="61"/>
-      <c r="AL25" s="61"/>
-      <c r="AM25" s="68"/>
+      <c r="AF25" s="61"/>
+      <c r="AG25" s="62"/>
+      <c r="AH25" s="62"/>
+      <c r="AI25" s="62"/>
+      <c r="AJ25" s="62"/>
+      <c r="AK25" s="62"/>
+      <c r="AL25" s="62"/>
+      <c r="AM25" s="63"/>
     </row>
     <row r="26" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="81"/>
+      <c r="B26" s="78"/>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -15175,14 +15175,14 @@
       <c r="AC26" s="17"/>
       <c r="AD26" s="17"/>
       <c r="AE26" s="6"/>
-      <c r="AF26" s="67"/>
-      <c r="AG26" s="61"/>
-      <c r="AH26" s="61"/>
-      <c r="AI26" s="61"/>
-      <c r="AJ26" s="61"/>
-      <c r="AK26" s="61"/>
-      <c r="AL26" s="61"/>
-      <c r="AM26" s="68"/>
+      <c r="AF26" s="61"/>
+      <c r="AG26" s="62"/>
+      <c r="AH26" s="62"/>
+      <c r="AI26" s="62"/>
+      <c r="AJ26" s="62"/>
+      <c r="AK26" s="62"/>
+      <c r="AL26" s="62"/>
+      <c r="AM26" s="63"/>
     </row>
     <row r="27" spans="1:39" ht="14.25" customHeight="1">
       <c r="A27" s="55"/>
@@ -15218,20 +15218,20 @@
       <c r="AC27" s="17"/>
       <c r="AD27" s="17"/>
       <c r="AE27" s="6"/>
-      <c r="AF27" s="67"/>
-      <c r="AG27" s="61"/>
-      <c r="AH27" s="61"/>
-      <c r="AI27" s="61"/>
-      <c r="AJ27" s="61"/>
-      <c r="AK27" s="61"/>
-      <c r="AL27" s="61"/>
-      <c r="AM27" s="68"/>
+      <c r="AF27" s="61"/>
+      <c r="AG27" s="62"/>
+      <c r="AH27" s="62"/>
+      <c r="AI27" s="62"/>
+      <c r="AJ27" s="62"/>
+      <c r="AK27" s="62"/>
+      <c r="AL27" s="62"/>
+      <c r="AM27" s="63"/>
     </row>
     <row r="28" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="81"/>
+      <c r="B28" s="78"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -15263,14 +15263,14 @@
       <c r="AC28" s="17"/>
       <c r="AD28" s="17"/>
       <c r="AE28" s="6"/>
-      <c r="AF28" s="67"/>
-      <c r="AG28" s="61"/>
-      <c r="AH28" s="61"/>
-      <c r="AI28" s="61"/>
-      <c r="AJ28" s="61"/>
-      <c r="AK28" s="61"/>
-      <c r="AL28" s="61"/>
-      <c r="AM28" s="68"/>
+      <c r="AF28" s="61"/>
+      <c r="AG28" s="62"/>
+      <c r="AH28" s="62"/>
+      <c r="AI28" s="62"/>
+      <c r="AJ28" s="62"/>
+      <c r="AK28" s="62"/>
+      <c r="AL28" s="62"/>
+      <c r="AM28" s="63"/>
     </row>
     <row r="29" spans="1:39" ht="14.25" customHeight="1">
       <c r="A29" s="55"/>
@@ -15306,20 +15306,20 @@
       <c r="AC29" s="17"/>
       <c r="AD29" s="17"/>
       <c r="AE29" s="6"/>
-      <c r="AF29" s="67"/>
-      <c r="AG29" s="61"/>
-      <c r="AH29" s="61"/>
-      <c r="AI29" s="61"/>
-      <c r="AJ29" s="61"/>
-      <c r="AK29" s="61"/>
-      <c r="AL29" s="61"/>
-      <c r="AM29" s="68"/>
+      <c r="AF29" s="61"/>
+      <c r="AG29" s="62"/>
+      <c r="AH29" s="62"/>
+      <c r="AI29" s="62"/>
+      <c r="AJ29" s="62"/>
+      <c r="AK29" s="62"/>
+      <c r="AL29" s="62"/>
+      <c r="AM29" s="63"/>
     </row>
     <row r="30" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="82"/>
+      <c r="B30" s="79"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -15351,14 +15351,14 @@
       <c r="AC30" s="17"/>
       <c r="AD30" s="17"/>
       <c r="AE30" s="6"/>
-      <c r="AF30" s="67"/>
-      <c r="AG30" s="61"/>
-      <c r="AH30" s="61"/>
-      <c r="AI30" s="61"/>
-      <c r="AJ30" s="61"/>
-      <c r="AK30" s="61"/>
-      <c r="AL30" s="61"/>
-      <c r="AM30" s="68"/>
+      <c r="AF30" s="61"/>
+      <c r="AG30" s="62"/>
+      <c r="AH30" s="62"/>
+      <c r="AI30" s="62"/>
+      <c r="AJ30" s="62"/>
+      <c r="AK30" s="62"/>
+      <c r="AL30" s="62"/>
+      <c r="AM30" s="63"/>
     </row>
     <row r="31" spans="1:39" ht="14.25" customHeight="1">
       <c r="A31" s="55"/>
@@ -15394,20 +15394,20 @@
       <c r="AC31" s="17"/>
       <c r="AD31" s="17"/>
       <c r="AE31" s="6"/>
-      <c r="AF31" s="67"/>
-      <c r="AG31" s="61"/>
-      <c r="AH31" s="61"/>
-      <c r="AI31" s="61"/>
-      <c r="AJ31" s="61"/>
-      <c r="AK31" s="61"/>
-      <c r="AL31" s="61"/>
-      <c r="AM31" s="68"/>
+      <c r="AF31" s="61"/>
+      <c r="AG31" s="62"/>
+      <c r="AH31" s="62"/>
+      <c r="AI31" s="62"/>
+      <c r="AJ31" s="62"/>
+      <c r="AK31" s="62"/>
+      <c r="AL31" s="62"/>
+      <c r="AM31" s="63"/>
     </row>
     <row r="32" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="82"/>
+      <c r="B32" s="79"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -15439,14 +15439,14 @@
       <c r="AC32" s="17"/>
       <c r="AD32" s="17"/>
       <c r="AE32" s="6"/>
-      <c r="AF32" s="67"/>
-      <c r="AG32" s="61"/>
-      <c r="AH32" s="61"/>
-      <c r="AI32" s="61"/>
-      <c r="AJ32" s="61"/>
-      <c r="AK32" s="61"/>
-      <c r="AL32" s="61"/>
-      <c r="AM32" s="68"/>
+      <c r="AF32" s="61"/>
+      <c r="AG32" s="62"/>
+      <c r="AH32" s="62"/>
+      <c r="AI32" s="62"/>
+      <c r="AJ32" s="62"/>
+      <c r="AK32" s="62"/>
+      <c r="AL32" s="62"/>
+      <c r="AM32" s="63"/>
     </row>
     <row r="33" spans="1:39" ht="14.25" customHeight="1">
       <c r="A33" s="55"/>
@@ -15482,20 +15482,20 @@
       <c r="AC33" s="17"/>
       <c r="AD33" s="17"/>
       <c r="AE33" s="6"/>
-      <c r="AF33" s="67"/>
-      <c r="AG33" s="61"/>
-      <c r="AH33" s="61"/>
-      <c r="AI33" s="61"/>
-      <c r="AJ33" s="61"/>
-      <c r="AK33" s="61"/>
-      <c r="AL33" s="61"/>
-      <c r="AM33" s="68"/>
+      <c r="AF33" s="61"/>
+      <c r="AG33" s="62"/>
+      <c r="AH33" s="62"/>
+      <c r="AI33" s="62"/>
+      <c r="AJ33" s="62"/>
+      <c r="AK33" s="62"/>
+      <c r="AL33" s="62"/>
+      <c r="AM33" s="63"/>
     </row>
     <row r="34" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="82"/>
+      <c r="B34" s="79"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -15527,14 +15527,14 @@
       <c r="AC34" s="17"/>
       <c r="AD34" s="17"/>
       <c r="AE34" s="6"/>
-      <c r="AF34" s="67"/>
-      <c r="AG34" s="61"/>
-      <c r="AH34" s="61"/>
-      <c r="AI34" s="61"/>
-      <c r="AJ34" s="61"/>
-      <c r="AK34" s="61"/>
-      <c r="AL34" s="61"/>
-      <c r="AM34" s="68"/>
+      <c r="AF34" s="61"/>
+      <c r="AG34" s="62"/>
+      <c r="AH34" s="62"/>
+      <c r="AI34" s="62"/>
+      <c r="AJ34" s="62"/>
+      <c r="AK34" s="62"/>
+      <c r="AL34" s="62"/>
+      <c r="AM34" s="63"/>
     </row>
     <row r="35" spans="1:39" ht="14.25" customHeight="1">
       <c r="A35" s="55"/>
@@ -15570,20 +15570,20 @@
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
       <c r="AE35" s="6"/>
-      <c r="AF35" s="67"/>
-      <c r="AG35" s="61"/>
-      <c r="AH35" s="61"/>
-      <c r="AI35" s="61"/>
-      <c r="AJ35" s="61"/>
-      <c r="AK35" s="61"/>
-      <c r="AL35" s="61"/>
-      <c r="AM35" s="68"/>
+      <c r="AF35" s="61"/>
+      <c r="AG35" s="62"/>
+      <c r="AH35" s="62"/>
+      <c r="AI35" s="62"/>
+      <c r="AJ35" s="62"/>
+      <c r="AK35" s="62"/>
+      <c r="AL35" s="62"/>
+      <c r="AM35" s="63"/>
     </row>
     <row r="36" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="82"/>
+      <c r="B36" s="79"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -15615,14 +15615,14 @@
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
       <c r="AE36" s="6"/>
-      <c r="AF36" s="67"/>
-      <c r="AG36" s="61"/>
-      <c r="AH36" s="61"/>
-      <c r="AI36" s="61"/>
-      <c r="AJ36" s="61"/>
-      <c r="AK36" s="61"/>
-      <c r="AL36" s="61"/>
-      <c r="AM36" s="68"/>
+      <c r="AF36" s="61"/>
+      <c r="AG36" s="62"/>
+      <c r="AH36" s="62"/>
+      <c r="AI36" s="62"/>
+      <c r="AJ36" s="62"/>
+      <c r="AK36" s="62"/>
+      <c r="AL36" s="62"/>
+      <c r="AM36" s="63"/>
     </row>
     <row r="37" spans="1:39" ht="14.25" customHeight="1">
       <c r="A37" s="55"/>
@@ -15658,20 +15658,20 @@
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
       <c r="AE37" s="6"/>
-      <c r="AF37" s="69"/>
-      <c r="AG37" s="70"/>
-      <c r="AH37" s="70"/>
-      <c r="AI37" s="70"/>
-      <c r="AJ37" s="70"/>
-      <c r="AK37" s="70"/>
-      <c r="AL37" s="70"/>
-      <c r="AM37" s="71"/>
+      <c r="AF37" s="64"/>
+      <c r="AG37" s="65"/>
+      <c r="AH37" s="65"/>
+      <c r="AI37" s="65"/>
+      <c r="AJ37" s="65"/>
+      <c r="AK37" s="65"/>
+      <c r="AL37" s="65"/>
+      <c r="AM37" s="66"/>
     </row>
     <row r="38" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A38" s="56" t="s">
+      <c r="A38" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="82"/>
+      <c r="B38" s="79"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -15756,10 +15756,10 @@
       <c r="AM39" s="52"/>
     </row>
     <row r="40" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="82"/>
+      <c r="B40" s="79"/>
       <c r="D40" s="22"/>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -15844,10 +15844,10 @@
       <c r="AM41" s="52"/>
     </row>
     <row r="42" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="82"/>
+      <c r="B42" s="79"/>
       <c r="D42" s="22"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -15932,10 +15932,10 @@
       <c r="AM43" s="52"/>
     </row>
     <row r="44" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="82"/>
+      <c r="B44" s="79"/>
       <c r="D44" s="22"/>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -15967,14 +15967,14 @@
       <c r="AC44" s="17"/>
       <c r="AD44" s="17"/>
       <c r="AE44" s="6"/>
-      <c r="AF44" s="73"/>
-      <c r="AG44" s="74"/>
-      <c r="AH44" s="74"/>
-      <c r="AI44" s="74"/>
-      <c r="AJ44" s="74"/>
-      <c r="AK44" s="74"/>
-      <c r="AL44" s="74"/>
-      <c r="AM44" s="75"/>
+      <c r="AF44" s="70"/>
+      <c r="AG44" s="71"/>
+      <c r="AH44" s="71"/>
+      <c r="AI44" s="71"/>
+      <c r="AJ44" s="71"/>
+      <c r="AK44" s="71"/>
+      <c r="AL44" s="71"/>
+      <c r="AM44" s="72"/>
     </row>
     <row r="45" spans="1:39" ht="18" customHeight="1">
       <c r="A45" s="55"/>
@@ -16010,20 +16010,20 @@
       <c r="AC45" s="17"/>
       <c r="AD45" s="17"/>
       <c r="AE45" s="6"/>
-      <c r="AF45" s="76"/>
-      <c r="AG45" s="61"/>
-      <c r="AH45" s="61"/>
-      <c r="AI45" s="61"/>
-      <c r="AJ45" s="61"/>
-      <c r="AK45" s="61"/>
-      <c r="AL45" s="61"/>
-      <c r="AM45" s="77"/>
+      <c r="AF45" s="73"/>
+      <c r="AG45" s="62"/>
+      <c r="AH45" s="62"/>
+      <c r="AI45" s="62"/>
+      <c r="AJ45" s="62"/>
+      <c r="AK45" s="62"/>
+      <c r="AL45" s="62"/>
+      <c r="AM45" s="74"/>
     </row>
     <row r="46" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A46" s="56" t="s">
+      <c r="A46" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="82"/>
+      <c r="B46" s="79"/>
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -16055,14 +16055,14 @@
       <c r="AC46" s="17"/>
       <c r="AD46" s="17"/>
       <c r="AE46" s="6"/>
-      <c r="AF46" s="76"/>
-      <c r="AG46" s="61"/>
-      <c r="AH46" s="61"/>
-      <c r="AI46" s="61"/>
-      <c r="AJ46" s="61"/>
-      <c r="AK46" s="61"/>
-      <c r="AL46" s="61"/>
-      <c r="AM46" s="77"/>
+      <c r="AF46" s="73"/>
+      <c r="AG46" s="62"/>
+      <c r="AH46" s="62"/>
+      <c r="AI46" s="62"/>
+      <c r="AJ46" s="62"/>
+      <c r="AK46" s="62"/>
+      <c r="AL46" s="62"/>
+      <c r="AM46" s="74"/>
     </row>
     <row r="47" spans="1:39" ht="18" customHeight="1">
       <c r="A47" s="55"/>
@@ -16098,20 +16098,20 @@
       <c r="AC47" s="17"/>
       <c r="AD47" s="17"/>
       <c r="AE47" s="6"/>
-      <c r="AF47" s="76"/>
-      <c r="AG47" s="61"/>
-      <c r="AH47" s="61"/>
-      <c r="AI47" s="61"/>
-      <c r="AJ47" s="61"/>
-      <c r="AK47" s="61"/>
-      <c r="AL47" s="61"/>
-      <c r="AM47" s="77"/>
+      <c r="AF47" s="73"/>
+      <c r="AG47" s="62"/>
+      <c r="AH47" s="62"/>
+      <c r="AI47" s="62"/>
+      <c r="AJ47" s="62"/>
+      <c r="AK47" s="62"/>
+      <c r="AL47" s="62"/>
+      <c r="AM47" s="74"/>
     </row>
     <row r="48" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="82"/>
+      <c r="B48" s="79"/>
       <c r="D48" s="22"/>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -16143,14 +16143,14 @@
       <c r="AC48" s="17"/>
       <c r="AD48" s="17"/>
       <c r="AE48" s="6"/>
-      <c r="AF48" s="76"/>
-      <c r="AG48" s="61"/>
-      <c r="AH48" s="61"/>
-      <c r="AI48" s="61"/>
-      <c r="AJ48" s="61"/>
-      <c r="AK48" s="61"/>
-      <c r="AL48" s="61"/>
-      <c r="AM48" s="77"/>
+      <c r="AF48" s="73"/>
+      <c r="AG48" s="62"/>
+      <c r="AH48" s="62"/>
+      <c r="AI48" s="62"/>
+      <c r="AJ48" s="62"/>
+      <c r="AK48" s="62"/>
+      <c r="AL48" s="62"/>
+      <c r="AM48" s="74"/>
     </row>
     <row r="49" spans="1:39" ht="14.25" customHeight="1">
       <c r="A49" s="55"/>
@@ -16186,20 +16186,20 @@
       <c r="AC49" s="17"/>
       <c r="AD49" s="17"/>
       <c r="AE49" s="6"/>
-      <c r="AF49" s="76"/>
-      <c r="AG49" s="61"/>
-      <c r="AH49" s="61"/>
-      <c r="AI49" s="61"/>
-      <c r="AJ49" s="61"/>
-      <c r="AK49" s="61"/>
-      <c r="AL49" s="61"/>
-      <c r="AM49" s="77"/>
+      <c r="AF49" s="73"/>
+      <c r="AG49" s="62"/>
+      <c r="AH49" s="62"/>
+      <c r="AI49" s="62"/>
+      <c r="AJ49" s="62"/>
+      <c r="AK49" s="62"/>
+      <c r="AL49" s="62"/>
+      <c r="AM49" s="74"/>
     </row>
     <row r="50" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A50" s="56" t="s">
+      <c r="A50" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="82"/>
+      <c r="B50" s="79"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -16231,14 +16231,14 @@
       <c r="AC50" s="17"/>
       <c r="AD50" s="17"/>
       <c r="AE50" s="6"/>
-      <c r="AF50" s="76"/>
-      <c r="AG50" s="61"/>
-      <c r="AH50" s="61"/>
-      <c r="AI50" s="61"/>
-      <c r="AJ50" s="61"/>
-      <c r="AK50" s="61"/>
-      <c r="AL50" s="61"/>
-      <c r="AM50" s="77"/>
+      <c r="AF50" s="73"/>
+      <c r="AG50" s="62"/>
+      <c r="AH50" s="62"/>
+      <c r="AI50" s="62"/>
+      <c r="AJ50" s="62"/>
+      <c r="AK50" s="62"/>
+      <c r="AL50" s="62"/>
+      <c r="AM50" s="74"/>
     </row>
     <row r="51" spans="1:39" ht="18" customHeight="1">
       <c r="A51" s="55"/>
@@ -16274,20 +16274,20 @@
       <c r="AC51" s="17"/>
       <c r="AD51" s="17"/>
       <c r="AE51" s="6"/>
-      <c r="AF51" s="76"/>
-      <c r="AG51" s="61"/>
-      <c r="AH51" s="61"/>
-      <c r="AI51" s="61"/>
-      <c r="AJ51" s="61"/>
-      <c r="AK51" s="61"/>
-      <c r="AL51" s="61"/>
-      <c r="AM51" s="77"/>
+      <c r="AF51" s="73"/>
+      <c r="AG51" s="62"/>
+      <c r="AH51" s="62"/>
+      <c r="AI51" s="62"/>
+      <c r="AJ51" s="62"/>
+      <c r="AK51" s="62"/>
+      <c r="AL51" s="62"/>
+      <c r="AM51" s="74"/>
     </row>
     <row r="52" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A52" s="56" t="s">
+      <c r="A52" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="82"/>
+      <c r="B52" s="79"/>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
@@ -16319,14 +16319,14 @@
       <c r="AC52" s="17"/>
       <c r="AD52" s="17"/>
       <c r="AE52" s="6"/>
-      <c r="AF52" s="76"/>
-      <c r="AG52" s="61"/>
-      <c r="AH52" s="61"/>
-      <c r="AI52" s="61"/>
-      <c r="AJ52" s="61"/>
-      <c r="AK52" s="61"/>
-      <c r="AL52" s="61"/>
-      <c r="AM52" s="77"/>
+      <c r="AF52" s="73"/>
+      <c r="AG52" s="62"/>
+      <c r="AH52" s="62"/>
+      <c r="AI52" s="62"/>
+      <c r="AJ52" s="62"/>
+      <c r="AK52" s="62"/>
+      <c r="AL52" s="62"/>
+      <c r="AM52" s="74"/>
     </row>
     <row r="53" spans="1:39" ht="18" customHeight="1">
       <c r="A53" s="55"/>
@@ -16362,20 +16362,20 @@
       <c r="AC53" s="17"/>
       <c r="AD53" s="17"/>
       <c r="AE53" s="6"/>
-      <c r="AF53" s="76"/>
-      <c r="AG53" s="61"/>
-      <c r="AH53" s="61"/>
-      <c r="AI53" s="61"/>
-      <c r="AJ53" s="61"/>
-      <c r="AK53" s="61"/>
-      <c r="AL53" s="61"/>
-      <c r="AM53" s="77"/>
+      <c r="AF53" s="73"/>
+      <c r="AG53" s="62"/>
+      <c r="AH53" s="62"/>
+      <c r="AI53" s="62"/>
+      <c r="AJ53" s="62"/>
+      <c r="AK53" s="62"/>
+      <c r="AL53" s="62"/>
+      <c r="AM53" s="74"/>
     </row>
     <row r="54" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A54" s="56" t="s">
+      <c r="A54" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="82"/>
+      <c r="B54" s="79"/>
       <c r="D54" s="22"/>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -16407,14 +16407,14 @@
       <c r="AC54" s="17"/>
       <c r="AD54" s="17"/>
       <c r="AE54" s="6"/>
-      <c r="AF54" s="76"/>
-      <c r="AG54" s="61"/>
-      <c r="AH54" s="61"/>
-      <c r="AI54" s="61"/>
-      <c r="AJ54" s="61"/>
-      <c r="AK54" s="61"/>
-      <c r="AL54" s="61"/>
-      <c r="AM54" s="77"/>
+      <c r="AF54" s="73"/>
+      <c r="AG54" s="62"/>
+      <c r="AH54" s="62"/>
+      <c r="AI54" s="62"/>
+      <c r="AJ54" s="62"/>
+      <c r="AK54" s="62"/>
+      <c r="AL54" s="62"/>
+      <c r="AM54" s="74"/>
     </row>
     <row r="55" spans="1:39" ht="18" customHeight="1">
       <c r="A55" s="55"/>
@@ -16450,20 +16450,20 @@
       <c r="AC55" s="17"/>
       <c r="AD55" s="17"/>
       <c r="AE55" s="6"/>
-      <c r="AF55" s="76"/>
-      <c r="AG55" s="61"/>
-      <c r="AH55" s="61"/>
-      <c r="AI55" s="61"/>
-      <c r="AJ55" s="61"/>
-      <c r="AK55" s="61"/>
-      <c r="AL55" s="61"/>
-      <c r="AM55" s="77"/>
+      <c r="AF55" s="73"/>
+      <c r="AG55" s="62"/>
+      <c r="AH55" s="62"/>
+      <c r="AI55" s="62"/>
+      <c r="AJ55" s="62"/>
+      <c r="AK55" s="62"/>
+      <c r="AL55" s="62"/>
+      <c r="AM55" s="74"/>
     </row>
     <row r="56" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="82"/>
+      <c r="B56" s="79"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -16495,14 +16495,14 @@
       <c r="AC56" s="17"/>
       <c r="AD56" s="17"/>
       <c r="AE56" s="6"/>
-      <c r="AF56" s="76"/>
-      <c r="AG56" s="61"/>
-      <c r="AH56" s="61"/>
-      <c r="AI56" s="61"/>
-      <c r="AJ56" s="61"/>
-      <c r="AK56" s="61"/>
-      <c r="AL56" s="61"/>
-      <c r="AM56" s="77"/>
+      <c r="AF56" s="73"/>
+      <c r="AG56" s="62"/>
+      <c r="AH56" s="62"/>
+      <c r="AI56" s="62"/>
+      <c r="AJ56" s="62"/>
+      <c r="AK56" s="62"/>
+      <c r="AL56" s="62"/>
+      <c r="AM56" s="74"/>
     </row>
     <row r="57" spans="1:39" ht="14.25" customHeight="1">
       <c r="A57" s="55"/>
@@ -16538,20 +16538,20 @@
       <c r="AC57" s="17"/>
       <c r="AD57" s="17"/>
       <c r="AE57" s="6"/>
-      <c r="AF57" s="76"/>
-      <c r="AG57" s="61"/>
-      <c r="AH57" s="61"/>
-      <c r="AI57" s="61"/>
-      <c r="AJ57" s="61"/>
-      <c r="AK57" s="61"/>
-      <c r="AL57" s="61"/>
-      <c r="AM57" s="77"/>
+      <c r="AF57" s="73"/>
+      <c r="AG57" s="62"/>
+      <c r="AH57" s="62"/>
+      <c r="AI57" s="62"/>
+      <c r="AJ57" s="62"/>
+      <c r="AK57" s="62"/>
+      <c r="AL57" s="62"/>
+      <c r="AM57" s="74"/>
     </row>
     <row r="58" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="B58" s="82"/>
+      <c r="B58" s="79"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -16583,14 +16583,14 @@
       <c r="AC58" s="17"/>
       <c r="AD58" s="17"/>
       <c r="AE58" s="6"/>
-      <c r="AF58" s="76"/>
-      <c r="AG58" s="61"/>
-      <c r="AH58" s="61"/>
-      <c r="AI58" s="61"/>
-      <c r="AJ58" s="61"/>
-      <c r="AK58" s="61"/>
-      <c r="AL58" s="61"/>
-      <c r="AM58" s="77"/>
+      <c r="AF58" s="73"/>
+      <c r="AG58" s="62"/>
+      <c r="AH58" s="62"/>
+      <c r="AI58" s="62"/>
+      <c r="AJ58" s="62"/>
+      <c r="AK58" s="62"/>
+      <c r="AL58" s="62"/>
+      <c r="AM58" s="74"/>
     </row>
     <row r="59" spans="1:39" ht="18" customHeight="1">
       <c r="A59" s="55"/>
@@ -16626,20 +16626,20 @@
       <c r="AC59" s="17"/>
       <c r="AD59" s="17"/>
       <c r="AE59" s="6"/>
-      <c r="AF59" s="76"/>
-      <c r="AG59" s="61"/>
-      <c r="AH59" s="61"/>
-      <c r="AI59" s="61"/>
-      <c r="AJ59" s="61"/>
-      <c r="AK59" s="61"/>
-      <c r="AL59" s="61"/>
-      <c r="AM59" s="77"/>
+      <c r="AF59" s="73"/>
+      <c r="AG59" s="62"/>
+      <c r="AH59" s="62"/>
+      <c r="AI59" s="62"/>
+      <c r="AJ59" s="62"/>
+      <c r="AK59" s="62"/>
+      <c r="AL59" s="62"/>
+      <c r="AM59" s="74"/>
     </row>
     <row r="60" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A60" s="56" t="s">
+      <c r="A60" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="82"/>
+      <c r="B60" s="79"/>
       <c r="D60" s="22"/>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -16671,14 +16671,14 @@
       <c r="AC60" s="17"/>
       <c r="AD60" s="17"/>
       <c r="AE60" s="6"/>
-      <c r="AF60" s="76"/>
-      <c r="AG60" s="61"/>
-      <c r="AH60" s="61"/>
-      <c r="AI60" s="61"/>
-      <c r="AJ60" s="61"/>
-      <c r="AK60" s="61"/>
-      <c r="AL60" s="61"/>
-      <c r="AM60" s="77"/>
+      <c r="AF60" s="73"/>
+      <c r="AG60" s="62"/>
+      <c r="AH60" s="62"/>
+      <c r="AI60" s="62"/>
+      <c r="AJ60" s="62"/>
+      <c r="AK60" s="62"/>
+      <c r="AL60" s="62"/>
+      <c r="AM60" s="74"/>
     </row>
     <row r="61" spans="1:39" ht="18" customHeight="1">
       <c r="A61" s="55"/>
@@ -16714,20 +16714,20 @@
       <c r="AC61" s="17"/>
       <c r="AD61" s="17"/>
       <c r="AE61" s="6"/>
-      <c r="AF61" s="76"/>
-      <c r="AG61" s="61"/>
-      <c r="AH61" s="61"/>
-      <c r="AI61" s="61"/>
-      <c r="AJ61" s="61"/>
-      <c r="AK61" s="61"/>
-      <c r="AL61" s="61"/>
-      <c r="AM61" s="77"/>
+      <c r="AF61" s="73"/>
+      <c r="AG61" s="62"/>
+      <c r="AH61" s="62"/>
+      <c r="AI61" s="62"/>
+      <c r="AJ61" s="62"/>
+      <c r="AK61" s="62"/>
+      <c r="AL61" s="62"/>
+      <c r="AM61" s="74"/>
     </row>
     <row r="62" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A62" s="56" t="s">
+      <c r="A62" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="82"/>
+      <c r="B62" s="79"/>
       <c r="D62" s="22"/>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -16759,14 +16759,14 @@
       <c r="AC62" s="17"/>
       <c r="AD62" s="17"/>
       <c r="AE62" s="6"/>
-      <c r="AF62" s="76"/>
-      <c r="AG62" s="61"/>
-      <c r="AH62" s="61"/>
-      <c r="AI62" s="61"/>
-      <c r="AJ62" s="61"/>
-      <c r="AK62" s="61"/>
-      <c r="AL62" s="61"/>
-      <c r="AM62" s="77"/>
+      <c r="AF62" s="73"/>
+      <c r="AG62" s="62"/>
+      <c r="AH62" s="62"/>
+      <c r="AI62" s="62"/>
+      <c r="AJ62" s="62"/>
+      <c r="AK62" s="62"/>
+      <c r="AL62" s="62"/>
+      <c r="AM62" s="74"/>
     </row>
     <row r="63" spans="1:39" ht="18" customHeight="1">
       <c r="A63" s="55"/>
@@ -16802,20 +16802,20 @@
       <c r="AC63" s="32"/>
       <c r="AD63" s="32"/>
       <c r="AE63" s="6"/>
-      <c r="AF63" s="76"/>
-      <c r="AG63" s="61"/>
-      <c r="AH63" s="61"/>
-      <c r="AI63" s="61"/>
-      <c r="AJ63" s="61"/>
-      <c r="AK63" s="61"/>
-      <c r="AL63" s="61"/>
-      <c r="AM63" s="77"/>
+      <c r="AF63" s="73"/>
+      <c r="AG63" s="62"/>
+      <c r="AH63" s="62"/>
+      <c r="AI63" s="62"/>
+      <c r="AJ63" s="62"/>
+      <c r="AK63" s="62"/>
+      <c r="AL63" s="62"/>
+      <c r="AM63" s="74"/>
     </row>
     <row r="64" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A64" s="56" t="s">
+      <c r="A64" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="B64" s="82"/>
+      <c r="B64" s="79"/>
       <c r="D64" s="22"/>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
@@ -16847,14 +16847,14 @@
       <c r="AC64" s="32"/>
       <c r="AD64" s="32"/>
       <c r="AE64" s="6"/>
-      <c r="AF64" s="76"/>
-      <c r="AG64" s="61"/>
-      <c r="AH64" s="61"/>
-      <c r="AI64" s="61"/>
-      <c r="AJ64" s="61"/>
-      <c r="AK64" s="61"/>
-      <c r="AL64" s="61"/>
-      <c r="AM64" s="77"/>
+      <c r="AF64" s="73"/>
+      <c r="AG64" s="62"/>
+      <c r="AH64" s="62"/>
+      <c r="AI64" s="62"/>
+      <c r="AJ64" s="62"/>
+      <c r="AK64" s="62"/>
+      <c r="AL64" s="62"/>
+      <c r="AM64" s="74"/>
     </row>
     <row r="65" spans="1:39" ht="18" customHeight="1">
       <c r="A65" s="55"/>
@@ -16890,20 +16890,20 @@
       <c r="AC65" s="32"/>
       <c r="AD65" s="32"/>
       <c r="AE65" s="6"/>
-      <c r="AF65" s="76"/>
-      <c r="AG65" s="61"/>
-      <c r="AH65" s="61"/>
-      <c r="AI65" s="61"/>
-      <c r="AJ65" s="61"/>
-      <c r="AK65" s="61"/>
-      <c r="AL65" s="61"/>
-      <c r="AM65" s="77"/>
+      <c r="AF65" s="73"/>
+      <c r="AG65" s="62"/>
+      <c r="AH65" s="62"/>
+      <c r="AI65" s="62"/>
+      <c r="AJ65" s="62"/>
+      <c r="AK65" s="62"/>
+      <c r="AL65" s="62"/>
+      <c r="AM65" s="74"/>
     </row>
     <row r="66" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A66" s="56" t="s">
+      <c r="A66" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B66" s="54"/>
+      <c r="B66" s="56"/>
       <c r="D66" s="22"/>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
@@ -16935,14 +16935,14 @@
       <c r="AC66" s="17"/>
       <c r="AD66" s="17"/>
       <c r="AE66" s="6"/>
-      <c r="AF66" s="76"/>
-      <c r="AG66" s="61"/>
-      <c r="AH66" s="61"/>
-      <c r="AI66" s="61"/>
-      <c r="AJ66" s="61"/>
-      <c r="AK66" s="61"/>
-      <c r="AL66" s="61"/>
-      <c r="AM66" s="77"/>
+      <c r="AF66" s="73"/>
+      <c r="AG66" s="62"/>
+      <c r="AH66" s="62"/>
+      <c r="AI66" s="62"/>
+      <c r="AJ66" s="62"/>
+      <c r="AK66" s="62"/>
+      <c r="AL66" s="62"/>
+      <c r="AM66" s="74"/>
     </row>
     <row r="67" spans="1:39" ht="14.25" customHeight="1">
       <c r="A67" s="55"/>
@@ -16978,20 +16978,20 @@
       <c r="AC67" s="17"/>
       <c r="AD67" s="17"/>
       <c r="AE67" s="6"/>
-      <c r="AF67" s="76"/>
-      <c r="AG67" s="61"/>
-      <c r="AH67" s="61"/>
-      <c r="AI67" s="61"/>
-      <c r="AJ67" s="61"/>
-      <c r="AK67" s="61"/>
-      <c r="AL67" s="61"/>
-      <c r="AM67" s="77"/>
+      <c r="AF67" s="73"/>
+      <c r="AG67" s="62"/>
+      <c r="AH67" s="62"/>
+      <c r="AI67" s="62"/>
+      <c r="AJ67" s="62"/>
+      <c r="AK67" s="62"/>
+      <c r="AL67" s="62"/>
+      <c r="AM67" s="74"/>
     </row>
     <row r="68" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A68" s="56" t="s">
+      <c r="A68" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B68" s="54"/>
+      <c r="B68" s="56"/>
       <c r="D68" s="22"/>
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
@@ -17023,14 +17023,14 @@
       <c r="AC68" s="17"/>
       <c r="AD68" s="17"/>
       <c r="AE68" s="6"/>
-      <c r="AF68" s="76"/>
-      <c r="AG68" s="61"/>
-      <c r="AH68" s="61"/>
-      <c r="AI68" s="61"/>
-      <c r="AJ68" s="61"/>
-      <c r="AK68" s="61"/>
-      <c r="AL68" s="61"/>
-      <c r="AM68" s="77"/>
+      <c r="AF68" s="73"/>
+      <c r="AG68" s="62"/>
+      <c r="AH68" s="62"/>
+      <c r="AI68" s="62"/>
+      <c r="AJ68" s="62"/>
+      <c r="AK68" s="62"/>
+      <c r="AL68" s="62"/>
+      <c r="AM68" s="74"/>
     </row>
     <row r="69" spans="1:39" ht="14.25" customHeight="1">
       <c r="A69" s="55"/>
@@ -17066,20 +17066,20 @@
       <c r="AC69" s="17"/>
       <c r="AD69" s="17"/>
       <c r="AE69" s="6"/>
-      <c r="AF69" s="76"/>
-      <c r="AG69" s="61"/>
-      <c r="AH69" s="61"/>
-      <c r="AI69" s="61"/>
-      <c r="AJ69" s="61"/>
-      <c r="AK69" s="61"/>
-      <c r="AL69" s="61"/>
-      <c r="AM69" s="77"/>
+      <c r="AF69" s="73"/>
+      <c r="AG69" s="62"/>
+      <c r="AH69" s="62"/>
+      <c r="AI69" s="62"/>
+      <c r="AJ69" s="62"/>
+      <c r="AK69" s="62"/>
+      <c r="AL69" s="62"/>
+      <c r="AM69" s="74"/>
     </row>
     <row r="70" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A70" s="56" t="s">
+      <c r="A70" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="B70" s="54"/>
+      <c r="B70" s="56"/>
       <c r="D70" s="22"/>
       <c r="E70" s="22"/>
       <c r="F70" s="22"/>
@@ -17111,14 +17111,14 @@
       <c r="AC70" s="17"/>
       <c r="AD70" s="17"/>
       <c r="AE70" s="6"/>
-      <c r="AF70" s="76"/>
-      <c r="AG70" s="61"/>
-      <c r="AH70" s="61"/>
-      <c r="AI70" s="61"/>
-      <c r="AJ70" s="61"/>
-      <c r="AK70" s="61"/>
-      <c r="AL70" s="61"/>
-      <c r="AM70" s="77"/>
+      <c r="AF70" s="73"/>
+      <c r="AG70" s="62"/>
+      <c r="AH70" s="62"/>
+      <c r="AI70" s="62"/>
+      <c r="AJ70" s="62"/>
+      <c r="AK70" s="62"/>
+      <c r="AL70" s="62"/>
+      <c r="AM70" s="74"/>
     </row>
     <row r="71" spans="1:39" ht="14.25" customHeight="1">
       <c r="A71" s="55"/>
@@ -17154,20 +17154,20 @@
       <c r="AC71" s="17"/>
       <c r="AD71" s="17"/>
       <c r="AE71" s="6"/>
-      <c r="AF71" s="76"/>
-      <c r="AG71" s="61"/>
-      <c r="AH71" s="61"/>
-      <c r="AI71" s="61"/>
-      <c r="AJ71" s="61"/>
-      <c r="AK71" s="61"/>
-      <c r="AL71" s="61"/>
-      <c r="AM71" s="77"/>
+      <c r="AF71" s="73"/>
+      <c r="AG71" s="62"/>
+      <c r="AH71" s="62"/>
+      <c r="AI71" s="62"/>
+      <c r="AJ71" s="62"/>
+      <c r="AK71" s="62"/>
+      <c r="AL71" s="62"/>
+      <c r="AM71" s="74"/>
     </row>
     <row r="72" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A72" s="56" t="s">
+      <c r="A72" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="B72" s="54"/>
+      <c r="B72" s="56"/>
       <c r="D72" s="22"/>
       <c r="E72" s="22"/>
       <c r="F72" s="22"/>
@@ -17199,14 +17199,14 @@
       <c r="AC72" s="17"/>
       <c r="AD72" s="17"/>
       <c r="AE72" s="6"/>
-      <c r="AF72" s="78"/>
-      <c r="AG72" s="79"/>
-      <c r="AH72" s="79"/>
-      <c r="AI72" s="79"/>
-      <c r="AJ72" s="79"/>
-      <c r="AK72" s="79"/>
-      <c r="AL72" s="79"/>
-      <c r="AM72" s="80"/>
+      <c r="AF72" s="75"/>
+      <c r="AG72" s="76"/>
+      <c r="AH72" s="76"/>
+      <c r="AI72" s="76"/>
+      <c r="AJ72" s="76"/>
+      <c r="AK72" s="76"/>
+      <c r="AL72" s="76"/>
+      <c r="AM72" s="77"/>
     </row>
     <row r="73" spans="1:39" ht="14.25" customHeight="1">
       <c r="A73" s="55"/>
@@ -17254,10 +17254,10 @@
       <c r="AM73" s="38"/>
     </row>
     <row r="74" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A74" s="56" t="s">
+      <c r="A74" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B74" s="54"/>
+      <c r="B74" s="56"/>
       <c r="D74" s="22"/>
       <c r="E74" s="22"/>
       <c r="F74" s="22"/>
@@ -17346,8 +17346,8 @@
       <c r="AM75" s="38"/>
     </row>
     <row r="76" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A76" s="83"/>
-      <c r="B76" s="83"/>
+      <c r="A76" s="57"/>
+      <c r="B76" s="57"/>
       <c r="D76" s="22"/>
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
@@ -17436,8 +17436,8 @@
       <c r="AM77" s="38"/>
     </row>
     <row r="78" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A78" s="83"/>
-      <c r="B78" s="83"/>
+      <c r="A78" s="57"/>
+      <c r="B78" s="57"/>
       <c r="D78" s="22"/>
       <c r="E78" s="22"/>
       <c r="F78" s="22"/>
@@ -17524,8 +17524,8 @@
       <c r="AM79" s="38"/>
     </row>
     <row r="80" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A80" s="83"/>
-      <c r="B80" s="83"/>
+      <c r="A80" s="57"/>
+      <c r="B80" s="57"/>
       <c r="D80" s="22"/>
       <c r="E80" s="22"/>
       <c r="F80" s="22"/>
@@ -18569,29 +18569,47 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="AF3:AM37"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="AF44:AM72"/>
     <mergeCell ref="B70:B71"/>
     <mergeCell ref="B46:B47"/>
@@ -18605,51 +18623,33 @@
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="B66:B67"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="AF3:AM37"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B24:B25"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B78:B79"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="86" orientation="portrait"/>

--- a/Documents/Planification_Projet_2026.xlsx
+++ b/Documents/Planification_Projet_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fauret.SNIRW\Projet_banc_test_self\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB1C592-604F-48DE-A3FE-B57D5DBD865C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1C6CAF-3F2D-4500-8246-EA438EC82CB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10328,7 +10328,7 @@
       <c r="K49" s="40"/>
       <c r="L49" s="18"/>
       <c r="M49" s="18"/>
-      <c r="N49" s="17"/>
+      <c r="N49" s="40"/>
       <c r="O49" s="17"/>
       <c r="P49" s="25"/>
       <c r="Q49" s="26"/>

--- a/Documents/Planification_Projet_2026.xlsx
+++ b/Documents/Planification_Projet_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fauret.SNIRW\Projet_banc_test_self\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1C6CAF-3F2D-4500-8246-EA438EC82CB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D604E5EA-7480-46D8-A770-554C54C138E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2022,30 +2022,37 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2064,19 +2071,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2618,12 +2618,12 @@
       <c r="Y1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="80">
+      <c r="Z1" s="57">
         <v>2024</v>
       </c>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="82"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="59"/>
       <c r="AD1" s="6"/>
       <c r="AE1" s="4" t="s">
         <v>2</v>
@@ -2678,10 +2678,10 @@
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
       <c r="I3" s="13" t="s">
         <v>5</v>
       </c>
@@ -2746,31 +2746,31 @@
         <v>25</v>
       </c>
       <c r="AD3" s="6"/>
-      <c r="AE3" s="58" t="s">
+      <c r="AE3" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="60"/>
+      <c r="AF3" s="65"/>
+      <c r="AG3" s="65"/>
+      <c r="AH3" s="65"/>
+      <c r="AI3" s="65"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="65"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="14.25" customHeight="1">
-      <c r="D4" s="67"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
       <c r="AD4" s="6"/>
-      <c r="AE4" s="61"/>
-      <c r="AF4" s="62"/>
-      <c r="AG4" s="62"/>
-      <c r="AH4" s="62"/>
-      <c r="AI4" s="62"/>
-      <c r="AJ4" s="62"/>
-      <c r="AK4" s="62"/>
-      <c r="AL4" s="63"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="61"/>
+      <c r="AG4" s="61"/>
+      <c r="AH4" s="61"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="61"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
@@ -2811,20 +2811,20 @@
       <c r="AA5" s="16"/>
       <c r="AC5" s="16"/>
       <c r="AD5" s="6"/>
-      <c r="AE5" s="61"/>
-      <c r="AF5" s="62"/>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="62"/>
-      <c r="AI5" s="62"/>
-      <c r="AJ5" s="62"/>
-      <c r="AK5" s="62"/>
-      <c r="AL5" s="63"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="68"/>
+      <c r="B6" s="72"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -2852,14 +2852,14 @@
       <c r="AB6" s="17"/>
       <c r="AC6" s="17"/>
       <c r="AD6" s="6"/>
-      <c r="AE6" s="61"/>
-      <c r="AF6" s="62"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
-      <c r="AL6" s="63"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="61"/>
+      <c r="AG6" s="61"/>
+      <c r="AH6" s="61"/>
+      <c r="AI6" s="61"/>
+      <c r="AJ6" s="61"/>
+      <c r="AK6" s="61"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="55"/>
@@ -2891,20 +2891,20 @@
       <c r="AB7" s="17"/>
       <c r="AC7" s="17"/>
       <c r="AD7" s="6"/>
-      <c r="AE7" s="61"/>
-      <c r="AF7" s="62"/>
-      <c r="AG7" s="62"/>
-      <c r="AH7" s="62"/>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="62"/>
-      <c r="AL7" s="63"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="61"/>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="61"/>
+      <c r="AK7" s="61"/>
+      <c r="AL7" s="68"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="69"/>
+      <c r="B8" s="63"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
@@ -2932,14 +2932,14 @@
       <c r="AB8" s="17"/>
       <c r="AC8" s="17"/>
       <c r="AD8" s="6"/>
-      <c r="AE8" s="61"/>
-      <c r="AF8" s="62"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="62"/>
-      <c r="AL8" s="63"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="61"/>
+      <c r="AG8" s="61"/>
+      <c r="AH8" s="61"/>
+      <c r="AI8" s="61"/>
+      <c r="AJ8" s="61"/>
+      <c r="AK8" s="61"/>
+      <c r="AL8" s="68"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1">
       <c r="A9" s="55"/>
@@ -2971,20 +2971,20 @@
       <c r="AB9" s="17"/>
       <c r="AC9" s="17"/>
       <c r="AD9" s="6"/>
-      <c r="AE9" s="61"/>
-      <c r="AF9" s="62"/>
-      <c r="AG9" s="62"/>
-      <c r="AH9" s="62"/>
-      <c r="AI9" s="62"/>
-      <c r="AJ9" s="62"/>
-      <c r="AK9" s="62"/>
-      <c r="AL9" s="63"/>
+      <c r="AE9" s="67"/>
+      <c r="AF9" s="61"/>
+      <c r="AG9" s="61"/>
+      <c r="AH9" s="61"/>
+      <c r="AI9" s="61"/>
+      <c r="AJ9" s="61"/>
+      <c r="AK9" s="61"/>
+      <c r="AL9" s="68"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="69"/>
+      <c r="B10" s="63"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -3012,14 +3012,14 @@
       <c r="AB10" s="17"/>
       <c r="AC10" s="17"/>
       <c r="AD10" s="6"/>
-      <c r="AE10" s="61"/>
-      <c r="AF10" s="62"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="62"/>
-      <c r="AJ10" s="62"/>
-      <c r="AK10" s="62"/>
-      <c r="AL10" s="63"/>
+      <c r="AE10" s="67"/>
+      <c r="AF10" s="61"/>
+      <c r="AG10" s="61"/>
+      <c r="AH10" s="61"/>
+      <c r="AI10" s="61"/>
+      <c r="AJ10" s="61"/>
+      <c r="AK10" s="61"/>
+      <c r="AL10" s="68"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1">
       <c r="A11" s="55"/>
@@ -3051,20 +3051,20 @@
       <c r="AB11" s="17"/>
       <c r="AC11" s="17"/>
       <c r="AD11" s="6"/>
-      <c r="AE11" s="61"/>
-      <c r="AF11" s="62"/>
-      <c r="AG11" s="62"/>
-      <c r="AH11" s="62"/>
-      <c r="AI11" s="62"/>
-      <c r="AJ11" s="62"/>
-      <c r="AK11" s="62"/>
-      <c r="AL11" s="63"/>
+      <c r="AE11" s="67"/>
+      <c r="AF11" s="61"/>
+      <c r="AG11" s="61"/>
+      <c r="AH11" s="61"/>
+      <c r="AI11" s="61"/>
+      <c r="AJ11" s="61"/>
+      <c r="AK11" s="61"/>
+      <c r="AL11" s="68"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="69"/>
+      <c r="B12" s="63"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -3092,14 +3092,14 @@
       <c r="AB12" s="17"/>
       <c r="AC12" s="17"/>
       <c r="AD12" s="6"/>
-      <c r="AE12" s="61"/>
-      <c r="AF12" s="62"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
-      <c r="AL12" s="63"/>
+      <c r="AE12" s="67"/>
+      <c r="AF12" s="61"/>
+      <c r="AG12" s="61"/>
+      <c r="AH12" s="61"/>
+      <c r="AI12" s="61"/>
+      <c r="AJ12" s="61"/>
+      <c r="AK12" s="61"/>
+      <c r="AL12" s="68"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1">
       <c r="A13" s="55"/>
@@ -3131,20 +3131,20 @@
       <c r="AB13" s="17"/>
       <c r="AC13" s="17"/>
       <c r="AD13" s="6"/>
-      <c r="AE13" s="61"/>
-      <c r="AF13" s="62"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="62"/>
-      <c r="AJ13" s="62"/>
-      <c r="AK13" s="62"/>
-      <c r="AL13" s="63"/>
+      <c r="AE13" s="67"/>
+      <c r="AF13" s="61"/>
+      <c r="AG13" s="61"/>
+      <c r="AH13" s="61"/>
+      <c r="AI13" s="61"/>
+      <c r="AJ13" s="61"/>
+      <c r="AK13" s="61"/>
+      <c r="AL13" s="68"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="69"/>
+      <c r="B14" s="63"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -3172,14 +3172,14 @@
       <c r="AB14" s="17"/>
       <c r="AC14" s="17"/>
       <c r="AD14" s="6"/>
-      <c r="AE14" s="61"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="63"/>
+      <c r="AE14" s="67"/>
+      <c r="AF14" s="61"/>
+      <c r="AG14" s="61"/>
+      <c r="AH14" s="61"/>
+      <c r="AI14" s="61"/>
+      <c r="AJ14" s="61"/>
+      <c r="AK14" s="61"/>
+      <c r="AL14" s="68"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1">
       <c r="A15" s="55"/>
@@ -3211,20 +3211,20 @@
       <c r="AB15" s="17"/>
       <c r="AC15" s="17"/>
       <c r="AD15" s="6"/>
-      <c r="AE15" s="61"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="63"/>
+      <c r="AE15" s="67"/>
+      <c r="AF15" s="61"/>
+      <c r="AG15" s="61"/>
+      <c r="AH15" s="61"/>
+      <c r="AI15" s="61"/>
+      <c r="AJ15" s="61"/>
+      <c r="AK15" s="61"/>
+      <c r="AL15" s="68"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="56"/>
+      <c r="B16" s="54"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -3252,14 +3252,14 @@
       <c r="AB16" s="17"/>
       <c r="AC16" s="17"/>
       <c r="AD16" s="6"/>
-      <c r="AE16" s="61"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
-      <c r="AL16" s="63"/>
+      <c r="AE16" s="67"/>
+      <c r="AF16" s="61"/>
+      <c r="AG16" s="61"/>
+      <c r="AH16" s="61"/>
+      <c r="AI16" s="61"/>
+      <c r="AJ16" s="61"/>
+      <c r="AK16" s="61"/>
+      <c r="AL16" s="68"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
       <c r="A17" s="55"/>
@@ -3291,20 +3291,20 @@
       <c r="AB17" s="17"/>
       <c r="AC17" s="17"/>
       <c r="AD17" s="6"/>
-      <c r="AE17" s="61"/>
-      <c r="AF17" s="62"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="62"/>
-      <c r="AK17" s="62"/>
-      <c r="AL17" s="63"/>
+      <c r="AE17" s="67"/>
+      <c r="AF17" s="61"/>
+      <c r="AG17" s="61"/>
+      <c r="AH17" s="61"/>
+      <c r="AI17" s="61"/>
+      <c r="AJ17" s="61"/>
+      <c r="AK17" s="61"/>
+      <c r="AL17" s="68"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="56"/>
+      <c r="B18" s="54"/>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -3332,14 +3332,14 @@
       <c r="AB18" s="17"/>
       <c r="AC18" s="17"/>
       <c r="AD18" s="6"/>
-      <c r="AE18" s="61"/>
-      <c r="AF18" s="62"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="62"/>
-      <c r="AK18" s="62"/>
-      <c r="AL18" s="63"/>
+      <c r="AE18" s="67"/>
+      <c r="AF18" s="61"/>
+      <c r="AG18" s="61"/>
+      <c r="AH18" s="61"/>
+      <c r="AI18" s="61"/>
+      <c r="AJ18" s="61"/>
+      <c r="AK18" s="61"/>
+      <c r="AL18" s="68"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1">
       <c r="A19" s="55"/>
@@ -3371,20 +3371,20 @@
       <c r="AB19" s="17"/>
       <c r="AC19" s="17"/>
       <c r="AD19" s="6"/>
-      <c r="AE19" s="61"/>
-      <c r="AF19" s="62"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="62"/>
-      <c r="AL19" s="63"/>
+      <c r="AE19" s="67"/>
+      <c r="AF19" s="61"/>
+      <c r="AG19" s="61"/>
+      <c r="AH19" s="61"/>
+      <c r="AI19" s="61"/>
+      <c r="AJ19" s="61"/>
+      <c r="AK19" s="61"/>
+      <c r="AL19" s="68"/>
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="56"/>
+      <c r="B20" s="54"/>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -3412,14 +3412,14 @@
       <c r="AB20" s="17"/>
       <c r="AC20" s="17"/>
       <c r="AD20" s="6"/>
-      <c r="AE20" s="61"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="62"/>
-      <c r="AL20" s="63"/>
+      <c r="AE20" s="67"/>
+      <c r="AF20" s="61"/>
+      <c r="AG20" s="61"/>
+      <c r="AH20" s="61"/>
+      <c r="AI20" s="61"/>
+      <c r="AJ20" s="61"/>
+      <c r="AK20" s="61"/>
+      <c r="AL20" s="68"/>
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
       <c r="A21" s="55"/>
@@ -3451,20 +3451,20 @@
       <c r="AB21" s="17"/>
       <c r="AC21" s="17"/>
       <c r="AD21" s="6"/>
-      <c r="AE21" s="61"/>
-      <c r="AF21" s="62"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="62"/>
-      <c r="AJ21" s="62"/>
-      <c r="AK21" s="62"/>
-      <c r="AL21" s="63"/>
+      <c r="AE21" s="67"/>
+      <c r="AF21" s="61"/>
+      <c r="AG21" s="61"/>
+      <c r="AH21" s="61"/>
+      <c r="AI21" s="61"/>
+      <c r="AJ21" s="61"/>
+      <c r="AK21" s="61"/>
+      <c r="AL21" s="68"/>
     </row>
     <row r="22" spans="1:38" ht="15" customHeight="1">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="56"/>
+      <c r="B22" s="54"/>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -3492,14 +3492,14 @@
       <c r="AB22" s="17"/>
       <c r="AC22" s="17"/>
       <c r="AD22" s="6"/>
-      <c r="AE22" s="61"/>
-      <c r="AF22" s="62"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="62"/>
-      <c r="AL22" s="63"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="61"/>
+      <c r="AG22" s="61"/>
+      <c r="AH22" s="61"/>
+      <c r="AI22" s="61"/>
+      <c r="AJ22" s="61"/>
+      <c r="AK22" s="61"/>
+      <c r="AL22" s="68"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
       <c r="A23" s="55"/>
@@ -3531,20 +3531,20 @@
       <c r="AB23" s="17"/>
       <c r="AC23" s="17"/>
       <c r="AD23" s="6"/>
-      <c r="AE23" s="61"/>
-      <c r="AF23" s="62"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="62"/>
-      <c r="AL23" s="63"/>
+      <c r="AE23" s="67"/>
+      <c r="AF23" s="61"/>
+      <c r="AG23" s="61"/>
+      <c r="AH23" s="61"/>
+      <c r="AI23" s="61"/>
+      <c r="AJ23" s="61"/>
+      <c r="AK23" s="61"/>
+      <c r="AL23" s="68"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="56"/>
+      <c r="B24" s="54"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -3572,14 +3572,14 @@
       <c r="AB24" s="17"/>
       <c r="AC24" s="17"/>
       <c r="AD24" s="6"/>
-      <c r="AE24" s="61"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="62"/>
-      <c r="AJ24" s="62"/>
-      <c r="AK24" s="62"/>
-      <c r="AL24" s="63"/>
+      <c r="AE24" s="67"/>
+      <c r="AF24" s="61"/>
+      <c r="AG24" s="61"/>
+      <c r="AH24" s="61"/>
+      <c r="AI24" s="61"/>
+      <c r="AJ24" s="61"/>
+      <c r="AK24" s="61"/>
+      <c r="AL24" s="68"/>
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" s="55"/>
@@ -3611,20 +3611,20 @@
       <c r="AB25" s="17"/>
       <c r="AC25" s="17"/>
       <c r="AD25" s="6"/>
-      <c r="AE25" s="61"/>
-      <c r="AF25" s="62"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
-      <c r="AK25" s="62"/>
-      <c r="AL25" s="63"/>
+      <c r="AE25" s="67"/>
+      <c r="AF25" s="61"/>
+      <c r="AG25" s="61"/>
+      <c r="AH25" s="61"/>
+      <c r="AI25" s="61"/>
+      <c r="AJ25" s="61"/>
+      <c r="AK25" s="61"/>
+      <c r="AL25" s="68"/>
     </row>
     <row r="26" spans="1:38" ht="15" customHeight="1">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="56"/>
+      <c r="B26" s="54"/>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -3652,14 +3652,14 @@
       <c r="AB26" s="17"/>
       <c r="AC26" s="17"/>
       <c r="AD26" s="6"/>
-      <c r="AE26" s="61"/>
-      <c r="AF26" s="62"/>
-      <c r="AG26" s="62"/>
-      <c r="AH26" s="62"/>
-      <c r="AI26" s="62"/>
-      <c r="AJ26" s="62"/>
-      <c r="AK26" s="62"/>
-      <c r="AL26" s="63"/>
+      <c r="AE26" s="67"/>
+      <c r="AF26" s="61"/>
+      <c r="AG26" s="61"/>
+      <c r="AH26" s="61"/>
+      <c r="AI26" s="61"/>
+      <c r="AJ26" s="61"/>
+      <c r="AK26" s="61"/>
+      <c r="AL26" s="68"/>
     </row>
     <row r="27" spans="1:38" ht="15" customHeight="1">
       <c r="A27" s="55"/>
@@ -3691,20 +3691,20 @@
       <c r="AB27" s="17"/>
       <c r="AC27" s="17"/>
       <c r="AD27" s="6"/>
-      <c r="AE27" s="61"/>
-      <c r="AF27" s="62"/>
-      <c r="AG27" s="62"/>
-      <c r="AH27" s="62"/>
-      <c r="AI27" s="62"/>
-      <c r="AJ27" s="62"/>
-      <c r="AK27" s="62"/>
-      <c r="AL27" s="63"/>
+      <c r="AE27" s="67"/>
+      <c r="AF27" s="61"/>
+      <c r="AG27" s="61"/>
+      <c r="AH27" s="61"/>
+      <c r="AI27" s="61"/>
+      <c r="AJ27" s="61"/>
+      <c r="AK27" s="61"/>
+      <c r="AL27" s="68"/>
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="56"/>
+      <c r="B28" s="54"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -3732,14 +3732,14 @@
       <c r="AB28" s="17"/>
       <c r="AC28" s="17"/>
       <c r="AD28" s="6"/>
-      <c r="AE28" s="61"/>
-      <c r="AF28" s="62"/>
-      <c r="AG28" s="62"/>
-      <c r="AH28" s="62"/>
-      <c r="AI28" s="62"/>
-      <c r="AJ28" s="62"/>
-      <c r="AK28" s="62"/>
-      <c r="AL28" s="63"/>
+      <c r="AE28" s="67"/>
+      <c r="AF28" s="61"/>
+      <c r="AG28" s="61"/>
+      <c r="AH28" s="61"/>
+      <c r="AI28" s="61"/>
+      <c r="AJ28" s="61"/>
+      <c r="AK28" s="61"/>
+      <c r="AL28" s="68"/>
     </row>
     <row r="29" spans="1:38" ht="15" customHeight="1">
       <c r="A29" s="55"/>
@@ -3771,20 +3771,20 @@
       <c r="AB29" s="17"/>
       <c r="AC29" s="17"/>
       <c r="AD29" s="6"/>
-      <c r="AE29" s="61"/>
-      <c r="AF29" s="62"/>
-      <c r="AG29" s="62"/>
-      <c r="AH29" s="62"/>
-      <c r="AI29" s="62"/>
-      <c r="AJ29" s="62"/>
-      <c r="AK29" s="62"/>
-      <c r="AL29" s="63"/>
+      <c r="AE29" s="67"/>
+      <c r="AF29" s="61"/>
+      <c r="AG29" s="61"/>
+      <c r="AH29" s="61"/>
+      <c r="AI29" s="61"/>
+      <c r="AJ29" s="61"/>
+      <c r="AK29" s="61"/>
+      <c r="AL29" s="68"/>
     </row>
     <row r="30" spans="1:38" ht="15" customHeight="1">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="56"/>
+      <c r="B30" s="54"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -3812,14 +3812,14 @@
       <c r="AB30" s="17"/>
       <c r="AC30" s="17"/>
       <c r="AD30" s="6"/>
-      <c r="AE30" s="61"/>
-      <c r="AF30" s="62"/>
-      <c r="AG30" s="62"/>
-      <c r="AH30" s="62"/>
-      <c r="AI30" s="62"/>
-      <c r="AJ30" s="62"/>
-      <c r="AK30" s="62"/>
-      <c r="AL30" s="63"/>
+      <c r="AE30" s="67"/>
+      <c r="AF30" s="61"/>
+      <c r="AG30" s="61"/>
+      <c r="AH30" s="61"/>
+      <c r="AI30" s="61"/>
+      <c r="AJ30" s="61"/>
+      <c r="AK30" s="61"/>
+      <c r="AL30" s="68"/>
     </row>
     <row r="31" spans="1:38" ht="15" customHeight="1">
       <c r="A31" s="55"/>
@@ -3851,20 +3851,20 @@
       <c r="AB31" s="17"/>
       <c r="AC31" s="17"/>
       <c r="AD31" s="6"/>
-      <c r="AE31" s="61"/>
-      <c r="AF31" s="62"/>
-      <c r="AG31" s="62"/>
-      <c r="AH31" s="62"/>
-      <c r="AI31" s="62"/>
-      <c r="AJ31" s="62"/>
-      <c r="AK31" s="62"/>
-      <c r="AL31" s="63"/>
+      <c r="AE31" s="67"/>
+      <c r="AF31" s="61"/>
+      <c r="AG31" s="61"/>
+      <c r="AH31" s="61"/>
+      <c r="AI31" s="61"/>
+      <c r="AJ31" s="61"/>
+      <c r="AK31" s="61"/>
+      <c r="AL31" s="68"/>
     </row>
     <row r="32" spans="1:38" ht="15" customHeight="1">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="78"/>
+      <c r="B32" s="81"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -3892,14 +3892,14 @@
       <c r="AB32" s="17"/>
       <c r="AC32" s="17"/>
       <c r="AD32" s="6"/>
-      <c r="AE32" s="61"/>
-      <c r="AF32" s="62"/>
-      <c r="AG32" s="62"/>
-      <c r="AH32" s="62"/>
-      <c r="AI32" s="62"/>
-      <c r="AJ32" s="62"/>
-      <c r="AK32" s="62"/>
-      <c r="AL32" s="63"/>
+      <c r="AE32" s="67"/>
+      <c r="AF32" s="61"/>
+      <c r="AG32" s="61"/>
+      <c r="AH32" s="61"/>
+      <c r="AI32" s="61"/>
+      <c r="AJ32" s="61"/>
+      <c r="AK32" s="61"/>
+      <c r="AL32" s="68"/>
     </row>
     <row r="33" spans="1:38" ht="15" customHeight="1">
       <c r="A33" s="55"/>
@@ -3931,20 +3931,20 @@
       <c r="AB33" s="17"/>
       <c r="AC33" s="17"/>
       <c r="AD33" s="6"/>
-      <c r="AE33" s="61"/>
-      <c r="AF33" s="62"/>
-      <c r="AG33" s="62"/>
-      <c r="AH33" s="62"/>
-      <c r="AI33" s="62"/>
-      <c r="AJ33" s="62"/>
-      <c r="AK33" s="62"/>
-      <c r="AL33" s="63"/>
+      <c r="AE33" s="67"/>
+      <c r="AF33" s="61"/>
+      <c r="AG33" s="61"/>
+      <c r="AH33" s="61"/>
+      <c r="AI33" s="61"/>
+      <c r="AJ33" s="61"/>
+      <c r="AK33" s="61"/>
+      <c r="AL33" s="68"/>
     </row>
     <row r="34" spans="1:38" ht="15" customHeight="1">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="79"/>
+      <c r="B34" s="82"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -3972,14 +3972,14 @@
       <c r="AB34" s="17"/>
       <c r="AC34" s="17"/>
       <c r="AD34" s="6"/>
-      <c r="AE34" s="61"/>
-      <c r="AF34" s="62"/>
-      <c r="AG34" s="62"/>
-      <c r="AH34" s="62"/>
-      <c r="AI34" s="62"/>
-      <c r="AJ34" s="62"/>
-      <c r="AK34" s="62"/>
-      <c r="AL34" s="63"/>
+      <c r="AE34" s="67"/>
+      <c r="AF34" s="61"/>
+      <c r="AG34" s="61"/>
+      <c r="AH34" s="61"/>
+      <c r="AI34" s="61"/>
+      <c r="AJ34" s="61"/>
+      <c r="AK34" s="61"/>
+      <c r="AL34" s="68"/>
     </row>
     <row r="35" spans="1:38" ht="15" customHeight="1">
       <c r="A35" s="55"/>
@@ -4011,20 +4011,20 @@
       <c r="AB35" s="17"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="6"/>
-      <c r="AE35" s="64"/>
-      <c r="AF35" s="65"/>
-      <c r="AG35" s="65"/>
-      <c r="AH35" s="65"/>
-      <c r="AI35" s="65"/>
-      <c r="AJ35" s="65"/>
-      <c r="AK35" s="65"/>
-      <c r="AL35" s="66"/>
+      <c r="AE35" s="69"/>
+      <c r="AF35" s="70"/>
+      <c r="AG35" s="70"/>
+      <c r="AH35" s="70"/>
+      <c r="AI35" s="70"/>
+      <c r="AJ35" s="70"/>
+      <c r="AK35" s="70"/>
+      <c r="AL35" s="71"/>
     </row>
     <row r="36" spans="1:38" ht="15" customHeight="1">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="56"/>
+      <c r="B36" s="54"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -4101,10 +4101,10 @@
       <c r="AL37" s="6"/>
     </row>
     <row r="38" spans="1:38" ht="15" customHeight="1">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="56"/>
+      <c r="B38" s="54"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -4171,22 +4171,22 @@
       <c r="AB39" s="17"/>
       <c r="AC39" s="17"/>
       <c r="AD39" s="6"/>
-      <c r="AE39" s="70" t="s">
+      <c r="AE39" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="AF39" s="71"/>
-      <c r="AG39" s="71"/>
-      <c r="AH39" s="71"/>
-      <c r="AI39" s="71"/>
-      <c r="AJ39" s="71"/>
-      <c r="AK39" s="71"/>
-      <c r="AL39" s="72"/>
+      <c r="AF39" s="74"/>
+      <c r="AG39" s="74"/>
+      <c r="AH39" s="74"/>
+      <c r="AI39" s="74"/>
+      <c r="AJ39" s="74"/>
+      <c r="AK39" s="74"/>
+      <c r="AL39" s="75"/>
     </row>
     <row r="40" spans="1:38" ht="15" customHeight="1">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="56"/>
+      <c r="B40" s="54"/>
       <c r="D40" s="22"/>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -4214,14 +4214,14 @@
       <c r="AB40" s="17"/>
       <c r="AC40" s="17"/>
       <c r="AD40" s="6"/>
-      <c r="AE40" s="73"/>
-      <c r="AF40" s="62"/>
-      <c r="AG40" s="62"/>
-      <c r="AH40" s="62"/>
-      <c r="AI40" s="62"/>
-      <c r="AJ40" s="62"/>
-      <c r="AK40" s="62"/>
-      <c r="AL40" s="74"/>
+      <c r="AE40" s="76"/>
+      <c r="AF40" s="61"/>
+      <c r="AG40" s="61"/>
+      <c r="AH40" s="61"/>
+      <c r="AI40" s="61"/>
+      <c r="AJ40" s="61"/>
+      <c r="AK40" s="61"/>
+      <c r="AL40" s="77"/>
     </row>
     <row r="41" spans="1:38" ht="15" customHeight="1">
       <c r="A41" s="55"/>
@@ -4253,20 +4253,20 @@
       <c r="AB41" s="17"/>
       <c r="AC41" s="17"/>
       <c r="AD41" s="6"/>
-      <c r="AE41" s="73"/>
-      <c r="AF41" s="62"/>
-      <c r="AG41" s="62"/>
-      <c r="AH41" s="62"/>
-      <c r="AI41" s="62"/>
-      <c r="AJ41" s="62"/>
-      <c r="AK41" s="62"/>
-      <c r="AL41" s="74"/>
+      <c r="AE41" s="76"/>
+      <c r="AF41" s="61"/>
+      <c r="AG41" s="61"/>
+      <c r="AH41" s="61"/>
+      <c r="AI41" s="61"/>
+      <c r="AJ41" s="61"/>
+      <c r="AK41" s="61"/>
+      <c r="AL41" s="77"/>
     </row>
     <row r="42" spans="1:38" ht="15" customHeight="1">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="56"/>
+      <c r="B42" s="54"/>
       <c r="D42" s="22"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -4294,14 +4294,14 @@
       <c r="AB42" s="17"/>
       <c r="AC42" s="17"/>
       <c r="AD42" s="6"/>
-      <c r="AE42" s="73"/>
-      <c r="AF42" s="62"/>
-      <c r="AG42" s="62"/>
-      <c r="AH42" s="62"/>
-      <c r="AI42" s="62"/>
-      <c r="AJ42" s="62"/>
-      <c r="AK42" s="62"/>
-      <c r="AL42" s="74"/>
+      <c r="AE42" s="76"/>
+      <c r="AF42" s="61"/>
+      <c r="AG42" s="61"/>
+      <c r="AH42" s="61"/>
+      <c r="AI42" s="61"/>
+      <c r="AJ42" s="61"/>
+      <c r="AK42" s="61"/>
+      <c r="AL42" s="77"/>
     </row>
     <row r="43" spans="1:38" ht="15" customHeight="1">
       <c r="A43" s="55"/>
@@ -4333,20 +4333,20 @@
       <c r="AB43" s="17"/>
       <c r="AC43" s="17"/>
       <c r="AD43" s="6"/>
-      <c r="AE43" s="73"/>
-      <c r="AF43" s="62"/>
-      <c r="AG43" s="62"/>
-      <c r="AH43" s="62"/>
-      <c r="AI43" s="62"/>
-      <c r="AJ43" s="62"/>
-      <c r="AK43" s="62"/>
-      <c r="AL43" s="74"/>
+      <c r="AE43" s="76"/>
+      <c r="AF43" s="61"/>
+      <c r="AG43" s="61"/>
+      <c r="AH43" s="61"/>
+      <c r="AI43" s="61"/>
+      <c r="AJ43" s="61"/>
+      <c r="AK43" s="61"/>
+      <c r="AL43" s="77"/>
     </row>
     <row r="44" spans="1:38" ht="15" customHeight="1">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="83"/>
+      <c r="B44" s="62"/>
       <c r="D44" s="22"/>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -4374,14 +4374,14 @@
       <c r="AB44" s="17"/>
       <c r="AC44" s="17"/>
       <c r="AD44" s="6"/>
-      <c r="AE44" s="73"/>
-      <c r="AF44" s="62"/>
-      <c r="AG44" s="62"/>
-      <c r="AH44" s="62"/>
-      <c r="AI44" s="62"/>
-      <c r="AJ44" s="62"/>
-      <c r="AK44" s="62"/>
-      <c r="AL44" s="74"/>
+      <c r="AE44" s="76"/>
+      <c r="AF44" s="61"/>
+      <c r="AG44" s="61"/>
+      <c r="AH44" s="61"/>
+      <c r="AI44" s="61"/>
+      <c r="AJ44" s="61"/>
+      <c r="AK44" s="61"/>
+      <c r="AL44" s="77"/>
     </row>
     <row r="45" spans="1:38" ht="15" customHeight="1">
       <c r="A45" s="55"/>
@@ -4413,20 +4413,20 @@
       <c r="AB45" s="17"/>
       <c r="AC45" s="17"/>
       <c r="AD45" s="6"/>
-      <c r="AE45" s="73"/>
-      <c r="AF45" s="62"/>
-      <c r="AG45" s="62"/>
-      <c r="AH45" s="62"/>
-      <c r="AI45" s="62"/>
-      <c r="AJ45" s="62"/>
-      <c r="AK45" s="62"/>
-      <c r="AL45" s="74"/>
+      <c r="AE45" s="76"/>
+      <c r="AF45" s="61"/>
+      <c r="AG45" s="61"/>
+      <c r="AH45" s="61"/>
+      <c r="AI45" s="61"/>
+      <c r="AJ45" s="61"/>
+      <c r="AK45" s="61"/>
+      <c r="AL45" s="77"/>
     </row>
     <row r="46" spans="1:38" ht="15" customHeight="1">
-      <c r="A46" s="54" t="s">
+      <c r="A46" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="56"/>
+      <c r="B46" s="54"/>
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -4454,14 +4454,14 @@
       <c r="AB46" s="17"/>
       <c r="AC46" s="17"/>
       <c r="AD46" s="6"/>
-      <c r="AE46" s="73"/>
-      <c r="AF46" s="62"/>
-      <c r="AG46" s="62"/>
-      <c r="AH46" s="62"/>
-      <c r="AI46" s="62"/>
-      <c r="AJ46" s="62"/>
-      <c r="AK46" s="62"/>
-      <c r="AL46" s="74"/>
+      <c r="AE46" s="76"/>
+      <c r="AF46" s="61"/>
+      <c r="AG46" s="61"/>
+      <c r="AH46" s="61"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="61"/>
+      <c r="AK46" s="61"/>
+      <c r="AL46" s="77"/>
     </row>
     <row r="47" spans="1:38" ht="15" customHeight="1">
       <c r="A47" s="55"/>
@@ -4493,20 +4493,20 @@
       <c r="AB47" s="17"/>
       <c r="AC47" s="17"/>
       <c r="AD47" s="6"/>
-      <c r="AE47" s="73"/>
-      <c r="AF47" s="62"/>
-      <c r="AG47" s="62"/>
-      <c r="AH47" s="62"/>
-      <c r="AI47" s="62"/>
-      <c r="AJ47" s="62"/>
-      <c r="AK47" s="62"/>
-      <c r="AL47" s="74"/>
+      <c r="AE47" s="76"/>
+      <c r="AF47" s="61"/>
+      <c r="AG47" s="61"/>
+      <c r="AH47" s="61"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="61"/>
+      <c r="AL47" s="77"/>
     </row>
     <row r="48" spans="1:38" ht="15" customHeight="1">
-      <c r="A48" s="54" t="s">
+      <c r="A48" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="56"/>
+      <c r="B48" s="54"/>
       <c r="D48" s="22"/>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -4534,14 +4534,14 @@
       <c r="AB48" s="17"/>
       <c r="AC48" s="17"/>
       <c r="AD48" s="6"/>
-      <c r="AE48" s="73"/>
-      <c r="AF48" s="62"/>
-      <c r="AG48" s="62"/>
-      <c r="AH48" s="62"/>
-      <c r="AI48" s="62"/>
-      <c r="AJ48" s="62"/>
-      <c r="AK48" s="62"/>
-      <c r="AL48" s="74"/>
+      <c r="AE48" s="76"/>
+      <c r="AF48" s="61"/>
+      <c r="AG48" s="61"/>
+      <c r="AH48" s="61"/>
+      <c r="AI48" s="61"/>
+      <c r="AJ48" s="61"/>
+      <c r="AK48" s="61"/>
+      <c r="AL48" s="77"/>
     </row>
     <row r="49" spans="1:38" ht="15" customHeight="1">
       <c r="A49" s="55"/>
@@ -4573,20 +4573,20 @@
       <c r="AB49" s="17"/>
       <c r="AC49" s="17"/>
       <c r="AD49" s="6"/>
-      <c r="AE49" s="73"/>
-      <c r="AF49" s="62"/>
-      <c r="AG49" s="62"/>
-      <c r="AH49" s="62"/>
-      <c r="AI49" s="62"/>
-      <c r="AJ49" s="62"/>
-      <c r="AK49" s="62"/>
-      <c r="AL49" s="74"/>
+      <c r="AE49" s="76"/>
+      <c r="AF49" s="61"/>
+      <c r="AG49" s="61"/>
+      <c r="AH49" s="61"/>
+      <c r="AI49" s="61"/>
+      <c r="AJ49" s="61"/>
+      <c r="AK49" s="61"/>
+      <c r="AL49" s="77"/>
     </row>
     <row r="50" spans="1:38" ht="15" customHeight="1">
-      <c r="A50" s="54" t="s">
+      <c r="A50" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="56"/>
+      <c r="B50" s="54"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -4614,14 +4614,14 @@
       <c r="AB50" s="17"/>
       <c r="AC50" s="17"/>
       <c r="AD50" s="6"/>
-      <c r="AE50" s="73"/>
-      <c r="AF50" s="62"/>
-      <c r="AG50" s="62"/>
-      <c r="AH50" s="62"/>
-      <c r="AI50" s="62"/>
-      <c r="AJ50" s="62"/>
-      <c r="AK50" s="62"/>
-      <c r="AL50" s="74"/>
+      <c r="AE50" s="76"/>
+      <c r="AF50" s="61"/>
+      <c r="AG50" s="61"/>
+      <c r="AH50" s="61"/>
+      <c r="AI50" s="61"/>
+      <c r="AJ50" s="61"/>
+      <c r="AK50" s="61"/>
+      <c r="AL50" s="77"/>
     </row>
     <row r="51" spans="1:38" ht="15" customHeight="1">
       <c r="A51" s="55"/>
@@ -4653,20 +4653,20 @@
       <c r="AB51" s="17"/>
       <c r="AC51" s="17"/>
       <c r="AD51" s="6"/>
-      <c r="AE51" s="73"/>
-      <c r="AF51" s="62"/>
-      <c r="AG51" s="62"/>
-      <c r="AH51" s="62"/>
-      <c r="AI51" s="62"/>
-      <c r="AJ51" s="62"/>
-      <c r="AK51" s="62"/>
-      <c r="AL51" s="74"/>
+      <c r="AE51" s="76"/>
+      <c r="AF51" s="61"/>
+      <c r="AG51" s="61"/>
+      <c r="AH51" s="61"/>
+      <c r="AI51" s="61"/>
+      <c r="AJ51" s="61"/>
+      <c r="AK51" s="61"/>
+      <c r="AL51" s="77"/>
     </row>
     <row r="52" spans="1:38" ht="15" customHeight="1">
-      <c r="A52" s="54" t="s">
+      <c r="A52" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="56"/>
+      <c r="B52" s="54"/>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
@@ -4694,14 +4694,14 @@
       <c r="AB52" s="17"/>
       <c r="AC52" s="17"/>
       <c r="AD52" s="6"/>
-      <c r="AE52" s="73"/>
-      <c r="AF52" s="62"/>
-      <c r="AG52" s="62"/>
-      <c r="AH52" s="62"/>
-      <c r="AI52" s="62"/>
-      <c r="AJ52" s="62"/>
-      <c r="AK52" s="62"/>
-      <c r="AL52" s="74"/>
+      <c r="AE52" s="76"/>
+      <c r="AF52" s="61"/>
+      <c r="AG52" s="61"/>
+      <c r="AH52" s="61"/>
+      <c r="AI52" s="61"/>
+      <c r="AJ52" s="61"/>
+      <c r="AK52" s="61"/>
+      <c r="AL52" s="77"/>
     </row>
     <row r="53" spans="1:38" ht="15" customHeight="1">
       <c r="A53" s="55"/>
@@ -4733,20 +4733,20 @@
       <c r="AB53" s="17"/>
       <c r="AC53" s="17"/>
       <c r="AD53" s="6"/>
-      <c r="AE53" s="73"/>
-      <c r="AF53" s="62"/>
-      <c r="AG53" s="62"/>
-      <c r="AH53" s="62"/>
-      <c r="AI53" s="62"/>
-      <c r="AJ53" s="62"/>
-      <c r="AK53" s="62"/>
-      <c r="AL53" s="74"/>
+      <c r="AE53" s="76"/>
+      <c r="AF53" s="61"/>
+      <c r="AG53" s="61"/>
+      <c r="AH53" s="61"/>
+      <c r="AI53" s="61"/>
+      <c r="AJ53" s="61"/>
+      <c r="AK53" s="61"/>
+      <c r="AL53" s="77"/>
     </row>
     <row r="54" spans="1:38" ht="15" customHeight="1">
-      <c r="A54" s="54" t="s">
+      <c r="A54" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="56"/>
+      <c r="B54" s="54"/>
       <c r="D54" s="22"/>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -4774,14 +4774,14 @@
       <c r="AB54" s="17"/>
       <c r="AC54" s="17"/>
       <c r="AD54" s="6"/>
-      <c r="AE54" s="73"/>
-      <c r="AF54" s="62"/>
-      <c r="AG54" s="62"/>
-      <c r="AH54" s="62"/>
-      <c r="AI54" s="62"/>
-      <c r="AJ54" s="62"/>
-      <c r="AK54" s="62"/>
-      <c r="AL54" s="74"/>
+      <c r="AE54" s="76"/>
+      <c r="AF54" s="61"/>
+      <c r="AG54" s="61"/>
+      <c r="AH54" s="61"/>
+      <c r="AI54" s="61"/>
+      <c r="AJ54" s="61"/>
+      <c r="AK54" s="61"/>
+      <c r="AL54" s="77"/>
     </row>
     <row r="55" spans="1:38" ht="15" customHeight="1">
       <c r="A55" s="55"/>
@@ -4813,20 +4813,20 @@
       <c r="AB55" s="17"/>
       <c r="AC55" s="17"/>
       <c r="AD55" s="6"/>
-      <c r="AE55" s="73"/>
-      <c r="AF55" s="62"/>
-      <c r="AG55" s="62"/>
-      <c r="AH55" s="62"/>
-      <c r="AI55" s="62"/>
-      <c r="AJ55" s="62"/>
-      <c r="AK55" s="62"/>
-      <c r="AL55" s="74"/>
+      <c r="AE55" s="76"/>
+      <c r="AF55" s="61"/>
+      <c r="AG55" s="61"/>
+      <c r="AH55" s="61"/>
+      <c r="AI55" s="61"/>
+      <c r="AJ55" s="61"/>
+      <c r="AK55" s="61"/>
+      <c r="AL55" s="77"/>
     </row>
     <row r="56" spans="1:38" ht="15" customHeight="1">
-      <c r="A56" s="54" t="s">
+      <c r="A56" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="56"/>
+      <c r="B56" s="54"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -4854,14 +4854,14 @@
       <c r="AB56" s="17"/>
       <c r="AC56" s="17"/>
       <c r="AD56" s="6"/>
-      <c r="AE56" s="75"/>
-      <c r="AF56" s="76"/>
-      <c r="AG56" s="76"/>
-      <c r="AH56" s="76"/>
-      <c r="AI56" s="76"/>
-      <c r="AJ56" s="76"/>
-      <c r="AK56" s="76"/>
-      <c r="AL56" s="77"/>
+      <c r="AE56" s="78"/>
+      <c r="AF56" s="79"/>
+      <c r="AG56" s="79"/>
+      <c r="AH56" s="79"/>
+      <c r="AI56" s="79"/>
+      <c r="AJ56" s="79"/>
+      <c r="AK56" s="79"/>
+      <c r="AL56" s="80"/>
     </row>
     <row r="57" spans="1:38" ht="15" customHeight="1">
       <c r="A57" s="55"/>
@@ -4905,10 +4905,10 @@
       <c r="AL57" s="38"/>
     </row>
     <row r="58" spans="1:38" ht="15" customHeight="1">
-      <c r="A58" s="54" t="s">
+      <c r="A58" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="56"/>
+      <c r="B58" s="54"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -4989,8 +4989,8 @@
       <c r="AL59" s="38"/>
     </row>
     <row r="60" spans="1:38" ht="15" customHeight="1">
-      <c r="A60" s="57"/>
-      <c r="B60" s="57"/>
+      <c r="A60" s="83"/>
+      <c r="B60" s="83"/>
       <c r="D60" s="22"/>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -5071,8 +5071,8 @@
       <c r="AL61" s="38"/>
     </row>
     <row r="62" spans="1:38" ht="15" customHeight="1">
-      <c r="A62" s="57"/>
-      <c r="B62" s="57"/>
+      <c r="A62" s="83"/>
+      <c r="B62" s="83"/>
       <c r="D62" s="22"/>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -5151,8 +5151,8 @@
       <c r="AL63" s="38"/>
     </row>
     <row r="64" spans="1:38" ht="15" customHeight="1">
-      <c r="A64" s="57"/>
-      <c r="B64" s="57"/>
+      <c r="A64" s="83"/>
+      <c r="B64" s="83"/>
       <c r="D64" s="22"/>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
@@ -8071,29 +8071,32 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B60:B61"/>
     <mergeCell ref="AE3:AL35"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="B6:B7"/>
@@ -8110,32 +8113,29 @@
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A48:A49"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="86" orientation="portrait"/>
@@ -8192,12 +8192,12 @@
       <c r="X1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="80">
+      <c r="Y1" s="57">
         <v>2026</v>
       </c>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="82"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="59"/>
       <c r="AC1" s="6"/>
       <c r="AD1" s="4" t="s">
         <v>2</v>
@@ -8316,16 +8316,16 @@
         <v>25</v>
       </c>
       <c r="AC3" s="6"/>
-      <c r="AD3" s="58" t="s">
+      <c r="AD3" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="60"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="65"/>
+      <c r="AG3" s="65"/>
+      <c r="AH3" s="65"/>
+      <c r="AI3" s="65"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="66"/>
     </row>
     <row r="4" spans="1:37" ht="14.25" customHeight="1">
       <c r="F4" s="12"/>
@@ -8351,14 +8351,14 @@
       <c r="AA4" s="12"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="6"/>
-      <c r="AD4" s="61"/>
-      <c r="AE4" s="62"/>
-      <c r="AF4" s="62"/>
-      <c r="AG4" s="62"/>
-      <c r="AH4" s="62"/>
-      <c r="AI4" s="62"/>
-      <c r="AJ4" s="62"/>
-      <c r="AK4" s="63"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="61"/>
+      <c r="AG4" s="61"/>
+      <c r="AH4" s="61"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="68"/>
     </row>
     <row r="5" spans="1:37" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
@@ -8404,17 +8404,17 @@
       <c r="AA5" s="12"/>
       <c r="AB5" s="16"/>
       <c r="AC5" s="6"/>
-      <c r="AD5" s="61"/>
-      <c r="AE5" s="62"/>
-      <c r="AF5" s="62"/>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="62"/>
-      <c r="AI5" s="62"/>
-      <c r="AJ5" s="62"/>
-      <c r="AK5" s="63"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="68"/>
     </row>
     <row r="6" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="56" t="s">
         <v>63</v>
       </c>
       <c r="B6" s="86" t="s">
@@ -8449,14 +8449,14 @@
       <c r="AA6" s="17"/>
       <c r="AB6" s="17"/>
       <c r="AC6" s="6"/>
-      <c r="AD6" s="61"/>
-      <c r="AE6" s="62"/>
-      <c r="AF6" s="62"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="63"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="61"/>
+      <c r="AF6" s="61"/>
+      <c r="AG6" s="61"/>
+      <c r="AH6" s="61"/>
+      <c r="AI6" s="61"/>
+      <c r="AJ6" s="61"/>
+      <c r="AK6" s="68"/>
     </row>
     <row r="7" spans="1:37" ht="14.25" customHeight="1">
       <c r="A7" s="55"/>
@@ -8496,20 +8496,20 @@
       <c r="AA7" s="17"/>
       <c r="AB7" s="17"/>
       <c r="AC7" s="6"/>
-      <c r="AD7" s="61"/>
-      <c r="AE7" s="62"/>
-      <c r="AF7" s="62"/>
-      <c r="AG7" s="62"/>
-      <c r="AH7" s="62"/>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="63"/>
+      <c r="AD7" s="67"/>
+      <c r="AE7" s="61"/>
+      <c r="AF7" s="61"/>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="61"/>
+      <c r="AK7" s="68"/>
     </row>
     <row r="8" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="84" t="s">
         <v>66</v>
       </c>
       <c r="D8" s="22"/>
@@ -8541,14 +8541,14 @@
       <c r="AA8" s="17"/>
       <c r="AB8" s="17"/>
       <c r="AC8" s="6"/>
-      <c r="AD8" s="61"/>
-      <c r="AE8" s="62"/>
-      <c r="AF8" s="62"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="63"/>
+      <c r="AD8" s="67"/>
+      <c r="AE8" s="61"/>
+      <c r="AF8" s="61"/>
+      <c r="AG8" s="61"/>
+      <c r="AH8" s="61"/>
+      <c r="AI8" s="61"/>
+      <c r="AJ8" s="61"/>
+      <c r="AK8" s="68"/>
     </row>
     <row r="9" spans="1:37" ht="14.25" customHeight="1">
       <c r="A9" s="55"/>
@@ -8584,20 +8584,20 @@
       <c r="AA9" s="17"/>
       <c r="AB9" s="17"/>
       <c r="AC9" s="6"/>
-      <c r="AD9" s="61"/>
-      <c r="AE9" s="62"/>
-      <c r="AF9" s="62"/>
-      <c r="AG9" s="62"/>
-      <c r="AH9" s="62"/>
-      <c r="AI9" s="62"/>
-      <c r="AJ9" s="62"/>
-      <c r="AK9" s="63"/>
+      <c r="AD9" s="67"/>
+      <c r="AE9" s="61"/>
+      <c r="AF9" s="61"/>
+      <c r="AG9" s="61"/>
+      <c r="AH9" s="61"/>
+      <c r="AI9" s="61"/>
+      <c r="AJ9" s="61"/>
+      <c r="AK9" s="68"/>
     </row>
     <row r="10" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="84" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="22"/>
@@ -8629,14 +8629,14 @@
       <c r="AA10" s="17"/>
       <c r="AB10" s="17"/>
       <c r="AC10" s="6"/>
-      <c r="AD10" s="61"/>
-      <c r="AE10" s="62"/>
-      <c r="AF10" s="62"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="62"/>
-      <c r="AJ10" s="62"/>
-      <c r="AK10" s="63"/>
+      <c r="AD10" s="67"/>
+      <c r="AE10" s="61"/>
+      <c r="AF10" s="61"/>
+      <c r="AG10" s="61"/>
+      <c r="AH10" s="61"/>
+      <c r="AI10" s="61"/>
+      <c r="AJ10" s="61"/>
+      <c r="AK10" s="68"/>
     </row>
     <row r="11" spans="1:37" ht="14.25" customHeight="1">
       <c r="A11" s="55"/>
@@ -8656,9 +8656,9 @@
       <c r="K11" s="40"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
       <c r="S11" s="18"/>
@@ -8672,20 +8672,20 @@
       <c r="AA11" s="17"/>
       <c r="AB11" s="17"/>
       <c r="AC11" s="6"/>
-      <c r="AD11" s="61"/>
-      <c r="AE11" s="62"/>
-      <c r="AF11" s="62"/>
-      <c r="AG11" s="62"/>
-      <c r="AH11" s="62"/>
-      <c r="AI11" s="62"/>
-      <c r="AJ11" s="62"/>
-      <c r="AK11" s="63"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="61"/>
+      <c r="AF11" s="61"/>
+      <c r="AG11" s="61"/>
+      <c r="AH11" s="61"/>
+      <c r="AI11" s="61"/>
+      <c r="AJ11" s="61"/>
+      <c r="AK11" s="68"/>
     </row>
     <row r="12" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="84" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="22"/>
@@ -8717,14 +8717,14 @@
       <c r="AA12" s="17"/>
       <c r="AB12" s="17"/>
       <c r="AC12" s="6"/>
-      <c r="AD12" s="61"/>
-      <c r="AE12" s="62"/>
-      <c r="AF12" s="62"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="63"/>
+      <c r="AD12" s="67"/>
+      <c r="AE12" s="61"/>
+      <c r="AF12" s="61"/>
+      <c r="AG12" s="61"/>
+      <c r="AH12" s="61"/>
+      <c r="AI12" s="61"/>
+      <c r="AJ12" s="61"/>
+      <c r="AK12" s="68"/>
     </row>
     <row r="13" spans="1:37" ht="17.25" customHeight="1">
       <c r="A13" s="55"/>
@@ -8760,20 +8760,20 @@
       <c r="AA13" s="17"/>
       <c r="AB13" s="17"/>
       <c r="AC13" s="6"/>
-      <c r="AD13" s="61"/>
-      <c r="AE13" s="62"/>
-      <c r="AF13" s="62"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="62"/>
-      <c r="AJ13" s="62"/>
-      <c r="AK13" s="63"/>
+      <c r="AD13" s="67"/>
+      <c r="AE13" s="61"/>
+      <c r="AF13" s="61"/>
+      <c r="AG13" s="61"/>
+      <c r="AH13" s="61"/>
+      <c r="AI13" s="61"/>
+      <c r="AJ13" s="61"/>
+      <c r="AK13" s="68"/>
     </row>
     <row r="14" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="84" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="22"/>
@@ -8805,14 +8805,14 @@
       <c r="AA14" s="17"/>
       <c r="AB14" s="17"/>
       <c r="AC14" s="6"/>
-      <c r="AD14" s="61"/>
-      <c r="AE14" s="62"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="63"/>
+      <c r="AD14" s="67"/>
+      <c r="AE14" s="61"/>
+      <c r="AF14" s="61"/>
+      <c r="AG14" s="61"/>
+      <c r="AH14" s="61"/>
+      <c r="AI14" s="61"/>
+      <c r="AJ14" s="61"/>
+      <c r="AK14" s="68"/>
     </row>
     <row r="15" spans="1:37" ht="17.25" customHeight="1">
       <c r="A15" s="55"/>
@@ -8832,11 +8832,11 @@
       <c r="K15" s="40"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
       <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="17"/>
@@ -8848,20 +8848,20 @@
       <c r="AA15" s="17"/>
       <c r="AB15" s="17"/>
       <c r="AC15" s="6"/>
-      <c r="AD15" s="61"/>
-      <c r="AE15" s="62"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="63"/>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="61"/>
+      <c r="AF15" s="61"/>
+      <c r="AG15" s="61"/>
+      <c r="AH15" s="61"/>
+      <c r="AI15" s="61"/>
+      <c r="AJ15" s="61"/>
+      <c r="AK15" s="68"/>
     </row>
     <row r="16" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="84" t="s">
         <v>70</v>
       </c>
       <c r="D16" s="22"/>
@@ -8893,14 +8893,14 @@
       <c r="AA16" s="17"/>
       <c r="AB16" s="17"/>
       <c r="AC16" s="6"/>
-      <c r="AD16" s="61"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="63"/>
+      <c r="AD16" s="67"/>
+      <c r="AE16" s="61"/>
+      <c r="AF16" s="61"/>
+      <c r="AG16" s="61"/>
+      <c r="AH16" s="61"/>
+      <c r="AI16" s="61"/>
+      <c r="AJ16" s="61"/>
+      <c r="AK16" s="68"/>
     </row>
     <row r="17" spans="1:37" ht="17.25" customHeight="1">
       <c r="A17" s="55"/>
@@ -8923,8 +8923,8 @@
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
       <c r="S17" s="18"/>
       <c r="T17" s="18"/>
       <c r="U17" s="17"/>
@@ -8936,20 +8936,20 @@
       <c r="AA17" s="17"/>
       <c r="AB17" s="17"/>
       <c r="AC17" s="6"/>
-      <c r="AD17" s="61"/>
-      <c r="AE17" s="62"/>
-      <c r="AF17" s="62"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="62"/>
-      <c r="AK17" s="63"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="61"/>
+      <c r="AF17" s="61"/>
+      <c r="AG17" s="61"/>
+      <c r="AH17" s="61"/>
+      <c r="AI17" s="61"/>
+      <c r="AJ17" s="61"/>
+      <c r="AK17" s="68"/>
     </row>
     <row r="18" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="85" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="22"/>
@@ -8981,14 +8981,14 @@
       <c r="AA18" s="17"/>
       <c r="AB18" s="17"/>
       <c r="AC18" s="6"/>
-      <c r="AD18" s="61"/>
-      <c r="AE18" s="62"/>
-      <c r="AF18" s="62"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="62"/>
-      <c r="AK18" s="63"/>
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="61"/>
+      <c r="AF18" s="61"/>
+      <c r="AG18" s="61"/>
+      <c r="AH18" s="61"/>
+      <c r="AI18" s="61"/>
+      <c r="AJ18" s="61"/>
+      <c r="AK18" s="68"/>
     </row>
     <row r="19" spans="1:37" ht="14.25" customHeight="1">
       <c r="A19" s="55"/>
@@ -9008,11 +9008,11 @@
       <c r="K19" s="17"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
       <c r="S19" s="18"/>
       <c r="T19" s="18"/>
       <c r="U19" s="17"/>
@@ -9024,20 +9024,20 @@
       <c r="AA19" s="17"/>
       <c r="AB19" s="17"/>
       <c r="AC19" s="6"/>
-      <c r="AD19" s="61"/>
-      <c r="AE19" s="62"/>
-      <c r="AF19" s="62"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="63"/>
+      <c r="AD19" s="67"/>
+      <c r="AE19" s="61"/>
+      <c r="AF19" s="61"/>
+      <c r="AG19" s="61"/>
+      <c r="AH19" s="61"/>
+      <c r="AI19" s="61"/>
+      <c r="AJ19" s="61"/>
+      <c r="AK19" s="68"/>
     </row>
     <row r="20" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="85" t="s">
         <v>73</v>
       </c>
       <c r="D20" s="22"/>
@@ -9069,14 +9069,14 @@
       <c r="AA20" s="17"/>
       <c r="AB20" s="17"/>
       <c r="AC20" s="6"/>
-      <c r="AD20" s="61"/>
-      <c r="AE20" s="62"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="63"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="61"/>
+      <c r="AF20" s="61"/>
+      <c r="AG20" s="61"/>
+      <c r="AH20" s="61"/>
+      <c r="AI20" s="61"/>
+      <c r="AJ20" s="61"/>
+      <c r="AK20" s="68"/>
     </row>
     <row r="21" spans="1:37" ht="14.25" customHeight="1">
       <c r="A21" s="55"/>
@@ -9112,20 +9112,20 @@
       <c r="AA21" s="17"/>
       <c r="AB21" s="17"/>
       <c r="AC21" s="6"/>
-      <c r="AD21" s="61"/>
-      <c r="AE21" s="62"/>
-      <c r="AF21" s="62"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="62"/>
-      <c r="AJ21" s="62"/>
-      <c r="AK21" s="63"/>
+      <c r="AD21" s="67"/>
+      <c r="AE21" s="61"/>
+      <c r="AF21" s="61"/>
+      <c r="AG21" s="61"/>
+      <c r="AH21" s="61"/>
+      <c r="AI21" s="61"/>
+      <c r="AJ21" s="61"/>
+      <c r="AK21" s="68"/>
     </row>
     <row r="22" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="84" t="s">
         <v>75</v>
       </c>
       <c r="D22" s="22"/>
@@ -9157,14 +9157,14 @@
       <c r="AA22" s="17"/>
       <c r="AB22" s="17"/>
       <c r="AC22" s="6"/>
-      <c r="AD22" s="61"/>
-      <c r="AE22" s="62"/>
-      <c r="AF22" s="62"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="63"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="61"/>
+      <c r="AF22" s="61"/>
+      <c r="AG22" s="61"/>
+      <c r="AH22" s="61"/>
+      <c r="AI22" s="61"/>
+      <c r="AJ22" s="61"/>
+      <c r="AK22" s="68"/>
     </row>
     <row r="23" spans="1:37" ht="14.25" customHeight="1">
       <c r="A23" s="55"/>
@@ -9184,10 +9184,10 @@
       <c r="K23" s="40"/>
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
       <c r="R23" s="17"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18"/>
@@ -9200,20 +9200,20 @@
       <c r="AA23" s="17"/>
       <c r="AB23" s="17"/>
       <c r="AC23" s="6"/>
-      <c r="AD23" s="61"/>
-      <c r="AE23" s="62"/>
-      <c r="AF23" s="62"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="63"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="61"/>
+      <c r="AF23" s="61"/>
+      <c r="AG23" s="61"/>
+      <c r="AH23" s="61"/>
+      <c r="AI23" s="61"/>
+      <c r="AJ23" s="61"/>
+      <c r="AK23" s="68"/>
     </row>
     <row r="24" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="85" t="s">
         <v>77</v>
       </c>
       <c r="D24" s="22"/>
@@ -9245,14 +9245,14 @@
       <c r="AA24" s="17"/>
       <c r="AB24" s="17"/>
       <c r="AC24" s="6"/>
-      <c r="AD24" s="61"/>
-      <c r="AE24" s="62"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="62"/>
-      <c r="AJ24" s="62"/>
-      <c r="AK24" s="63"/>
+      <c r="AD24" s="67"/>
+      <c r="AE24" s="61"/>
+      <c r="AF24" s="61"/>
+      <c r="AG24" s="61"/>
+      <c r="AH24" s="61"/>
+      <c r="AI24" s="61"/>
+      <c r="AJ24" s="61"/>
+      <c r="AK24" s="68"/>
     </row>
     <row r="25" spans="1:37" ht="14.25" customHeight="1">
       <c r="A25" s="55"/>
@@ -9272,11 +9272,11 @@
       <c r="K25" s="40"/>
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="40"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
       <c r="S25" s="18"/>
       <c r="T25" s="18"/>
       <c r="U25" s="17"/>
@@ -9288,20 +9288,20 @@
       <c r="AA25" s="17"/>
       <c r="AB25" s="17"/>
       <c r="AC25" s="6"/>
-      <c r="AD25" s="61"/>
-      <c r="AE25" s="62"/>
-      <c r="AF25" s="62"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
-      <c r="AK25" s="63"/>
+      <c r="AD25" s="67"/>
+      <c r="AE25" s="61"/>
+      <c r="AF25" s="61"/>
+      <c r="AG25" s="61"/>
+      <c r="AH25" s="61"/>
+      <c r="AI25" s="61"/>
+      <c r="AJ25" s="61"/>
+      <c r="AK25" s="68"/>
     </row>
     <row r="26" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="85" t="s">
+      <c r="B26" s="84" t="s">
         <v>66</v>
       </c>
       <c r="D26" s="22"/>
@@ -9333,14 +9333,14 @@
       <c r="AA26" s="17"/>
       <c r="AB26" s="17"/>
       <c r="AC26" s="6"/>
-      <c r="AD26" s="61"/>
-      <c r="AE26" s="62"/>
-      <c r="AF26" s="62"/>
-      <c r="AG26" s="62"/>
-      <c r="AH26" s="62"/>
-      <c r="AI26" s="62"/>
-      <c r="AJ26" s="62"/>
-      <c r="AK26" s="63"/>
+      <c r="AD26" s="67"/>
+      <c r="AE26" s="61"/>
+      <c r="AF26" s="61"/>
+      <c r="AG26" s="61"/>
+      <c r="AH26" s="61"/>
+      <c r="AI26" s="61"/>
+      <c r="AJ26" s="61"/>
+      <c r="AK26" s="68"/>
     </row>
     <row r="27" spans="1:37" ht="17.25" customHeight="1">
       <c r="A27" s="55"/>
@@ -9376,20 +9376,20 @@
       <c r="AA27" s="17"/>
       <c r="AB27" s="17"/>
       <c r="AC27" s="6"/>
-      <c r="AD27" s="61"/>
-      <c r="AE27" s="62"/>
-      <c r="AF27" s="62"/>
-      <c r="AG27" s="62"/>
-      <c r="AH27" s="62"/>
-      <c r="AI27" s="62"/>
-      <c r="AJ27" s="62"/>
-      <c r="AK27" s="63"/>
+      <c r="AD27" s="67"/>
+      <c r="AE27" s="61"/>
+      <c r="AF27" s="61"/>
+      <c r="AG27" s="61"/>
+      <c r="AH27" s="61"/>
+      <c r="AI27" s="61"/>
+      <c r="AJ27" s="61"/>
+      <c r="AK27" s="68"/>
     </row>
     <row r="28" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="84" t="s">
+      <c r="B28" s="85" t="s">
         <v>80</v>
       </c>
       <c r="D28" s="22"/>
@@ -9421,14 +9421,14 @@
       <c r="AA28" s="17"/>
       <c r="AB28" s="17"/>
       <c r="AC28" s="6"/>
-      <c r="AD28" s="61"/>
-      <c r="AE28" s="62"/>
-      <c r="AF28" s="62"/>
-      <c r="AG28" s="62"/>
-      <c r="AH28" s="62"/>
-      <c r="AI28" s="62"/>
-      <c r="AJ28" s="62"/>
-      <c r="AK28" s="63"/>
+      <c r="AD28" s="67"/>
+      <c r="AE28" s="61"/>
+      <c r="AF28" s="61"/>
+      <c r="AG28" s="61"/>
+      <c r="AH28" s="61"/>
+      <c r="AI28" s="61"/>
+      <c r="AJ28" s="61"/>
+      <c r="AK28" s="68"/>
     </row>
     <row r="29" spans="1:37" ht="14.25" customHeight="1">
       <c r="A29" s="55"/>
@@ -9464,20 +9464,20 @@
       <c r="AA29" s="17"/>
       <c r="AB29" s="17"/>
       <c r="AC29" s="6"/>
-      <c r="AD29" s="61"/>
-      <c r="AE29" s="62"/>
-      <c r="AF29" s="62"/>
-      <c r="AG29" s="62"/>
-      <c r="AH29" s="62"/>
-      <c r="AI29" s="62"/>
-      <c r="AJ29" s="62"/>
-      <c r="AK29" s="63"/>
+      <c r="AD29" s="67"/>
+      <c r="AE29" s="61"/>
+      <c r="AF29" s="61"/>
+      <c r="AG29" s="61"/>
+      <c r="AH29" s="61"/>
+      <c r="AI29" s="61"/>
+      <c r="AJ29" s="61"/>
+      <c r="AK29" s="68"/>
     </row>
     <row r="30" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="85" t="s">
+      <c r="B30" s="84" t="s">
         <v>69</v>
       </c>
       <c r="D30" s="22"/>
@@ -9509,14 +9509,14 @@
       <c r="AA30" s="17"/>
       <c r="AB30" s="17"/>
       <c r="AC30" s="6"/>
-      <c r="AD30" s="61"/>
-      <c r="AE30" s="62"/>
-      <c r="AF30" s="62"/>
-      <c r="AG30" s="62"/>
-      <c r="AH30" s="62"/>
-      <c r="AI30" s="62"/>
-      <c r="AJ30" s="62"/>
-      <c r="AK30" s="63"/>
+      <c r="AD30" s="67"/>
+      <c r="AE30" s="61"/>
+      <c r="AF30" s="61"/>
+      <c r="AG30" s="61"/>
+      <c r="AH30" s="61"/>
+      <c r="AI30" s="61"/>
+      <c r="AJ30" s="61"/>
+      <c r="AK30" s="68"/>
     </row>
     <row r="31" spans="1:37" ht="14.25" customHeight="1">
       <c r="A31" s="55"/>
@@ -9552,20 +9552,20 @@
       <c r="AA31" s="17"/>
       <c r="AB31" s="17"/>
       <c r="AC31" s="6"/>
-      <c r="AD31" s="64"/>
-      <c r="AE31" s="65"/>
-      <c r="AF31" s="65"/>
-      <c r="AG31" s="65"/>
-      <c r="AH31" s="65"/>
-      <c r="AI31" s="65"/>
-      <c r="AJ31" s="65"/>
-      <c r="AK31" s="66"/>
+      <c r="AD31" s="69"/>
+      <c r="AE31" s="70"/>
+      <c r="AF31" s="70"/>
+      <c r="AG31" s="70"/>
+      <c r="AH31" s="70"/>
+      <c r="AI31" s="70"/>
+      <c r="AJ31" s="70"/>
+      <c r="AK31" s="71"/>
     </row>
     <row r="32" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="84" t="s">
+      <c r="B32" s="85" t="s">
         <v>83</v>
       </c>
       <c r="D32" s="22"/>
@@ -9625,8 +9625,8 @@
       <c r="L33" s="28"/>
       <c r="M33" s="18"/>
       <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="40"/>
       <c r="Q33" s="17"/>
       <c r="R33" s="17"/>
       <c r="S33" s="18"/>
@@ -9650,10 +9650,10 @@
       <c r="AK33" s="52"/>
     </row>
     <row r="34" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="84" t="s">
         <v>71</v>
       </c>
       <c r="D34" s="22"/>
@@ -9685,14 +9685,14 @@
       <c r="AA34" s="17"/>
       <c r="AB34" s="17"/>
       <c r="AC34" s="6"/>
-      <c r="AD34" s="70"/>
-      <c r="AE34" s="71"/>
-      <c r="AF34" s="71"/>
-      <c r="AG34" s="71"/>
-      <c r="AH34" s="71"/>
-      <c r="AI34" s="71"/>
-      <c r="AJ34" s="71"/>
-      <c r="AK34" s="72"/>
+      <c r="AD34" s="73"/>
+      <c r="AE34" s="74"/>
+      <c r="AF34" s="74"/>
+      <c r="AG34" s="74"/>
+      <c r="AH34" s="74"/>
+      <c r="AI34" s="74"/>
+      <c r="AJ34" s="74"/>
+      <c r="AK34" s="75"/>
     </row>
     <row r="35" spans="1:37" ht="14.25" customHeight="1">
       <c r="A35" s="55"/>
@@ -9713,10 +9713,10 @@
       <c r="L35" s="31"/>
       <c r="M35" s="18"/>
       <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="40"/>
       <c r="S35" s="18"/>
       <c r="T35" s="18"/>
       <c r="U35" s="17"/>
@@ -9728,20 +9728,20 @@
       <c r="AA35" s="17"/>
       <c r="AB35" s="17"/>
       <c r="AC35" s="6"/>
-      <c r="AD35" s="73"/>
-      <c r="AE35" s="62"/>
-      <c r="AF35" s="62"/>
-      <c r="AG35" s="62"/>
-      <c r="AH35" s="62"/>
-      <c r="AI35" s="62"/>
-      <c r="AJ35" s="62"/>
-      <c r="AK35" s="74"/>
+      <c r="AD35" s="76"/>
+      <c r="AE35" s="61"/>
+      <c r="AF35" s="61"/>
+      <c r="AG35" s="61"/>
+      <c r="AH35" s="61"/>
+      <c r="AI35" s="61"/>
+      <c r="AJ35" s="61"/>
+      <c r="AK35" s="77"/>
     </row>
     <row r="36" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="84" t="s">
+      <c r="B36" s="85" t="s">
         <v>73</v>
       </c>
       <c r="D36" s="22"/>
@@ -9773,14 +9773,14 @@
       <c r="AA36" s="17"/>
       <c r="AB36" s="17"/>
       <c r="AC36" s="6"/>
-      <c r="AD36" s="73"/>
-      <c r="AE36" s="62"/>
-      <c r="AF36" s="62"/>
-      <c r="AG36" s="62"/>
-      <c r="AH36" s="62"/>
-      <c r="AI36" s="62"/>
-      <c r="AJ36" s="62"/>
-      <c r="AK36" s="74"/>
+      <c r="AD36" s="76"/>
+      <c r="AE36" s="61"/>
+      <c r="AF36" s="61"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="61"/>
+      <c r="AK36" s="77"/>
     </row>
     <row r="37" spans="1:37" ht="14.25" customHeight="1">
       <c r="A37" s="55"/>
@@ -9800,7 +9800,7 @@
       <c r="K37" s="40"/>
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
-      <c r="N37" s="17"/>
+      <c r="N37" s="40"/>
       <c r="O37" s="17"/>
       <c r="P37" s="17"/>
       <c r="Q37" s="17"/>
@@ -9816,20 +9816,20 @@
       <c r="AA37" s="17"/>
       <c r="AB37" s="17"/>
       <c r="AC37" s="6"/>
-      <c r="AD37" s="73"/>
-      <c r="AE37" s="62"/>
-      <c r="AF37" s="62"/>
-      <c r="AG37" s="62"/>
-      <c r="AH37" s="62"/>
-      <c r="AI37" s="62"/>
-      <c r="AJ37" s="62"/>
-      <c r="AK37" s="74"/>
+      <c r="AD37" s="76"/>
+      <c r="AE37" s="61"/>
+      <c r="AF37" s="61"/>
+      <c r="AG37" s="61"/>
+      <c r="AH37" s="61"/>
+      <c r="AI37" s="61"/>
+      <c r="AJ37" s="61"/>
+      <c r="AK37" s="77"/>
     </row>
     <row r="38" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="85" t="s">
+      <c r="B38" s="84" t="s">
         <v>75</v>
       </c>
       <c r="D38" s="22"/>
@@ -9861,14 +9861,14 @@
       <c r="AA38" s="17"/>
       <c r="AB38" s="17"/>
       <c r="AC38" s="6"/>
-      <c r="AD38" s="73"/>
-      <c r="AE38" s="62"/>
-      <c r="AF38" s="62"/>
-      <c r="AG38" s="62"/>
-      <c r="AH38" s="62"/>
-      <c r="AI38" s="62"/>
-      <c r="AJ38" s="62"/>
-      <c r="AK38" s="74"/>
+      <c r="AD38" s="76"/>
+      <c r="AE38" s="61"/>
+      <c r="AF38" s="61"/>
+      <c r="AG38" s="61"/>
+      <c r="AH38" s="61"/>
+      <c r="AI38" s="61"/>
+      <c r="AJ38" s="61"/>
+      <c r="AK38" s="77"/>
     </row>
     <row r="39" spans="1:37" ht="14.25" customHeight="1">
       <c r="A39" s="55"/>
@@ -9904,20 +9904,20 @@
       <c r="AA39" s="17"/>
       <c r="AB39" s="17"/>
       <c r="AC39" s="6"/>
-      <c r="AD39" s="73"/>
-      <c r="AE39" s="62"/>
-      <c r="AF39" s="62"/>
-      <c r="AG39" s="62"/>
-      <c r="AH39" s="62"/>
-      <c r="AI39" s="62"/>
-      <c r="AJ39" s="62"/>
-      <c r="AK39" s="74"/>
+      <c r="AD39" s="76"/>
+      <c r="AE39" s="61"/>
+      <c r="AF39" s="61"/>
+      <c r="AG39" s="61"/>
+      <c r="AH39" s="61"/>
+      <c r="AI39" s="61"/>
+      <c r="AJ39" s="61"/>
+      <c r="AK39" s="77"/>
     </row>
     <row r="40" spans="1:37" ht="15" customHeight="1">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="84" t="s">
+      <c r="B40" s="85" t="s">
         <v>77</v>
       </c>
       <c r="D40" s="22"/>
@@ -9949,14 +9949,14 @@
       <c r="AA40" s="17"/>
       <c r="AB40" s="17"/>
       <c r="AC40" s="6"/>
-      <c r="AD40" s="73"/>
-      <c r="AE40" s="62"/>
-      <c r="AF40" s="62"/>
-      <c r="AG40" s="62"/>
-      <c r="AH40" s="62"/>
-      <c r="AI40" s="62"/>
-      <c r="AJ40" s="62"/>
-      <c r="AK40" s="74"/>
+      <c r="AD40" s="76"/>
+      <c r="AE40" s="61"/>
+      <c r="AF40" s="61"/>
+      <c r="AG40" s="61"/>
+      <c r="AH40" s="61"/>
+      <c r="AI40" s="61"/>
+      <c r="AJ40" s="61"/>
+      <c r="AK40" s="77"/>
     </row>
     <row r="41" spans="1:37" ht="15" customHeight="1">
       <c r="A41" s="55"/>
@@ -9992,20 +9992,20 @@
       <c r="AA41" s="17"/>
       <c r="AB41" s="17"/>
       <c r="AC41" s="6"/>
-      <c r="AD41" s="73"/>
-      <c r="AE41" s="62"/>
-      <c r="AF41" s="62"/>
-      <c r="AG41" s="62"/>
-      <c r="AH41" s="62"/>
-      <c r="AI41" s="62"/>
-      <c r="AJ41" s="62"/>
-      <c r="AK41" s="74"/>
+      <c r="AD41" s="76"/>
+      <c r="AE41" s="61"/>
+      <c r="AF41" s="61"/>
+      <c r="AG41" s="61"/>
+      <c r="AH41" s="61"/>
+      <c r="AI41" s="61"/>
+      <c r="AJ41" s="61"/>
+      <c r="AK41" s="77"/>
     </row>
     <row r="42" spans="1:37" ht="15" customHeight="1">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="85" t="s">
+      <c r="B42" s="84" t="s">
         <v>66</v>
       </c>
       <c r="D42" s="22"/>
@@ -10037,14 +10037,14 @@
       <c r="AA42" s="17"/>
       <c r="AB42" s="17"/>
       <c r="AC42" s="6"/>
-      <c r="AD42" s="73"/>
-      <c r="AE42" s="62"/>
-      <c r="AF42" s="62"/>
-      <c r="AG42" s="62"/>
-      <c r="AH42" s="62"/>
-      <c r="AI42" s="62"/>
-      <c r="AJ42" s="62"/>
-      <c r="AK42" s="74"/>
+      <c r="AD42" s="76"/>
+      <c r="AE42" s="61"/>
+      <c r="AF42" s="61"/>
+      <c r="AG42" s="61"/>
+      <c r="AH42" s="61"/>
+      <c r="AI42" s="61"/>
+      <c r="AJ42" s="61"/>
+      <c r="AK42" s="77"/>
     </row>
     <row r="43" spans="1:37" ht="15" customHeight="1">
       <c r="A43" s="55"/>
@@ -10080,20 +10080,20 @@
       <c r="AA43" s="17"/>
       <c r="AB43" s="17"/>
       <c r="AC43" s="6"/>
-      <c r="AD43" s="73"/>
-      <c r="AE43" s="62"/>
-      <c r="AF43" s="62"/>
-      <c r="AG43" s="62"/>
-      <c r="AH43" s="62"/>
-      <c r="AI43" s="62"/>
-      <c r="AJ43" s="62"/>
-      <c r="AK43" s="74"/>
+      <c r="AD43" s="76"/>
+      <c r="AE43" s="61"/>
+      <c r="AF43" s="61"/>
+      <c r="AG43" s="61"/>
+      <c r="AH43" s="61"/>
+      <c r="AI43" s="61"/>
+      <c r="AJ43" s="61"/>
+      <c r="AK43" s="77"/>
     </row>
     <row r="44" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="84" t="s">
+      <c r="B44" s="85" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="22"/>
@@ -10125,14 +10125,14 @@
       <c r="AA44" s="17"/>
       <c r="AB44" s="17"/>
       <c r="AC44" s="6"/>
-      <c r="AD44" s="73"/>
-      <c r="AE44" s="62"/>
-      <c r="AF44" s="62"/>
-      <c r="AG44" s="62"/>
-      <c r="AH44" s="62"/>
-      <c r="AI44" s="62"/>
-      <c r="AJ44" s="62"/>
-      <c r="AK44" s="74"/>
+      <c r="AD44" s="76"/>
+      <c r="AE44" s="61"/>
+      <c r="AF44" s="61"/>
+      <c r="AG44" s="61"/>
+      <c r="AH44" s="61"/>
+      <c r="AI44" s="61"/>
+      <c r="AJ44" s="61"/>
+      <c r="AK44" s="77"/>
     </row>
     <row r="45" spans="1:37" ht="14.25" customHeight="1">
       <c r="A45" s="55"/>
@@ -10168,20 +10168,20 @@
       <c r="AA45" s="17"/>
       <c r="AB45" s="17"/>
       <c r="AC45" s="6"/>
-      <c r="AD45" s="73"/>
-      <c r="AE45" s="62"/>
-      <c r="AF45" s="62"/>
-      <c r="AG45" s="62"/>
-      <c r="AH45" s="62"/>
-      <c r="AI45" s="62"/>
-      <c r="AJ45" s="62"/>
-      <c r="AK45" s="74"/>
+      <c r="AD45" s="76"/>
+      <c r="AE45" s="61"/>
+      <c r="AF45" s="61"/>
+      <c r="AG45" s="61"/>
+      <c r="AH45" s="61"/>
+      <c r="AI45" s="61"/>
+      <c r="AJ45" s="61"/>
+      <c r="AK45" s="77"/>
     </row>
     <row r="46" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A46" s="54" t="s">
+      <c r="A46" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="85" t="s">
+      <c r="B46" s="84" t="s">
         <v>67</v>
       </c>
       <c r="D46" s="22"/>
@@ -10213,14 +10213,14 @@
       <c r="AA46" s="17"/>
       <c r="AB46" s="17"/>
       <c r="AC46" s="6"/>
-      <c r="AD46" s="73"/>
-      <c r="AE46" s="62"/>
-      <c r="AF46" s="62"/>
-      <c r="AG46" s="62"/>
-      <c r="AH46" s="62"/>
-      <c r="AI46" s="62"/>
-      <c r="AJ46" s="62"/>
-      <c r="AK46" s="74"/>
+      <c r="AD46" s="76"/>
+      <c r="AE46" s="61"/>
+      <c r="AF46" s="61"/>
+      <c r="AG46" s="61"/>
+      <c r="AH46" s="61"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="61"/>
+      <c r="AK46" s="77"/>
     </row>
     <row r="47" spans="1:37" ht="14.25" customHeight="1">
       <c r="A47" s="55"/>
@@ -10240,11 +10240,11 @@
       <c r="K47" s="17"/>
       <c r="L47" s="18"/>
       <c r="M47" s="18"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
+      <c r="N47" s="40"/>
+      <c r="O47" s="40"/>
+      <c r="P47" s="40"/>
+      <c r="Q47" s="40"/>
+      <c r="R47" s="40"/>
       <c r="S47" s="31"/>
       <c r="T47" s="31"/>
       <c r="U47" s="17"/>
@@ -10256,20 +10256,20 @@
       <c r="AA47" s="17"/>
       <c r="AB47" s="17"/>
       <c r="AC47" s="6"/>
-      <c r="AD47" s="73"/>
-      <c r="AE47" s="62"/>
-      <c r="AF47" s="62"/>
-      <c r="AG47" s="62"/>
-      <c r="AH47" s="62"/>
-      <c r="AI47" s="62"/>
-      <c r="AJ47" s="62"/>
-      <c r="AK47" s="74"/>
+      <c r="AD47" s="76"/>
+      <c r="AE47" s="61"/>
+      <c r="AF47" s="61"/>
+      <c r="AG47" s="61"/>
+      <c r="AH47" s="61"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="77"/>
     </row>
     <row r="48" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A48" s="54" t="s">
+      <c r="A48" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="84" t="s">
+      <c r="B48" s="85" t="s">
         <v>93</v>
       </c>
       <c r="D48" s="22"/>
@@ -10301,14 +10301,14 @@
       <c r="AA48" s="17"/>
       <c r="AB48" s="17"/>
       <c r="AC48" s="6"/>
-      <c r="AD48" s="75"/>
-      <c r="AE48" s="76"/>
-      <c r="AF48" s="76"/>
-      <c r="AG48" s="76"/>
-      <c r="AH48" s="76"/>
-      <c r="AI48" s="76"/>
-      <c r="AJ48" s="76"/>
-      <c r="AK48" s="77"/>
+      <c r="AD48" s="78"/>
+      <c r="AE48" s="79"/>
+      <c r="AF48" s="79"/>
+      <c r="AG48" s="79"/>
+      <c r="AH48" s="79"/>
+      <c r="AI48" s="79"/>
+      <c r="AJ48" s="79"/>
+      <c r="AK48" s="80"/>
     </row>
     <row r="49" spans="1:37" ht="14.25" customHeight="1">
       <c r="A49" s="55"/>
@@ -10329,7 +10329,7 @@
       <c r="L49" s="18"/>
       <c r="M49" s="18"/>
       <c r="N49" s="40"/>
-      <c r="O49" s="17"/>
+      <c r="O49" s="40"/>
       <c r="P49" s="25"/>
       <c r="Q49" s="26"/>
       <c r="R49" s="27"/>
@@ -10356,10 +10356,10 @@
       <c r="AK49" s="38"/>
     </row>
     <row r="50" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A50" s="54" t="s">
+      <c r="A50" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="84" t="s">
+      <c r="B50" s="85" t="s">
         <v>95</v>
       </c>
       <c r="D50" s="22"/>
@@ -10421,8 +10421,8 @@
       <c r="L51" s="18"/>
       <c r="M51" s="18"/>
       <c r="N51" s="40"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
+      <c r="O51" s="40"/>
+      <c r="P51" s="40"/>
       <c r="Q51" s="17"/>
       <c r="R51" s="17"/>
       <c r="S51" s="18"/>
@@ -10448,10 +10448,10 @@
       <c r="AK51" s="38"/>
     </row>
     <row r="52" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A52" s="54" t="s">
+      <c r="A52" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="84" t="s">
+      <c r="B52" s="85" t="s">
         <v>97</v>
       </c>
       <c r="D52" s="22"/>
@@ -10512,11 +10512,11 @@
       <c r="K53" s="17"/>
       <c r="L53" s="18"/>
       <c r="M53" s="18"/>
-      <c r="N53" s="40"/>
+      <c r="N53" s="17"/>
       <c r="O53" s="17"/>
       <c r="P53" s="17"/>
       <c r="Q53" s="17"/>
-      <c r="R53" s="17"/>
+      <c r="R53" s="40"/>
       <c r="S53" s="18"/>
       <c r="T53" s="18"/>
       <c r="U53" s="17"/>
@@ -10540,10 +10540,10 @@
       <c r="AK53" s="38"/>
     </row>
     <row r="54" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A54" s="54" t="s">
+      <c r="A54" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="B54" s="84" t="s">
+      <c r="B54" s="85" t="s">
         <v>99</v>
       </c>
       <c r="D54" s="22"/>
@@ -10604,11 +10604,11 @@
       <c r="K55" s="17"/>
       <c r="L55" s="18"/>
       <c r="M55" s="18"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-      <c r="R55" s="17"/>
+      <c r="N55" s="40"/>
+      <c r="O55" s="40"/>
+      <c r="P55" s="40"/>
+      <c r="Q55" s="40"/>
+      <c r="R55" s="40"/>
       <c r="S55" s="18"/>
       <c r="T55" s="18"/>
       <c r="U55" s="17"/>
@@ -10630,10 +10630,10 @@
       <c r="AK55" s="38"/>
     </row>
     <row r="56" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A56" s="54" t="s">
+      <c r="A56" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="B56" s="84" t="s">
+      <c r="B56" s="85" t="s">
         <v>101</v>
       </c>
       <c r="D56" s="22"/>
@@ -10692,11 +10692,11 @@
       <c r="K57" s="24"/>
       <c r="L57" s="28"/>
       <c r="M57" s="28"/>
-      <c r="N57" s="24"/>
-      <c r="O57" s="24"/>
-      <c r="P57" s="24"/>
-      <c r="Q57" s="24"/>
-      <c r="R57" s="24"/>
+      <c r="N57" s="40"/>
+      <c r="O57" s="40"/>
+      <c r="P57" s="40"/>
+      <c r="Q57" s="40"/>
+      <c r="R57" s="40"/>
       <c r="S57" s="28"/>
       <c r="T57" s="28"/>
       <c r="U57" s="24"/>
@@ -10710,10 +10710,10 @@
       <c r="AC57" s="6"/>
     </row>
     <row r="58" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A58" s="54" t="s">
+      <c r="A58" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="84" t="s">
+      <c r="B58" s="85" t="s">
         <v>103</v>
       </c>
       <c r="G58" s="12" t="e">
@@ -10783,10 +10783,10 @@
       <c r="AC59" s="6"/>
     </row>
     <row r="60" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A60" s="54" t="s">
+      <c r="A60" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="B60" s="84" t="s">
+      <c r="B60" s="85" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="12"/>
@@ -10860,10 +10860,10 @@
       <c r="AC61" s="6"/>
     </row>
     <row r="62" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="B62" s="84" t="s">
+      <c r="B62" s="85" t="s">
         <v>107</v>
       </c>
       <c r="F62" s="12"/>
@@ -10934,10 +10934,10 @@
       <c r="AC63" s="6"/>
     </row>
     <row r="64" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A64" s="54" t="s">
+      <c r="A64" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="B64" s="84" t="s">
+      <c r="B64" s="85" t="s">
         <v>109</v>
       </c>
       <c r="D64" s="22"/>
@@ -11010,10 +11010,10 @@
       <c r="AC65" s="6"/>
     </row>
     <row r="66" spans="1:29" ht="14.25" customHeight="1">
-      <c r="A66" s="54" t="s">
+      <c r="A66" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="B66" s="84" t="s">
+      <c r="B66" s="85" t="s">
         <v>111</v>
       </c>
       <c r="D66" s="22"/>
@@ -13905,6 +13905,55 @@
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="AD34:AK48"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="AD3:AK31"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="Y1:AB1"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="B26:B27"/>
@@ -13921,55 +13970,6 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="AD3:AK31"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AD34:AK48"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="86" orientation="portrait"/>
@@ -14024,12 +14024,12 @@
       <c r="Z1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="80">
+      <c r="AA1" s="57">
         <v>2024</v>
       </c>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="82"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="59"/>
       <c r="AE1" s="6"/>
       <c r="AF1" s="4" t="s">
         <v>2</v>
@@ -14085,10 +14085,10 @@
       <c r="A3" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
       <c r="J3" s="13" t="s">
         <v>5</v>
       </c>
@@ -14153,22 +14153,22 @@
         <v>25</v>
       </c>
       <c r="AE3" s="6"/>
-      <c r="AF3" s="58" t="s">
+      <c r="AF3" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="60"/>
+      <c r="AG3" s="65"/>
+      <c r="AH3" s="65"/>
+      <c r="AI3" s="65"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="65"/>
+      <c r="AL3" s="65"/>
+      <c r="AM3" s="66"/>
     </row>
     <row r="4" spans="1:39" ht="14.25" customHeight="1">
-      <c r="D4" s="67"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
@@ -14191,14 +14191,14 @@
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="6"/>
-      <c r="AF4" s="61"/>
-      <c r="AG4" s="62"/>
-      <c r="AH4" s="62"/>
-      <c r="AI4" s="62"/>
-      <c r="AJ4" s="62"/>
-      <c r="AK4" s="62"/>
-      <c r="AL4" s="62"/>
-      <c r="AM4" s="63"/>
+      <c r="AF4" s="67"/>
+      <c r="AG4" s="61"/>
+      <c r="AH4" s="61"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="61"/>
+      <c r="AL4" s="61"/>
+      <c r="AM4" s="68"/>
     </row>
     <row r="5" spans="1:39" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
@@ -14250,20 +14250,20 @@
       <c r="AC5" s="12"/>
       <c r="AD5" s="16"/>
       <c r="AE5" s="6"/>
-      <c r="AF5" s="61"/>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="62"/>
-      <c r="AI5" s="62"/>
-      <c r="AJ5" s="62"/>
-      <c r="AK5" s="62"/>
-      <c r="AL5" s="62"/>
-      <c r="AM5" s="63"/>
+      <c r="AF5" s="67"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
+      <c r="AM5" s="68"/>
     </row>
     <row r="6" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="68"/>
+      <c r="B6" s="72"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -14295,14 +14295,14 @@
       <c r="AC6" s="17"/>
       <c r="AD6" s="17"/>
       <c r="AE6" s="6"/>
-      <c r="AF6" s="61"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
-      <c r="AL6" s="62"/>
-      <c r="AM6" s="63"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="61"/>
+      <c r="AH6" s="61"/>
+      <c r="AI6" s="61"/>
+      <c r="AJ6" s="61"/>
+      <c r="AK6" s="61"/>
+      <c r="AL6" s="61"/>
+      <c r="AM6" s="68"/>
     </row>
     <row r="7" spans="1:39" ht="14.25" customHeight="1">
       <c r="A7" s="55"/>
@@ -14338,20 +14338,20 @@
       <c r="AC7" s="17"/>
       <c r="AD7" s="17"/>
       <c r="AE7" s="6"/>
-      <c r="AF7" s="61"/>
-      <c r="AG7" s="62"/>
-      <c r="AH7" s="62"/>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="62"/>
-      <c r="AL7" s="62"/>
-      <c r="AM7" s="63"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="61"/>
+      <c r="AK7" s="61"/>
+      <c r="AL7" s="61"/>
+      <c r="AM7" s="68"/>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="69"/>
+      <c r="B8" s="63"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
@@ -14383,14 +14383,14 @@
       <c r="AC8" s="17"/>
       <c r="AD8" s="17"/>
       <c r="AE8" s="6"/>
-      <c r="AF8" s="61"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="62"/>
-      <c r="AL8" s="62"/>
-      <c r="AM8" s="63"/>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="61"/>
+      <c r="AH8" s="61"/>
+      <c r="AI8" s="61"/>
+      <c r="AJ8" s="61"/>
+      <c r="AK8" s="61"/>
+      <c r="AL8" s="61"/>
+      <c r="AM8" s="68"/>
     </row>
     <row r="9" spans="1:39" ht="14.25" customHeight="1">
       <c r="A9" s="55"/>
@@ -14426,20 +14426,20 @@
       <c r="AC9" s="17"/>
       <c r="AD9" s="17"/>
       <c r="AE9" s="6"/>
-      <c r="AF9" s="61"/>
-      <c r="AG9" s="62"/>
-      <c r="AH9" s="62"/>
-      <c r="AI9" s="62"/>
-      <c r="AJ9" s="62"/>
-      <c r="AK9" s="62"/>
-      <c r="AL9" s="62"/>
-      <c r="AM9" s="63"/>
+      <c r="AF9" s="67"/>
+      <c r="AG9" s="61"/>
+      <c r="AH9" s="61"/>
+      <c r="AI9" s="61"/>
+      <c r="AJ9" s="61"/>
+      <c r="AK9" s="61"/>
+      <c r="AL9" s="61"/>
+      <c r="AM9" s="68"/>
     </row>
     <row r="10" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="69"/>
+      <c r="B10" s="63"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -14471,14 +14471,14 @@
       <c r="AC10" s="17"/>
       <c r="AD10" s="17"/>
       <c r="AE10" s="6"/>
-      <c r="AF10" s="61"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="62"/>
-      <c r="AJ10" s="62"/>
-      <c r="AK10" s="62"/>
-      <c r="AL10" s="62"/>
-      <c r="AM10" s="63"/>
+      <c r="AF10" s="67"/>
+      <c r="AG10" s="61"/>
+      <c r="AH10" s="61"/>
+      <c r="AI10" s="61"/>
+      <c r="AJ10" s="61"/>
+      <c r="AK10" s="61"/>
+      <c r="AL10" s="61"/>
+      <c r="AM10" s="68"/>
     </row>
     <row r="11" spans="1:39" ht="14.25" customHeight="1">
       <c r="A11" s="55"/>
@@ -14514,20 +14514,20 @@
       <c r="AC11" s="17"/>
       <c r="AD11" s="17"/>
       <c r="AE11" s="6"/>
-      <c r="AF11" s="61"/>
-      <c r="AG11" s="62"/>
-      <c r="AH11" s="62"/>
-      <c r="AI11" s="62"/>
-      <c r="AJ11" s="62"/>
-      <c r="AK11" s="62"/>
-      <c r="AL11" s="62"/>
-      <c r="AM11" s="63"/>
+      <c r="AF11" s="67"/>
+      <c r="AG11" s="61"/>
+      <c r="AH11" s="61"/>
+      <c r="AI11" s="61"/>
+      <c r="AJ11" s="61"/>
+      <c r="AK11" s="61"/>
+      <c r="AL11" s="61"/>
+      <c r="AM11" s="68"/>
     </row>
     <row r="12" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="69"/>
+      <c r="B12" s="63"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -14559,14 +14559,14 @@
       <c r="AC12" s="17"/>
       <c r="AD12" s="17"/>
       <c r="AE12" s="6"/>
-      <c r="AF12" s="61"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
-      <c r="AL12" s="62"/>
-      <c r="AM12" s="63"/>
+      <c r="AF12" s="67"/>
+      <c r="AG12" s="61"/>
+      <c r="AH12" s="61"/>
+      <c r="AI12" s="61"/>
+      <c r="AJ12" s="61"/>
+      <c r="AK12" s="61"/>
+      <c r="AL12" s="61"/>
+      <c r="AM12" s="68"/>
     </row>
     <row r="13" spans="1:39" ht="14.25" customHeight="1">
       <c r="A13" s="55"/>
@@ -14602,20 +14602,20 @@
       <c r="AC13" s="17"/>
       <c r="AD13" s="17"/>
       <c r="AE13" s="6"/>
-      <c r="AF13" s="61"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="62"/>
-      <c r="AJ13" s="62"/>
-      <c r="AK13" s="62"/>
-      <c r="AL13" s="62"/>
-      <c r="AM13" s="63"/>
+      <c r="AF13" s="67"/>
+      <c r="AG13" s="61"/>
+      <c r="AH13" s="61"/>
+      <c r="AI13" s="61"/>
+      <c r="AJ13" s="61"/>
+      <c r="AK13" s="61"/>
+      <c r="AL13" s="61"/>
+      <c r="AM13" s="68"/>
     </row>
     <row r="14" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="69"/>
+      <c r="B14" s="63"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -14647,14 +14647,14 @@
       <c r="AC14" s="17"/>
       <c r="AD14" s="17"/>
       <c r="AE14" s="6"/>
-      <c r="AF14" s="61"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="62"/>
-      <c r="AM14" s="63"/>
+      <c r="AF14" s="67"/>
+      <c r="AG14" s="61"/>
+      <c r="AH14" s="61"/>
+      <c r="AI14" s="61"/>
+      <c r="AJ14" s="61"/>
+      <c r="AK14" s="61"/>
+      <c r="AL14" s="61"/>
+      <c r="AM14" s="68"/>
     </row>
     <row r="15" spans="1:39" ht="17.25" customHeight="1">
       <c r="A15" s="55"/>
@@ -14690,20 +14690,20 @@
       <c r="AC15" s="17"/>
       <c r="AD15" s="17"/>
       <c r="AE15" s="6"/>
-      <c r="AF15" s="61"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="62"/>
-      <c r="AM15" s="63"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="61"/>
+      <c r="AH15" s="61"/>
+      <c r="AI15" s="61"/>
+      <c r="AJ15" s="61"/>
+      <c r="AK15" s="61"/>
+      <c r="AL15" s="61"/>
+      <c r="AM15" s="68"/>
     </row>
     <row r="16" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="69"/>
+      <c r="B16" s="63"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -14735,14 +14735,14 @@
       <c r="AC16" s="17"/>
       <c r="AD16" s="17"/>
       <c r="AE16" s="6"/>
-      <c r="AF16" s="61"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
-      <c r="AL16" s="62"/>
-      <c r="AM16" s="63"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="61"/>
+      <c r="AH16" s="61"/>
+      <c r="AI16" s="61"/>
+      <c r="AJ16" s="61"/>
+      <c r="AK16" s="61"/>
+      <c r="AL16" s="61"/>
+      <c r="AM16" s="68"/>
     </row>
     <row r="17" spans="1:39" ht="17.25" customHeight="1">
       <c r="A17" s="55"/>
@@ -14778,20 +14778,20 @@
       <c r="AC17" s="17"/>
       <c r="AD17" s="17"/>
       <c r="AE17" s="6"/>
-      <c r="AF17" s="61"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="62"/>
-      <c r="AK17" s="62"/>
-      <c r="AL17" s="62"/>
-      <c r="AM17" s="63"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="61"/>
+      <c r="AH17" s="61"/>
+      <c r="AI17" s="61"/>
+      <c r="AJ17" s="61"/>
+      <c r="AK17" s="61"/>
+      <c r="AL17" s="61"/>
+      <c r="AM17" s="68"/>
     </row>
     <row r="18" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="69"/>
+      <c r="B18" s="63"/>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -14823,14 +14823,14 @@
       <c r="AC18" s="17"/>
       <c r="AD18" s="17"/>
       <c r="AE18" s="6"/>
-      <c r="AF18" s="61"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="62"/>
-      <c r="AK18" s="62"/>
-      <c r="AL18" s="62"/>
-      <c r="AM18" s="63"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="61"/>
+      <c r="AH18" s="61"/>
+      <c r="AI18" s="61"/>
+      <c r="AJ18" s="61"/>
+      <c r="AK18" s="61"/>
+      <c r="AL18" s="61"/>
+      <c r="AM18" s="68"/>
     </row>
     <row r="19" spans="1:39" ht="17.25" customHeight="1">
       <c r="A19" s="55"/>
@@ -14866,20 +14866,20 @@
       <c r="AC19" s="17"/>
       <c r="AD19" s="17"/>
       <c r="AE19" s="6"/>
-      <c r="AF19" s="61"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="62"/>
-      <c r="AL19" s="62"/>
-      <c r="AM19" s="63"/>
+      <c r="AF19" s="67"/>
+      <c r="AG19" s="61"/>
+      <c r="AH19" s="61"/>
+      <c r="AI19" s="61"/>
+      <c r="AJ19" s="61"/>
+      <c r="AK19" s="61"/>
+      <c r="AL19" s="61"/>
+      <c r="AM19" s="68"/>
     </row>
     <row r="20" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="56"/>
+      <c r="B20" s="54"/>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -14911,14 +14911,14 @@
       <c r="AC20" s="17"/>
       <c r="AD20" s="17"/>
       <c r="AE20" s="6"/>
-      <c r="AF20" s="61"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="62"/>
-      <c r="AL20" s="62"/>
-      <c r="AM20" s="63"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="61"/>
+      <c r="AH20" s="61"/>
+      <c r="AI20" s="61"/>
+      <c r="AJ20" s="61"/>
+      <c r="AK20" s="61"/>
+      <c r="AL20" s="61"/>
+      <c r="AM20" s="68"/>
     </row>
     <row r="21" spans="1:39" ht="14.25" customHeight="1">
       <c r="A21" s="55"/>
@@ -14954,20 +14954,20 @@
       <c r="AC21" s="17"/>
       <c r="AD21" s="17"/>
       <c r="AE21" s="6"/>
-      <c r="AF21" s="61"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="62"/>
-      <c r="AJ21" s="62"/>
-      <c r="AK21" s="62"/>
-      <c r="AL21" s="62"/>
-      <c r="AM21" s="63"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="61"/>
+      <c r="AH21" s="61"/>
+      <c r="AI21" s="61"/>
+      <c r="AJ21" s="61"/>
+      <c r="AK21" s="61"/>
+      <c r="AL21" s="61"/>
+      <c r="AM21" s="68"/>
     </row>
     <row r="22" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="56"/>
+      <c r="B22" s="54"/>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -14999,14 +14999,14 @@
       <c r="AC22" s="17"/>
       <c r="AD22" s="17"/>
       <c r="AE22" s="6"/>
-      <c r="AF22" s="61"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="62"/>
-      <c r="AL22" s="62"/>
-      <c r="AM22" s="63"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="61"/>
+      <c r="AH22" s="61"/>
+      <c r="AI22" s="61"/>
+      <c r="AJ22" s="61"/>
+      <c r="AK22" s="61"/>
+      <c r="AL22" s="61"/>
+      <c r="AM22" s="68"/>
     </row>
     <row r="23" spans="1:39" ht="14.25" customHeight="1">
       <c r="A23" s="55"/>
@@ -15042,20 +15042,20 @@
       <c r="AC23" s="17"/>
       <c r="AD23" s="17"/>
       <c r="AE23" s="6"/>
-      <c r="AF23" s="61"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="62"/>
-      <c r="AL23" s="62"/>
-      <c r="AM23" s="63"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="61"/>
+      <c r="AH23" s="61"/>
+      <c r="AI23" s="61"/>
+      <c r="AJ23" s="61"/>
+      <c r="AK23" s="61"/>
+      <c r="AL23" s="61"/>
+      <c r="AM23" s="68"/>
     </row>
     <row r="24" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="78"/>
+      <c r="B24" s="81"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -15087,14 +15087,14 @@
       <c r="AC24" s="17"/>
       <c r="AD24" s="17"/>
       <c r="AE24" s="6"/>
-      <c r="AF24" s="61"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="62"/>
-      <c r="AJ24" s="62"/>
-      <c r="AK24" s="62"/>
-      <c r="AL24" s="62"/>
-      <c r="AM24" s="63"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="61"/>
+      <c r="AH24" s="61"/>
+      <c r="AI24" s="61"/>
+      <c r="AJ24" s="61"/>
+      <c r="AK24" s="61"/>
+      <c r="AL24" s="61"/>
+      <c r="AM24" s="68"/>
     </row>
     <row r="25" spans="1:39" ht="14.25" customHeight="1">
       <c r="A25" s="55"/>
@@ -15130,20 +15130,20 @@
       <c r="AC25" s="17"/>
       <c r="AD25" s="17"/>
       <c r="AE25" s="6"/>
-      <c r="AF25" s="61"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
-      <c r="AK25" s="62"/>
-      <c r="AL25" s="62"/>
-      <c r="AM25" s="63"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="61"/>
+      <c r="AH25" s="61"/>
+      <c r="AI25" s="61"/>
+      <c r="AJ25" s="61"/>
+      <c r="AK25" s="61"/>
+      <c r="AL25" s="61"/>
+      <c r="AM25" s="68"/>
     </row>
     <row r="26" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="78"/>
+      <c r="B26" s="81"/>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -15175,14 +15175,14 @@
       <c r="AC26" s="17"/>
       <c r="AD26" s="17"/>
       <c r="AE26" s="6"/>
-      <c r="AF26" s="61"/>
-      <c r="AG26" s="62"/>
-      <c r="AH26" s="62"/>
-      <c r="AI26" s="62"/>
-      <c r="AJ26" s="62"/>
-      <c r="AK26" s="62"/>
-      <c r="AL26" s="62"/>
-      <c r="AM26" s="63"/>
+      <c r="AF26" s="67"/>
+      <c r="AG26" s="61"/>
+      <c r="AH26" s="61"/>
+      <c r="AI26" s="61"/>
+      <c r="AJ26" s="61"/>
+      <c r="AK26" s="61"/>
+      <c r="AL26" s="61"/>
+      <c r="AM26" s="68"/>
     </row>
     <row r="27" spans="1:39" ht="14.25" customHeight="1">
       <c r="A27" s="55"/>
@@ -15218,20 +15218,20 @@
       <c r="AC27" s="17"/>
       <c r="AD27" s="17"/>
       <c r="AE27" s="6"/>
-      <c r="AF27" s="61"/>
-      <c r="AG27" s="62"/>
-      <c r="AH27" s="62"/>
-      <c r="AI27" s="62"/>
-      <c r="AJ27" s="62"/>
-      <c r="AK27" s="62"/>
-      <c r="AL27" s="62"/>
-      <c r="AM27" s="63"/>
+      <c r="AF27" s="67"/>
+      <c r="AG27" s="61"/>
+      <c r="AH27" s="61"/>
+      <c r="AI27" s="61"/>
+      <c r="AJ27" s="61"/>
+      <c r="AK27" s="61"/>
+      <c r="AL27" s="61"/>
+      <c r="AM27" s="68"/>
     </row>
     <row r="28" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="78"/>
+      <c r="B28" s="81"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -15263,14 +15263,14 @@
       <c r="AC28" s="17"/>
       <c r="AD28" s="17"/>
       <c r="AE28" s="6"/>
-      <c r="AF28" s="61"/>
-      <c r="AG28" s="62"/>
-      <c r="AH28" s="62"/>
-      <c r="AI28" s="62"/>
-      <c r="AJ28" s="62"/>
-      <c r="AK28" s="62"/>
-      <c r="AL28" s="62"/>
-      <c r="AM28" s="63"/>
+      <c r="AF28" s="67"/>
+      <c r="AG28" s="61"/>
+      <c r="AH28" s="61"/>
+      <c r="AI28" s="61"/>
+      <c r="AJ28" s="61"/>
+      <c r="AK28" s="61"/>
+      <c r="AL28" s="61"/>
+      <c r="AM28" s="68"/>
     </row>
     <row r="29" spans="1:39" ht="14.25" customHeight="1">
       <c r="A29" s="55"/>
@@ -15306,20 +15306,20 @@
       <c r="AC29" s="17"/>
       <c r="AD29" s="17"/>
       <c r="AE29" s="6"/>
-      <c r="AF29" s="61"/>
-      <c r="AG29" s="62"/>
-      <c r="AH29" s="62"/>
-      <c r="AI29" s="62"/>
-      <c r="AJ29" s="62"/>
-      <c r="AK29" s="62"/>
-      <c r="AL29" s="62"/>
-      <c r="AM29" s="63"/>
+      <c r="AF29" s="67"/>
+      <c r="AG29" s="61"/>
+      <c r="AH29" s="61"/>
+      <c r="AI29" s="61"/>
+      <c r="AJ29" s="61"/>
+      <c r="AK29" s="61"/>
+      <c r="AL29" s="61"/>
+      <c r="AM29" s="68"/>
     </row>
     <row r="30" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="79"/>
+      <c r="B30" s="82"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -15351,14 +15351,14 @@
       <c r="AC30" s="17"/>
       <c r="AD30" s="17"/>
       <c r="AE30" s="6"/>
-      <c r="AF30" s="61"/>
-      <c r="AG30" s="62"/>
-      <c r="AH30" s="62"/>
-      <c r="AI30" s="62"/>
-      <c r="AJ30" s="62"/>
-      <c r="AK30" s="62"/>
-      <c r="AL30" s="62"/>
-      <c r="AM30" s="63"/>
+      <c r="AF30" s="67"/>
+      <c r="AG30" s="61"/>
+      <c r="AH30" s="61"/>
+      <c r="AI30" s="61"/>
+      <c r="AJ30" s="61"/>
+      <c r="AK30" s="61"/>
+      <c r="AL30" s="61"/>
+      <c r="AM30" s="68"/>
     </row>
     <row r="31" spans="1:39" ht="14.25" customHeight="1">
       <c r="A31" s="55"/>
@@ -15394,20 +15394,20 @@
       <c r="AC31" s="17"/>
       <c r="AD31" s="17"/>
       <c r="AE31" s="6"/>
-      <c r="AF31" s="61"/>
-      <c r="AG31" s="62"/>
-      <c r="AH31" s="62"/>
-      <c r="AI31" s="62"/>
-      <c r="AJ31" s="62"/>
-      <c r="AK31" s="62"/>
-      <c r="AL31" s="62"/>
-      <c r="AM31" s="63"/>
+      <c r="AF31" s="67"/>
+      <c r="AG31" s="61"/>
+      <c r="AH31" s="61"/>
+      <c r="AI31" s="61"/>
+      <c r="AJ31" s="61"/>
+      <c r="AK31" s="61"/>
+      <c r="AL31" s="61"/>
+      <c r="AM31" s="68"/>
     </row>
     <row r="32" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="79"/>
+      <c r="B32" s="82"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -15439,14 +15439,14 @@
       <c r="AC32" s="17"/>
       <c r="AD32" s="17"/>
       <c r="AE32" s="6"/>
-      <c r="AF32" s="61"/>
-      <c r="AG32" s="62"/>
-      <c r="AH32" s="62"/>
-      <c r="AI32" s="62"/>
-      <c r="AJ32" s="62"/>
-      <c r="AK32" s="62"/>
-      <c r="AL32" s="62"/>
-      <c r="AM32" s="63"/>
+      <c r="AF32" s="67"/>
+      <c r="AG32" s="61"/>
+      <c r="AH32" s="61"/>
+      <c r="AI32" s="61"/>
+      <c r="AJ32" s="61"/>
+      <c r="AK32" s="61"/>
+      <c r="AL32" s="61"/>
+      <c r="AM32" s="68"/>
     </row>
     <row r="33" spans="1:39" ht="14.25" customHeight="1">
       <c r="A33" s="55"/>
@@ -15482,20 +15482,20 @@
       <c r="AC33" s="17"/>
       <c r="AD33" s="17"/>
       <c r="AE33" s="6"/>
-      <c r="AF33" s="61"/>
-      <c r="AG33" s="62"/>
-      <c r="AH33" s="62"/>
-      <c r="AI33" s="62"/>
-      <c r="AJ33" s="62"/>
-      <c r="AK33" s="62"/>
-      <c r="AL33" s="62"/>
-      <c r="AM33" s="63"/>
+      <c r="AF33" s="67"/>
+      <c r="AG33" s="61"/>
+      <c r="AH33" s="61"/>
+      <c r="AI33" s="61"/>
+      <c r="AJ33" s="61"/>
+      <c r="AK33" s="61"/>
+      <c r="AL33" s="61"/>
+      <c r="AM33" s="68"/>
     </row>
     <row r="34" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="79"/>
+      <c r="B34" s="82"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -15527,14 +15527,14 @@
       <c r="AC34" s="17"/>
       <c r="AD34" s="17"/>
       <c r="AE34" s="6"/>
-      <c r="AF34" s="61"/>
-      <c r="AG34" s="62"/>
-      <c r="AH34" s="62"/>
-      <c r="AI34" s="62"/>
-      <c r="AJ34" s="62"/>
-      <c r="AK34" s="62"/>
-      <c r="AL34" s="62"/>
-      <c r="AM34" s="63"/>
+      <c r="AF34" s="67"/>
+      <c r="AG34" s="61"/>
+      <c r="AH34" s="61"/>
+      <c r="AI34" s="61"/>
+      <c r="AJ34" s="61"/>
+      <c r="AK34" s="61"/>
+      <c r="AL34" s="61"/>
+      <c r="AM34" s="68"/>
     </row>
     <row r="35" spans="1:39" ht="14.25" customHeight="1">
       <c r="A35" s="55"/>
@@ -15570,20 +15570,20 @@
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
       <c r="AE35" s="6"/>
-      <c r="AF35" s="61"/>
-      <c r="AG35" s="62"/>
-      <c r="AH35" s="62"/>
-      <c r="AI35" s="62"/>
-      <c r="AJ35" s="62"/>
-      <c r="AK35" s="62"/>
-      <c r="AL35" s="62"/>
-      <c r="AM35" s="63"/>
+      <c r="AF35" s="67"/>
+      <c r="AG35" s="61"/>
+      <c r="AH35" s="61"/>
+      <c r="AI35" s="61"/>
+      <c r="AJ35" s="61"/>
+      <c r="AK35" s="61"/>
+      <c r="AL35" s="61"/>
+      <c r="AM35" s="68"/>
     </row>
     <row r="36" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="79"/>
+      <c r="B36" s="82"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -15615,14 +15615,14 @@
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
       <c r="AE36" s="6"/>
-      <c r="AF36" s="61"/>
-      <c r="AG36" s="62"/>
-      <c r="AH36" s="62"/>
-      <c r="AI36" s="62"/>
-      <c r="AJ36" s="62"/>
-      <c r="AK36" s="62"/>
-      <c r="AL36" s="62"/>
-      <c r="AM36" s="63"/>
+      <c r="AF36" s="67"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="61"/>
+      <c r="AK36" s="61"/>
+      <c r="AL36" s="61"/>
+      <c r="AM36" s="68"/>
     </row>
     <row r="37" spans="1:39" ht="14.25" customHeight="1">
       <c r="A37" s="55"/>
@@ -15658,20 +15658,20 @@
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
       <c r="AE37" s="6"/>
-      <c r="AF37" s="64"/>
-      <c r="AG37" s="65"/>
-      <c r="AH37" s="65"/>
-      <c r="AI37" s="65"/>
-      <c r="AJ37" s="65"/>
-      <c r="AK37" s="65"/>
-      <c r="AL37" s="65"/>
-      <c r="AM37" s="66"/>
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="70"/>
+      <c r="AH37" s="70"/>
+      <c r="AI37" s="70"/>
+      <c r="AJ37" s="70"/>
+      <c r="AK37" s="70"/>
+      <c r="AL37" s="70"/>
+      <c r="AM37" s="71"/>
     </row>
     <row r="38" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="79"/>
+      <c r="B38" s="82"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -15756,10 +15756,10 @@
       <c r="AM39" s="52"/>
     </row>
     <row r="40" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="79"/>
+      <c r="B40" s="82"/>
       <c r="D40" s="22"/>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -15844,10 +15844,10 @@
       <c r="AM41" s="52"/>
     </row>
     <row r="42" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="79"/>
+      <c r="B42" s="82"/>
       <c r="D42" s="22"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -15932,10 +15932,10 @@
       <c r="AM43" s="52"/>
     </row>
     <row r="44" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="79"/>
+      <c r="B44" s="82"/>
       <c r="D44" s="22"/>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -15967,14 +15967,14 @@
       <c r="AC44" s="17"/>
       <c r="AD44" s="17"/>
       <c r="AE44" s="6"/>
-      <c r="AF44" s="70"/>
-      <c r="AG44" s="71"/>
-      <c r="AH44" s="71"/>
-      <c r="AI44" s="71"/>
-      <c r="AJ44" s="71"/>
-      <c r="AK44" s="71"/>
-      <c r="AL44" s="71"/>
-      <c r="AM44" s="72"/>
+      <c r="AF44" s="73"/>
+      <c r="AG44" s="74"/>
+      <c r="AH44" s="74"/>
+      <c r="AI44" s="74"/>
+      <c r="AJ44" s="74"/>
+      <c r="AK44" s="74"/>
+      <c r="AL44" s="74"/>
+      <c r="AM44" s="75"/>
     </row>
     <row r="45" spans="1:39" ht="18" customHeight="1">
       <c r="A45" s="55"/>
@@ -16010,20 +16010,20 @@
       <c r="AC45" s="17"/>
       <c r="AD45" s="17"/>
       <c r="AE45" s="6"/>
-      <c r="AF45" s="73"/>
-      <c r="AG45" s="62"/>
-      <c r="AH45" s="62"/>
-      <c r="AI45" s="62"/>
-      <c r="AJ45" s="62"/>
-      <c r="AK45" s="62"/>
-      <c r="AL45" s="62"/>
-      <c r="AM45" s="74"/>
+      <c r="AF45" s="76"/>
+      <c r="AG45" s="61"/>
+      <c r="AH45" s="61"/>
+      <c r="AI45" s="61"/>
+      <c r="AJ45" s="61"/>
+      <c r="AK45" s="61"/>
+      <c r="AL45" s="61"/>
+      <c r="AM45" s="77"/>
     </row>
     <row r="46" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A46" s="54" t="s">
+      <c r="A46" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="79"/>
+      <c r="B46" s="82"/>
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -16055,14 +16055,14 @@
       <c r="AC46" s="17"/>
       <c r="AD46" s="17"/>
       <c r="AE46" s="6"/>
-      <c r="AF46" s="73"/>
-      <c r="AG46" s="62"/>
-      <c r="AH46" s="62"/>
-      <c r="AI46" s="62"/>
-      <c r="AJ46" s="62"/>
-      <c r="AK46" s="62"/>
-      <c r="AL46" s="62"/>
-      <c r="AM46" s="74"/>
+      <c r="AF46" s="76"/>
+      <c r="AG46" s="61"/>
+      <c r="AH46" s="61"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="61"/>
+      <c r="AK46" s="61"/>
+      <c r="AL46" s="61"/>
+      <c r="AM46" s="77"/>
     </row>
     <row r="47" spans="1:39" ht="18" customHeight="1">
       <c r="A47" s="55"/>
@@ -16098,20 +16098,20 @@
       <c r="AC47" s="17"/>
       <c r="AD47" s="17"/>
       <c r="AE47" s="6"/>
-      <c r="AF47" s="73"/>
-      <c r="AG47" s="62"/>
-      <c r="AH47" s="62"/>
-      <c r="AI47" s="62"/>
-      <c r="AJ47" s="62"/>
-      <c r="AK47" s="62"/>
-      <c r="AL47" s="62"/>
-      <c r="AM47" s="74"/>
+      <c r="AF47" s="76"/>
+      <c r="AG47" s="61"/>
+      <c r="AH47" s="61"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="61"/>
+      <c r="AL47" s="61"/>
+      <c r="AM47" s="77"/>
     </row>
     <row r="48" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A48" s="54" t="s">
+      <c r="A48" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="79"/>
+      <c r="B48" s="82"/>
       <c r="D48" s="22"/>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -16143,14 +16143,14 @@
       <c r="AC48" s="17"/>
       <c r="AD48" s="17"/>
       <c r="AE48" s="6"/>
-      <c r="AF48" s="73"/>
-      <c r="AG48" s="62"/>
-      <c r="AH48" s="62"/>
-      <c r="AI48" s="62"/>
-      <c r="AJ48" s="62"/>
-      <c r="AK48" s="62"/>
-      <c r="AL48" s="62"/>
-      <c r="AM48" s="74"/>
+      <c r="AF48" s="76"/>
+      <c r="AG48" s="61"/>
+      <c r="AH48" s="61"/>
+      <c r="AI48" s="61"/>
+      <c r="AJ48" s="61"/>
+      <c r="AK48" s="61"/>
+      <c r="AL48" s="61"/>
+      <c r="AM48" s="77"/>
     </row>
     <row r="49" spans="1:39" ht="14.25" customHeight="1">
       <c r="A49" s="55"/>
@@ -16186,20 +16186,20 @@
       <c r="AC49" s="17"/>
       <c r="AD49" s="17"/>
       <c r="AE49" s="6"/>
-      <c r="AF49" s="73"/>
-      <c r="AG49" s="62"/>
-      <c r="AH49" s="62"/>
-      <c r="AI49" s="62"/>
-      <c r="AJ49" s="62"/>
-      <c r="AK49" s="62"/>
-      <c r="AL49" s="62"/>
-      <c r="AM49" s="74"/>
+      <c r="AF49" s="76"/>
+      <c r="AG49" s="61"/>
+      <c r="AH49" s="61"/>
+      <c r="AI49" s="61"/>
+      <c r="AJ49" s="61"/>
+      <c r="AK49" s="61"/>
+      <c r="AL49" s="61"/>
+      <c r="AM49" s="77"/>
     </row>
     <row r="50" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A50" s="54" t="s">
+      <c r="A50" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="79"/>
+      <c r="B50" s="82"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -16231,14 +16231,14 @@
       <c r="AC50" s="17"/>
       <c r="AD50" s="17"/>
       <c r="AE50" s="6"/>
-      <c r="AF50" s="73"/>
-      <c r="AG50" s="62"/>
-      <c r="AH50" s="62"/>
-      <c r="AI50" s="62"/>
-      <c r="AJ50" s="62"/>
-      <c r="AK50" s="62"/>
-      <c r="AL50" s="62"/>
-      <c r="AM50" s="74"/>
+      <c r="AF50" s="76"/>
+      <c r="AG50" s="61"/>
+      <c r="AH50" s="61"/>
+      <c r="AI50" s="61"/>
+      <c r="AJ50" s="61"/>
+      <c r="AK50" s="61"/>
+      <c r="AL50" s="61"/>
+      <c r="AM50" s="77"/>
     </row>
     <row r="51" spans="1:39" ht="18" customHeight="1">
       <c r="A51" s="55"/>
@@ -16274,20 +16274,20 @@
       <c r="AC51" s="17"/>
       <c r="AD51" s="17"/>
       <c r="AE51" s="6"/>
-      <c r="AF51" s="73"/>
-      <c r="AG51" s="62"/>
-      <c r="AH51" s="62"/>
-      <c r="AI51" s="62"/>
-      <c r="AJ51" s="62"/>
-      <c r="AK51" s="62"/>
-      <c r="AL51" s="62"/>
-      <c r="AM51" s="74"/>
+      <c r="AF51" s="76"/>
+      <c r="AG51" s="61"/>
+      <c r="AH51" s="61"/>
+      <c r="AI51" s="61"/>
+      <c r="AJ51" s="61"/>
+      <c r="AK51" s="61"/>
+      <c r="AL51" s="61"/>
+      <c r="AM51" s="77"/>
     </row>
     <row r="52" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A52" s="54" t="s">
+      <c r="A52" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="79"/>
+      <c r="B52" s="82"/>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
@@ -16319,14 +16319,14 @@
       <c r="AC52" s="17"/>
       <c r="AD52" s="17"/>
       <c r="AE52" s="6"/>
-      <c r="AF52" s="73"/>
-      <c r="AG52" s="62"/>
-      <c r="AH52" s="62"/>
-      <c r="AI52" s="62"/>
-      <c r="AJ52" s="62"/>
-      <c r="AK52" s="62"/>
-      <c r="AL52" s="62"/>
-      <c r="AM52" s="74"/>
+      <c r="AF52" s="76"/>
+      <c r="AG52" s="61"/>
+      <c r="AH52" s="61"/>
+      <c r="AI52" s="61"/>
+      <c r="AJ52" s="61"/>
+      <c r="AK52" s="61"/>
+      <c r="AL52" s="61"/>
+      <c r="AM52" s="77"/>
     </row>
     <row r="53" spans="1:39" ht="18" customHeight="1">
       <c r="A53" s="55"/>
@@ -16362,20 +16362,20 @@
       <c r="AC53" s="17"/>
       <c r="AD53" s="17"/>
       <c r="AE53" s="6"/>
-      <c r="AF53" s="73"/>
-      <c r="AG53" s="62"/>
-      <c r="AH53" s="62"/>
-      <c r="AI53" s="62"/>
-      <c r="AJ53" s="62"/>
-      <c r="AK53" s="62"/>
-      <c r="AL53" s="62"/>
-      <c r="AM53" s="74"/>
+      <c r="AF53" s="76"/>
+      <c r="AG53" s="61"/>
+      <c r="AH53" s="61"/>
+      <c r="AI53" s="61"/>
+      <c r="AJ53" s="61"/>
+      <c r="AK53" s="61"/>
+      <c r="AL53" s="61"/>
+      <c r="AM53" s="77"/>
     </row>
     <row r="54" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A54" s="54" t="s">
+      <c r="A54" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="79"/>
+      <c r="B54" s="82"/>
       <c r="D54" s="22"/>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -16407,14 +16407,14 @@
       <c r="AC54" s="17"/>
       <c r="AD54" s="17"/>
       <c r="AE54" s="6"/>
-      <c r="AF54" s="73"/>
-      <c r="AG54" s="62"/>
-      <c r="AH54" s="62"/>
-      <c r="AI54" s="62"/>
-      <c r="AJ54" s="62"/>
-      <c r="AK54" s="62"/>
-      <c r="AL54" s="62"/>
-      <c r="AM54" s="74"/>
+      <c r="AF54" s="76"/>
+      <c r="AG54" s="61"/>
+      <c r="AH54" s="61"/>
+      <c r="AI54" s="61"/>
+      <c r="AJ54" s="61"/>
+      <c r="AK54" s="61"/>
+      <c r="AL54" s="61"/>
+      <c r="AM54" s="77"/>
     </row>
     <row r="55" spans="1:39" ht="18" customHeight="1">
       <c r="A55" s="55"/>
@@ -16450,20 +16450,20 @@
       <c r="AC55" s="17"/>
       <c r="AD55" s="17"/>
       <c r="AE55" s="6"/>
-      <c r="AF55" s="73"/>
-      <c r="AG55" s="62"/>
-      <c r="AH55" s="62"/>
-      <c r="AI55" s="62"/>
-      <c r="AJ55" s="62"/>
-      <c r="AK55" s="62"/>
-      <c r="AL55" s="62"/>
-      <c r="AM55" s="74"/>
+      <c r="AF55" s="76"/>
+      <c r="AG55" s="61"/>
+      <c r="AH55" s="61"/>
+      <c r="AI55" s="61"/>
+      <c r="AJ55" s="61"/>
+      <c r="AK55" s="61"/>
+      <c r="AL55" s="61"/>
+      <c r="AM55" s="77"/>
     </row>
     <row r="56" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A56" s="54" t="s">
+      <c r="A56" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="79"/>
+      <c r="B56" s="82"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -16495,14 +16495,14 @@
       <c r="AC56" s="17"/>
       <c r="AD56" s="17"/>
       <c r="AE56" s="6"/>
-      <c r="AF56" s="73"/>
-      <c r="AG56" s="62"/>
-      <c r="AH56" s="62"/>
-      <c r="AI56" s="62"/>
-      <c r="AJ56" s="62"/>
-      <c r="AK56" s="62"/>
-      <c r="AL56" s="62"/>
-      <c r="AM56" s="74"/>
+      <c r="AF56" s="76"/>
+      <c r="AG56" s="61"/>
+      <c r="AH56" s="61"/>
+      <c r="AI56" s="61"/>
+      <c r="AJ56" s="61"/>
+      <c r="AK56" s="61"/>
+      <c r="AL56" s="61"/>
+      <c r="AM56" s="77"/>
     </row>
     <row r="57" spans="1:39" ht="14.25" customHeight="1">
       <c r="A57" s="55"/>
@@ -16538,20 +16538,20 @@
       <c r="AC57" s="17"/>
       <c r="AD57" s="17"/>
       <c r="AE57" s="6"/>
-      <c r="AF57" s="73"/>
-      <c r="AG57" s="62"/>
-      <c r="AH57" s="62"/>
-      <c r="AI57" s="62"/>
-      <c r="AJ57" s="62"/>
-      <c r="AK57" s="62"/>
-      <c r="AL57" s="62"/>
-      <c r="AM57" s="74"/>
+      <c r="AF57" s="76"/>
+      <c r="AG57" s="61"/>
+      <c r="AH57" s="61"/>
+      <c r="AI57" s="61"/>
+      <c r="AJ57" s="61"/>
+      <c r="AK57" s="61"/>
+      <c r="AL57" s="61"/>
+      <c r="AM57" s="77"/>
     </row>
     <row r="58" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A58" s="54" t="s">
+      <c r="A58" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="B58" s="79"/>
+      <c r="B58" s="82"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -16583,14 +16583,14 @@
       <c r="AC58" s="17"/>
       <c r="AD58" s="17"/>
       <c r="AE58" s="6"/>
-      <c r="AF58" s="73"/>
-      <c r="AG58" s="62"/>
-      <c r="AH58" s="62"/>
-      <c r="AI58" s="62"/>
-      <c r="AJ58" s="62"/>
-      <c r="AK58" s="62"/>
-      <c r="AL58" s="62"/>
-      <c r="AM58" s="74"/>
+      <c r="AF58" s="76"/>
+      <c r="AG58" s="61"/>
+      <c r="AH58" s="61"/>
+      <c r="AI58" s="61"/>
+      <c r="AJ58" s="61"/>
+      <c r="AK58" s="61"/>
+      <c r="AL58" s="61"/>
+      <c r="AM58" s="77"/>
     </row>
     <row r="59" spans="1:39" ht="18" customHeight="1">
       <c r="A59" s="55"/>
@@ -16626,20 +16626,20 @@
       <c r="AC59" s="17"/>
       <c r="AD59" s="17"/>
       <c r="AE59" s="6"/>
-      <c r="AF59" s="73"/>
-      <c r="AG59" s="62"/>
-      <c r="AH59" s="62"/>
-      <c r="AI59" s="62"/>
-      <c r="AJ59" s="62"/>
-      <c r="AK59" s="62"/>
-      <c r="AL59" s="62"/>
-      <c r="AM59" s="74"/>
+      <c r="AF59" s="76"/>
+      <c r="AG59" s="61"/>
+      <c r="AH59" s="61"/>
+      <c r="AI59" s="61"/>
+      <c r="AJ59" s="61"/>
+      <c r="AK59" s="61"/>
+      <c r="AL59" s="61"/>
+      <c r="AM59" s="77"/>
     </row>
     <row r="60" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A60" s="54" t="s">
+      <c r="A60" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="79"/>
+      <c r="B60" s="82"/>
       <c r="D60" s="22"/>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -16671,14 +16671,14 @@
       <c r="AC60" s="17"/>
       <c r="AD60" s="17"/>
       <c r="AE60" s="6"/>
-      <c r="AF60" s="73"/>
-      <c r="AG60" s="62"/>
-      <c r="AH60" s="62"/>
-      <c r="AI60" s="62"/>
-      <c r="AJ60" s="62"/>
-      <c r="AK60" s="62"/>
-      <c r="AL60" s="62"/>
-      <c r="AM60" s="74"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="61"/>
+      <c r="AH60" s="61"/>
+      <c r="AI60" s="61"/>
+      <c r="AJ60" s="61"/>
+      <c r="AK60" s="61"/>
+      <c r="AL60" s="61"/>
+      <c r="AM60" s="77"/>
     </row>
     <row r="61" spans="1:39" ht="18" customHeight="1">
       <c r="A61" s="55"/>
@@ -16714,20 +16714,20 @@
       <c r="AC61" s="17"/>
       <c r="AD61" s="17"/>
       <c r="AE61" s="6"/>
-      <c r="AF61" s="73"/>
-      <c r="AG61" s="62"/>
-      <c r="AH61" s="62"/>
-      <c r="AI61" s="62"/>
-      <c r="AJ61" s="62"/>
-      <c r="AK61" s="62"/>
-      <c r="AL61" s="62"/>
-      <c r="AM61" s="74"/>
+      <c r="AF61" s="76"/>
+      <c r="AG61" s="61"/>
+      <c r="AH61" s="61"/>
+      <c r="AI61" s="61"/>
+      <c r="AJ61" s="61"/>
+      <c r="AK61" s="61"/>
+      <c r="AL61" s="61"/>
+      <c r="AM61" s="77"/>
     </row>
     <row r="62" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="79"/>
+      <c r="B62" s="82"/>
       <c r="D62" s="22"/>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -16759,14 +16759,14 @@
       <c r="AC62" s="17"/>
       <c r="AD62" s="17"/>
       <c r="AE62" s="6"/>
-      <c r="AF62" s="73"/>
-      <c r="AG62" s="62"/>
-      <c r="AH62" s="62"/>
-      <c r="AI62" s="62"/>
-      <c r="AJ62" s="62"/>
-      <c r="AK62" s="62"/>
-      <c r="AL62" s="62"/>
-      <c r="AM62" s="74"/>
+      <c r="AF62" s="76"/>
+      <c r="AG62" s="61"/>
+      <c r="AH62" s="61"/>
+      <c r="AI62" s="61"/>
+      <c r="AJ62" s="61"/>
+      <c r="AK62" s="61"/>
+      <c r="AL62" s="61"/>
+      <c r="AM62" s="77"/>
     </row>
     <row r="63" spans="1:39" ht="18" customHeight="1">
       <c r="A63" s="55"/>
@@ -16802,20 +16802,20 @@
       <c r="AC63" s="32"/>
       <c r="AD63" s="32"/>
       <c r="AE63" s="6"/>
-      <c r="AF63" s="73"/>
-      <c r="AG63" s="62"/>
-      <c r="AH63" s="62"/>
-      <c r="AI63" s="62"/>
-      <c r="AJ63" s="62"/>
-      <c r="AK63" s="62"/>
-      <c r="AL63" s="62"/>
-      <c r="AM63" s="74"/>
+      <c r="AF63" s="76"/>
+      <c r="AG63" s="61"/>
+      <c r="AH63" s="61"/>
+      <c r="AI63" s="61"/>
+      <c r="AJ63" s="61"/>
+      <c r="AK63" s="61"/>
+      <c r="AL63" s="61"/>
+      <c r="AM63" s="77"/>
     </row>
     <row r="64" spans="1:39" ht="17.25" customHeight="1">
-      <c r="A64" s="54" t="s">
+      <c r="A64" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="B64" s="79"/>
+      <c r="B64" s="82"/>
       <c r="D64" s="22"/>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
@@ -16847,14 +16847,14 @@
       <c r="AC64" s="32"/>
       <c r="AD64" s="32"/>
       <c r="AE64" s="6"/>
-      <c r="AF64" s="73"/>
-      <c r="AG64" s="62"/>
-      <c r="AH64" s="62"/>
-      <c r="AI64" s="62"/>
-      <c r="AJ64" s="62"/>
-      <c r="AK64" s="62"/>
-      <c r="AL64" s="62"/>
-      <c r="AM64" s="74"/>
+      <c r="AF64" s="76"/>
+      <c r="AG64" s="61"/>
+      <c r="AH64" s="61"/>
+      <c r="AI64" s="61"/>
+      <c r="AJ64" s="61"/>
+      <c r="AK64" s="61"/>
+      <c r="AL64" s="61"/>
+      <c r="AM64" s="77"/>
     </row>
     <row r="65" spans="1:39" ht="18" customHeight="1">
       <c r="A65" s="55"/>
@@ -16890,20 +16890,20 @@
       <c r="AC65" s="32"/>
       <c r="AD65" s="32"/>
       <c r="AE65" s="6"/>
-      <c r="AF65" s="73"/>
-      <c r="AG65" s="62"/>
-      <c r="AH65" s="62"/>
-      <c r="AI65" s="62"/>
-      <c r="AJ65" s="62"/>
-      <c r="AK65" s="62"/>
-      <c r="AL65" s="62"/>
-      <c r="AM65" s="74"/>
+      <c r="AF65" s="76"/>
+      <c r="AG65" s="61"/>
+      <c r="AH65" s="61"/>
+      <c r="AI65" s="61"/>
+      <c r="AJ65" s="61"/>
+      <c r="AK65" s="61"/>
+      <c r="AL65" s="61"/>
+      <c r="AM65" s="77"/>
     </row>
     <row r="66" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A66" s="54" t="s">
+      <c r="A66" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B66" s="56"/>
+      <c r="B66" s="54"/>
       <c r="D66" s="22"/>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
@@ -16935,14 +16935,14 @@
       <c r="AC66" s="17"/>
       <c r="AD66" s="17"/>
       <c r="AE66" s="6"/>
-      <c r="AF66" s="73"/>
-      <c r="AG66" s="62"/>
-      <c r="AH66" s="62"/>
-      <c r="AI66" s="62"/>
-      <c r="AJ66" s="62"/>
-      <c r="AK66" s="62"/>
-      <c r="AL66" s="62"/>
-      <c r="AM66" s="74"/>
+      <c r="AF66" s="76"/>
+      <c r="AG66" s="61"/>
+      <c r="AH66" s="61"/>
+      <c r="AI66" s="61"/>
+      <c r="AJ66" s="61"/>
+      <c r="AK66" s="61"/>
+      <c r="AL66" s="61"/>
+      <c r="AM66" s="77"/>
     </row>
     <row r="67" spans="1:39" ht="14.25" customHeight="1">
       <c r="A67" s="55"/>
@@ -16978,20 +16978,20 @@
       <c r="AC67" s="17"/>
       <c r="AD67" s="17"/>
       <c r="AE67" s="6"/>
-      <c r="AF67" s="73"/>
-      <c r="AG67" s="62"/>
-      <c r="AH67" s="62"/>
-      <c r="AI67" s="62"/>
-      <c r="AJ67" s="62"/>
-      <c r="AK67" s="62"/>
-      <c r="AL67" s="62"/>
-      <c r="AM67" s="74"/>
+      <c r="AF67" s="76"/>
+      <c r="AG67" s="61"/>
+      <c r="AH67" s="61"/>
+      <c r="AI67" s="61"/>
+      <c r="AJ67" s="61"/>
+      <c r="AK67" s="61"/>
+      <c r="AL67" s="61"/>
+      <c r="AM67" s="77"/>
     </row>
     <row r="68" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A68" s="54" t="s">
+      <c r="A68" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B68" s="56"/>
+      <c r="B68" s="54"/>
       <c r="D68" s="22"/>
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
@@ -17023,14 +17023,14 @@
       <c r="AC68" s="17"/>
       <c r="AD68" s="17"/>
       <c r="AE68" s="6"/>
-      <c r="AF68" s="73"/>
-      <c r="AG68" s="62"/>
-      <c r="AH68" s="62"/>
-      <c r="AI68" s="62"/>
-      <c r="AJ68" s="62"/>
-      <c r="AK68" s="62"/>
-      <c r="AL68" s="62"/>
-      <c r="AM68" s="74"/>
+      <c r="AF68" s="76"/>
+      <c r="AG68" s="61"/>
+      <c r="AH68" s="61"/>
+      <c r="AI68" s="61"/>
+      <c r="AJ68" s="61"/>
+      <c r="AK68" s="61"/>
+      <c r="AL68" s="61"/>
+      <c r="AM68" s="77"/>
     </row>
     <row r="69" spans="1:39" ht="14.25" customHeight="1">
       <c r="A69" s="55"/>
@@ -17066,20 +17066,20 @@
       <c r="AC69" s="17"/>
       <c r="AD69" s="17"/>
       <c r="AE69" s="6"/>
-      <c r="AF69" s="73"/>
-      <c r="AG69" s="62"/>
-      <c r="AH69" s="62"/>
-      <c r="AI69" s="62"/>
-      <c r="AJ69" s="62"/>
-      <c r="AK69" s="62"/>
-      <c r="AL69" s="62"/>
-      <c r="AM69" s="74"/>
+      <c r="AF69" s="76"/>
+      <c r="AG69" s="61"/>
+      <c r="AH69" s="61"/>
+      <c r="AI69" s="61"/>
+      <c r="AJ69" s="61"/>
+      <c r="AK69" s="61"/>
+      <c r="AL69" s="61"/>
+      <c r="AM69" s="77"/>
     </row>
     <row r="70" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A70" s="54" t="s">
+      <c r="A70" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B70" s="56"/>
+      <c r="B70" s="54"/>
       <c r="D70" s="22"/>
       <c r="E70" s="22"/>
       <c r="F70" s="22"/>
@@ -17111,14 +17111,14 @@
       <c r="AC70" s="17"/>
       <c r="AD70" s="17"/>
       <c r="AE70" s="6"/>
-      <c r="AF70" s="73"/>
-      <c r="AG70" s="62"/>
-      <c r="AH70" s="62"/>
-      <c r="AI70" s="62"/>
-      <c r="AJ70" s="62"/>
-      <c r="AK70" s="62"/>
-      <c r="AL70" s="62"/>
-      <c r="AM70" s="74"/>
+      <c r="AF70" s="76"/>
+      <c r="AG70" s="61"/>
+      <c r="AH70" s="61"/>
+      <c r="AI70" s="61"/>
+      <c r="AJ70" s="61"/>
+      <c r="AK70" s="61"/>
+      <c r="AL70" s="61"/>
+      <c r="AM70" s="77"/>
     </row>
     <row r="71" spans="1:39" ht="14.25" customHeight="1">
       <c r="A71" s="55"/>
@@ -17154,20 +17154,20 @@
       <c r="AC71" s="17"/>
       <c r="AD71" s="17"/>
       <c r="AE71" s="6"/>
-      <c r="AF71" s="73"/>
-      <c r="AG71" s="62"/>
-      <c r="AH71" s="62"/>
-      <c r="AI71" s="62"/>
-      <c r="AJ71" s="62"/>
-      <c r="AK71" s="62"/>
-      <c r="AL71" s="62"/>
-      <c r="AM71" s="74"/>
+      <c r="AF71" s="76"/>
+      <c r="AG71" s="61"/>
+      <c r="AH71" s="61"/>
+      <c r="AI71" s="61"/>
+      <c r="AJ71" s="61"/>
+      <c r="AK71" s="61"/>
+      <c r="AL71" s="61"/>
+      <c r="AM71" s="77"/>
     </row>
     <row r="72" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A72" s="54" t="s">
+      <c r="A72" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B72" s="56"/>
+      <c r="B72" s="54"/>
       <c r="D72" s="22"/>
       <c r="E72" s="22"/>
       <c r="F72" s="22"/>
@@ -17199,14 +17199,14 @@
       <c r="AC72" s="17"/>
       <c r="AD72" s="17"/>
       <c r="AE72" s="6"/>
-      <c r="AF72" s="75"/>
-      <c r="AG72" s="76"/>
-      <c r="AH72" s="76"/>
-      <c r="AI72" s="76"/>
-      <c r="AJ72" s="76"/>
-      <c r="AK72" s="76"/>
-      <c r="AL72" s="76"/>
-      <c r="AM72" s="77"/>
+      <c r="AF72" s="78"/>
+      <c r="AG72" s="79"/>
+      <c r="AH72" s="79"/>
+      <c r="AI72" s="79"/>
+      <c r="AJ72" s="79"/>
+      <c r="AK72" s="79"/>
+      <c r="AL72" s="79"/>
+      <c r="AM72" s="80"/>
     </row>
     <row r="73" spans="1:39" ht="14.25" customHeight="1">
       <c r="A73" s="55"/>
@@ -17254,10 +17254,10 @@
       <c r="AM73" s="38"/>
     </row>
     <row r="74" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A74" s="54" t="s">
+      <c r="A74" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B74" s="56"/>
+      <c r="B74" s="54"/>
       <c r="D74" s="22"/>
       <c r="E74" s="22"/>
       <c r="F74" s="22"/>
@@ -17346,8 +17346,8 @@
       <c r="AM75" s="38"/>
     </row>
     <row r="76" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A76" s="57"/>
-      <c r="B76" s="57"/>
+      <c r="A76" s="83"/>
+      <c r="B76" s="83"/>
       <c r="D76" s="22"/>
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
@@ -17436,8 +17436,8 @@
       <c r="AM77" s="38"/>
     </row>
     <row r="78" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A78" s="57"/>
-      <c r="B78" s="57"/>
+      <c r="A78" s="83"/>
+      <c r="B78" s="83"/>
       <c r="D78" s="22"/>
       <c r="E78" s="22"/>
       <c r="F78" s="22"/>
@@ -17524,8 +17524,8 @@
       <c r="AM79" s="38"/>
     </row>
     <row r="80" spans="1:39" ht="14.25" customHeight="1">
-      <c r="A80" s="57"/>
-      <c r="B80" s="57"/>
+      <c r="A80" s="83"/>
+      <c r="B80" s="83"/>
       <c r="D80" s="22"/>
       <c r="E80" s="22"/>
       <c r="F80" s="22"/>
@@ -18569,60 +18569,17 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="AF3:AM37"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="AF44:AM72"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B78:B79"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A48:A49"/>
@@ -18639,17 +18596,60 @@
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="AF44:AM72"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="AF3:AM37"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="86" orientation="portrait"/>
